--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E96AF0-DC2A-410E-BD07-8756402E5142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B966D7-976E-4995-9441-26AE6CB70811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -225,6 +225,105 @@
     <t>カード4種</t>
     <rPh sb="4" eb="5">
       <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変身時</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セレクトシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボーナスシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアシーン(?)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵がダメージを食らったときのエフェクト</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予想コスト</t>
+    <rPh sb="0" eb="2">
+      <t>ヨソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインマップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1コスト1時間</t>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -250,7 +349,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,8 +368,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -279,38 +390,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -321,23 +410,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -674,199 +766,527 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FBCCA6-458C-4FC6-A258-62A5B476A274}">
-  <dimension ref="B12:D57"/>
+  <dimension ref="B8:I62"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="4" max="4" width="12.375" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="12" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B13" s="1" t="s">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B13" s="1"/>
+      <c r="C13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B17" s="3" t="s">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B18" s="3" t="s">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B19" s="3"/>
-      <c r="C19" t="s">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B20" s="3"/>
-      <c r="C20" t="s">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B21" s="3"/>
-      <c r="C21" t="s">
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B22" s="3"/>
-      <c r="C22" t="s">
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B23" s="3"/>
-      <c r="C23" t="s">
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B26" s="3" t="s">
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B27" s="3" t="s">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B28" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B29" s="3" t="s">
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1">
+        <v>3</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B30" s="3"/>
-      <c r="C30" t="s">
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B31" s="3"/>
-      <c r="C31" t="s">
+      <c r="D31" s="1"/>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B32" s="3"/>
-      <c r="C32" t="s">
+      <c r="D32" s="1"/>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B33" s="3"/>
-      <c r="C33" t="s">
+      <c r="D33" s="1"/>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B35" s="2" t="s">
+      <c r="D34" s="1"/>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B36" s="3">
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B37" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B41" s="2" t="s">
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1">
+        <v>15</v>
+      </c>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B42" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B48" s="2" t="s">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B49" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B50" s="2" t="s">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B54" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B55" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B53" s="2" t="s">
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B57" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B58" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B54" t="s">
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B59" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="56" spans="2:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B56" s="4" t="s">
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1">
+        <v>2</v>
+      </c>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B61" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B57" s="5" t="s">
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B62" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B966D7-976E-4995-9441-26AE6CB70811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7200D5BC-46EB-4992-A1CE-B8DCF6AF4C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5355" yWindow="3030" windowWidth="23130" windowHeight="15345" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7200D5BC-46EB-4992-A1CE-B8DCF6AF4C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC6BF95-2562-40A9-A6DB-1CCDEBCC03E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5355" yWindow="3030" windowWidth="23130" windowHeight="15345" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -806,7 +806,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
@@ -1065,7 +1065,7 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F37" s="1"/>
     </row>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC6BF95-2562-40A9-A6DB-1CCDEBCC03E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7189F269-782A-43FE-9035-7903CEA35016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="3030" windowWidth="23130" windowHeight="15345" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -179,23 +179,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>狼</t>
-    <rPh sb="0" eb="1">
-      <t>オオカミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>爪攻撃</t>
-    <rPh sb="0" eb="1">
-      <t>ツメ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>4種</t>
     <rPh sb="1" eb="2">
       <t>シュ</t>
@@ -325,6 +308,36 @@
     <rPh sb="0" eb="1">
       <t>ソウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カービイのステージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優しめ1-1</t>
+    <rPh sb="0" eb="1">
+      <t>ヤサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カービイの能力</t>
+    <rPh sb="5" eb="7">
+      <t>ノウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アーチャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーニング</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -766,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FBCCA6-458C-4FC6-A258-62A5B476A274}">
-  <dimension ref="B8:I62"/>
+  <dimension ref="B8:L62"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
@@ -774,28 +787,36 @@
     <col min="5" max="5" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.4">
       <c r="E8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="J10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
       <c r="C13" s="5" t="s">
         <v>18</v>
@@ -809,7 +830,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>0</v>
       </c>
@@ -818,7 +839,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
@@ -829,7 +850,7 @@
       </c>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
@@ -863,7 +884,9 @@
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="C19" s="1" t="s">
         <v>15</v>
       </c>
@@ -876,7 +899,9 @@
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -889,7 +914,9 @@
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -902,7 +929,9 @@
       <c r="F21" s="1"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -916,15 +945,9 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
-      <c r="C23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
@@ -965,7 +988,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -985,10 +1008,10 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1030,7 +1053,7 @@
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1">
@@ -1040,7 +1063,7 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -1108,7 +1131,7 @@
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -1119,7 +1142,7 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B44" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -1139,7 +1162,7 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B46" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -1173,7 +1196,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -1182,7 +1205,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -1191,7 +1214,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -1200,7 +1223,7 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B53" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -1209,7 +1232,7 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B54" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -1227,7 +1250,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -1236,7 +1259,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B57" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -1254,7 +1277,7 @@
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B59" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -1272,7 +1295,7 @@
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B61" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -1281,7 +1304,7 @@
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B62" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7189F269-782A-43FE-9035-7903CEA35016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25CE445-FB8B-49B3-BF7E-4C0AC25D226B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -338,6 +338,27 @@
   </si>
   <si>
     <t>バーニング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4-2のとげとげがいっぱいあるところ、バーニングに使える</t>
+    <rPh sb="25" eb="26">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボム2体のボス</t>
+    <rPh sb="3" eb="4">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5-1の最後らへん</t>
+    <rPh sb="4" eb="6">
+      <t>サイゴ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -423,7 +444,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -443,6 +464,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -779,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FBCCA6-458C-4FC6-A258-62A5B476A274}">
-  <dimension ref="B8:L62"/>
+  <dimension ref="B8:S62"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
@@ -787,12 +811,12 @@
     <col min="5" max="5" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.4">
       <c r="E8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.4">
       <c r="J10" t="s">
         <v>45</v>
       </c>
@@ -800,7 +824,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
@@ -815,8 +839,17 @@
       <c r="I12" s="6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12" t="s">
+        <v>51</v>
+      </c>
+      <c r="S12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
       <c r="C13" s="5" t="s">
         <v>18</v>
@@ -830,7 +863,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>0</v>
       </c>
@@ -838,8 +871,14 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="L14" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
@@ -850,7 +889,7 @@
       </c>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
@@ -861,7 +900,7 @@
       </c>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
@@ -871,8 +910,11 @@
         <v>1</v>
       </c>
       <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="M17" s="7">
+        <v>45781</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
@@ -883,7 +925,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
         <v>47</v>
       </c>
@@ -898,7 +940,7 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
         <v>48</v>
       </c>
@@ -913,7 +955,7 @@
       </c>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
@@ -928,7 +970,7 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
         <v>50</v>
       </c>
@@ -943,28 +985,28 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
@@ -975,7 +1017,7 @@
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
@@ -986,7 +1028,7 @@
       </c>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
         <v>42</v>
       </c>
@@ -997,7 +1039,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B29" s="2" t="s">
         <v>1</v>
       </c>
@@ -1006,7 +1048,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1017,7 +1059,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
         <v>14</v>
@@ -1028,7 +1070,7 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
         <v>16</v>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25CE445-FB8B-49B3-BF7E-4C0AC25D226B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027BE60E-D997-42CB-AFCA-01AFF89AECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -415,7 +415,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -438,13 +438,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -466,7 +479,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -803,28 +819,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FBCCA6-458C-4FC6-A258-62A5B476A274}">
-  <dimension ref="B8:S62"/>
+  <dimension ref="B8:T76"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
-    <col min="4" max="4" width="12.375" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="4" width="42.375" customWidth="1"/>
+    <col min="5" max="5" width="16.25" customWidth="1"/>
+    <col min="12" max="12" width="15.625" customWidth="1"/>
+    <col min="13" max="13" width="47.375" customWidth="1"/>
+    <col min="15" max="15" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.4">
       <c r="E8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="J10" t="s">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="J10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L10" t="s">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
@@ -836,20 +878,27 @@
       <c r="F12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="L12">
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1">
         <v>2</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="S12" t="s">
+      <c r="N12" s="1"/>
+      <c r="O12" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="T12" s="1"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
       <c r="C13" s="5" t="s">
         <v>18</v>
@@ -859,11 +908,22 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="I13">
+      <c r="H13">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>0</v>
       </c>
@@ -871,14 +931,23 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="L14" t="s">
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
@@ -888,8 +957,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
@@ -899,8 +979,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
@@ -910,11 +1001,21 @@
         <v>1</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="M17" s="7">
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="8">
         <v>45781</v>
       </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,7 +1026,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
         <v>47</v>
       </c>
@@ -940,7 +1041,7 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
         <v>48</v>
       </c>
@@ -955,7 +1056,7 @@
       </c>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
@@ -970,7 +1071,7 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
         <v>50</v>
       </c>
@@ -985,28 +1086,28 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
@@ -1017,7 +1118,7 @@
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
@@ -1028,7 +1129,7 @@
       </c>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
         <v>42</v>
       </c>
@@ -1039,19 +1140,13 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B29" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.4">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B30" s="1" t="s">
-        <v>24</v>
-      </c>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.4">
       <c r="C30" s="1" t="s">
         <v>26</v>
       </c>
@@ -1059,8 +1154,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B31" s="1"/>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.4">
       <c r="C31" s="1" t="s">
         <v>14</v>
       </c>
@@ -1070,8 +1164,7 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B32" s="1"/>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.4">
       <c r="C32" s="1" t="s">
         <v>16</v>
       </c>
@@ -1082,7 +1175,6 @@
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,7 +1185,6 @@
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
         <v>27</v>
       </c>
@@ -1104,8 +1195,8 @@
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B35" s="1" t="s">
-        <v>42</v>
+      <c r="B35" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -1115,8 +1206,8 @@
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B36" s="2" t="s">
-        <v>2</v>
+      <c r="B36" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -1124,9 +1215,7 @@
       <c r="F36" s="1"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="1">
-        <v>3</v>
-      </c>
+      <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
@@ -1156,7 +1245,9 @@
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B41" s="1"/>
+      <c r="B41" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -1164,7 +1255,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -1172,8 +1263,8 @@
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B43" s="1" t="s">
-        <v>30</v>
+      <c r="B43" s="1">
+        <v>3</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -1183,9 +1274,7 @@
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B44" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1">
@@ -1194,18 +1283,14 @@
       <c r="F44" s="1"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B45" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B46" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1">
@@ -1221,15 +1306,17 @@
       <c r="F47" s="1"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B48" s="1"/>
+      <c r="B48" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B49" s="2" t="s">
-        <v>5</v>
+      <c r="B49" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -1238,7 +1325,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -1246,8 +1333,8 @@
       <c r="F50" s="1"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B51" s="1" t="s">
-        <v>33</v>
+      <c r="B51" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -1256,7 +1343,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -1264,18 +1351,14 @@
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B53" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B54" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1283,7 +1366,7 @@
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -1292,7 +1375,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -1301,7 +1384,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B57" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -1309,8 +1392,8 @@
       <c r="F57" s="1"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B58" s="2" t="s">
-        <v>7</v>
+      <c r="B58" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -1319,7 +1402,7 @@
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B59" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -1329,7 +1412,9 @@
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B60" s="1"/>
+      <c r="B60" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -1337,7 +1422,7 @@
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B61" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -1345,13 +1430,65 @@
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C62" s="1"/>
+      <c r="B62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="7"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B63" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B65" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B66" s="1"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B67" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B68" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B69" s="1"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B70" s="1"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B71" s="1"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B76" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027BE60E-D997-42CB-AFCA-01AFF89AECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D91C77B-3FB1-4AFF-BBF4-153830392700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="61">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -179,13 +180,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4種</t>
-    <rPh sb="1" eb="2">
-      <t>シュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ステージ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -194,21 +188,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>熊</t>
-    <rPh sb="0" eb="1">
-      <t>クマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>３ステージ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カード4種</t>
-    <rPh sb="4" eb="5">
-      <t>シュ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -358,6 +338,79 @@
     <t>5-1の最後らへん</t>
     <rPh sb="4" eb="6">
       <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1ステージ3マップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>構想(イメージ)</t>
+    <rPh sb="0" eb="2">
+      <t>コウソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3種</t>
+    <rPh sb="1" eb="2">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近づいたら攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弓+矢</t>
+    <rPh sb="0" eb="1">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(弓)</t>
+    <rPh sb="1" eb="2">
+      <t>ユミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カード3種</t>
+    <rPh sb="4" eb="5">
+      <t>シュ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -819,10 +872,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FBCCA6-458C-4FC6-A258-62A5B476A274}">
-  <dimension ref="B8:T76"/>
+  <dimension ref="B11:H84"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="26.5" customWidth="1"/>
     <col min="3" max="3" width="36.625" customWidth="1"/>
     <col min="4" max="4" width="42.375" customWidth="1"/>
     <col min="5" max="5" width="16.25" customWidth="1"/>
@@ -831,74 +884,30 @@
     <col min="15" max="15" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="J10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="E12" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1">
-        <v>2</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="T12" s="1"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
       <c r="C13" s="5" t="s">
         <v>18</v>
@@ -911,19 +920,8 @@
       <c r="H13">
         <v>56</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>0</v>
       </c>
@@ -931,23 +929,8 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
@@ -957,19 +940,8 @@
         <v>1</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
@@ -979,19 +951,8 @@
         <v>1</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,21 +962,8 @@
         <v>1</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="8">
-        <v>45781</v>
-      </c>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
@@ -1026,9 +974,9 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>15</v>
@@ -1041,9 +989,9 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>14</v>
@@ -1056,9 +1004,9 @@
       </c>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>16</v>
@@ -1071,9 +1019,9 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>17</v>
@@ -1086,28 +1034,28 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
@@ -1118,7 +1066,7 @@
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
@@ -1129,9 +1077,9 @@
       </c>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -1140,31 +1088,35 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="C30" s="1" t="s">
-        <v>26</v>
-      </c>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
         <v>16</v>
       </c>
@@ -1175,6 +1127,7 @@
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
@@ -1185,9 +1138,8 @@
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="C34" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1">
         <v>1</v>
@@ -1195,36 +1147,34 @@
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B35" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1">
-        <v>2</v>
-      </c>
+      <c r="E35" s="1"/>
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B36" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="1"/>
+      <c r="B37" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F37" s="1"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1232,82 +1182,98 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="C39" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="E39" s="1">
+        <v>25</v>
+      </c>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
+      <c r="C40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B42" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B43" s="1">
-        <v>3</v>
-      </c>
+      <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="1">
-        <v>2</v>
-      </c>
+      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D44" s="1"/>
-      <c r="E44" s="1">
-        <v>2</v>
-      </c>
+      <c r="E44" s="1"/>
       <c r="F44" s="1"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="1">
-        <v>3</v>
-      </c>
+      <c r="E46" s="1"/>
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B48" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -1315,39 +1281,39 @@
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B49" s="1" t="s">
-        <v>30</v>
+      <c r="B49" s="1">
+        <v>3</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="E49" s="1">
+        <v>2</v>
+      </c>
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B50" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
       <c r="F50" s="1"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B51" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B52" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
+      <c r="E52" s="1">
+        <v>3</v>
+      </c>
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
@@ -1358,15 +1324,17 @@
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B54" s="1"/>
+      <c r="B54" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B55" s="2" t="s">
-        <v>5</v>
+      <c r="B55" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -1375,7 +1343,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -1383,8 +1351,8 @@
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B57" s="1" t="s">
-        <v>33</v>
+      <c r="B57" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -1402,18 +1370,16 @@
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B59" s="1" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="1">
-        <v>2</v>
-      </c>
+      <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B60" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -1421,8 +1387,8 @@
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B61" s="2" t="s">
-        <v>6</v>
+      <c r="B61" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -1430,69 +1396,282 @@
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C62" s="7"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B63" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="B63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B66" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B70" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B71" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B72" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B65" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B66" s="1"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B67" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B68" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B69" s="1"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B70" s="1"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B71" s="1"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B73" s="1"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B73" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B75" s="1"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B76" s="1"/>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B75" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B76" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B78" s="1"/>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B80" s="1"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B81" s="1"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B83" s="1"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B84" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3309F7D1-9E11-4871-B9F4-4548CC9271F7}">
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="19.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="8">
+        <v>45781</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D91C77B-3FB1-4AFF-BBF4-153830392700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8605B4-FDED-4B46-830B-3665FCC029EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="1" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="68">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -412,6 +414,58 @@
     <rPh sb="4" eb="5">
       <t>シュ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制作の流れ</t>
+    <rPh sb="0" eb="2">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進捗メモ</t>
+    <rPh sb="0" eb="2">
+      <t>シンチョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Characterクラス作成、プレイヤークラス継承、プレイヤーを動かせるようにした</t>
+    <rPh sb="12" eb="14">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケイショウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ジャンプ、モーションをする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スナイパー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -510,7 +564,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -536,6 +590,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1544,6 +1601,9 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.625" customWidth="1"/>
+    <col min="4" max="4" width="22.5" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="6" width="30.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
@@ -1584,14 +1644,13 @@
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1">
-        <v>2</v>
+      <c r="D6" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H6" s="1"/>
@@ -1645,7 +1704,9 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1674,4 +1735,82 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB307D3-D8E6-40F6-9514-43EB28D76C56}">
+  <dimension ref="B2:I4"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="9.125" customWidth="1"/>
+    <col min="6" max="6" width="9.625" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B2" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
+  <dimension ref="B2:C4"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="77.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B3" s="9">
+        <v>45963</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8605B4-FDED-4B46-830B-3665FCC029EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07E654E-889D-4E85-8211-81AE1A69BDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="1" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="84">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -466,6 +466,125 @@
   </si>
   <si>
     <t>スナイパー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カービイデラックスの花形ステージ、ギミック</t>
+    <rPh sb="10" eb="12">
+      <t>ハナガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1面</t>
+    <rPh sb="1" eb="2">
+      <t>メン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2面</t>
+    <rPh sb="1" eb="2">
+      <t>メン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3面</t>
+    <rPh sb="1" eb="2">
+      <t>メン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カード作成</t>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未定</t>
+    <rPh sb="0" eb="2">
+      <t>ミテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計１８</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計６</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計10</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計９</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計12</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>未定</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -473,7 +592,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,8 +608,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,8 +646,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -558,13 +689,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -593,6 +737,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -929,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FBCCA6-458C-4FC6-A258-62A5B476A274}">
-  <dimension ref="B11:H84"/>
+  <dimension ref="B11:H96"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="26.5" customWidth="1"/>
@@ -975,7 +1125,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="H13">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.4">
@@ -984,8 +1134,13 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="E14" s="2">
+        <v>19</v>
+      </c>
       <c r="F14" s="1"/>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
@@ -996,7 +1151,9 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
@@ -1223,8 +1380,8 @@
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1">
-        <v>2</v>
+      <c r="E37" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="F37" s="1"/>
     </row>
@@ -1243,9 +1400,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="1">
-        <v>25</v>
-      </c>
+      <c r="E39" s="1"/>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
@@ -1256,7 +1411,9 @@
       <c r="D40" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="1"/>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
@@ -1267,7 +1424,9 @@
       <c r="D41" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="1"/>
+      <c r="E41" s="1">
+        <v>2</v>
+      </c>
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
@@ -1278,7 +1437,9 @@
       <c r="D42" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="1"/>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
@@ -1307,7 +1468,9 @@
       <c r="D45" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E45" s="1"/>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
@@ -1316,7 +1479,9 @@
         <v>16</v>
       </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="E46" s="1">
+        <v>2</v>
+      </c>
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
@@ -1325,7 +1490,9 @@
         <v>17</v>
       </c>
       <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
       <c r="F47" s="1"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
@@ -1334,7 +1501,9 @@
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="E48" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
@@ -1344,7 +1513,7 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="1"/>
     </row>
@@ -1353,7 +1522,7 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="1"/>
     </row>
@@ -1361,16 +1530,16 @@
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="E51" s="1">
+        <v>3</v>
+      </c>
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1">
-        <v>3</v>
-      </c>
+      <c r="E52" s="1"/>
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
@@ -1386,7 +1555,9 @@
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
+      <c r="E54" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="F54" s="1"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
@@ -1395,7 +1566,9 @@
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
+      <c r="E55" s="1">
+        <v>3</v>
+      </c>
       <c r="F55" s="1"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
@@ -1404,7 +1577,9 @@
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
+      <c r="E56" s="1">
+        <v>3</v>
+      </c>
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
@@ -1413,7 +1588,9 @@
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
+      <c r="E57" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="F57" s="1"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
@@ -1431,7 +1608,9 @@
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
+      <c r="E59" s="1">
+        <v>3</v>
+      </c>
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
@@ -1440,7 +1619,9 @@
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
+      <c r="E60" s="1">
+        <v>3</v>
+      </c>
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
@@ -1449,7 +1630,9 @@
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
@@ -1465,7 +1648,9 @@
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
+      <c r="E63" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="F63" s="1"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
@@ -1501,9 +1686,7 @@
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
-      <c r="E67" s="1">
-        <v>2</v>
-      </c>
+      <c r="E67" s="1"/>
       <c r="F67" s="1"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
@@ -1521,7 +1704,9 @@
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
+      <c r="E69" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
@@ -1530,63 +1715,245 @@
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
       <c r="F70" s="1"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B71" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="B71" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+      <c r="F71" s="1"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B72" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1">
+        <v>2</v>
+      </c>
+      <c r="F72" s="1"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B73" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1">
+        <v>2</v>
+      </c>
+      <c r="F73" s="1"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B74" s="1"/>
+      <c r="B74" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1">
+        <v>2</v>
+      </c>
+      <c r="F74" s="1"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B75" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1">
+        <v>2</v>
+      </c>
+      <c r="F75" s="1"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B76" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" t="s">
-        <v>51</v>
-      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1">
+        <v>2</v>
+      </c>
+      <c r="F76" s="1"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B77" s="1"/>
+      <c r="B77" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1">
+        <v>2</v>
+      </c>
+      <c r="F77" s="1"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B78" s="1"/>
+      <c r="C78" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1">
+        <v>2</v>
+      </c>
+      <c r="F78" s="1"/>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B79" s="1"/>
+      <c r="C79" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1">
+        <v>2</v>
+      </c>
+      <c r="F79" s="1"/>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B80" s="1"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B81" s="1"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B82" s="1"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B83" s="1"/>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B84" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B82" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B83" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B84" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E84" s="1">
+        <v>6</v>
+      </c>
+      <c r="F84" s="1"/>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B88" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B96" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1707,7 +2074,9 @@
       <c r="D10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07E654E-889D-4E85-8211-81AE1A69BDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B41EC2-463F-43EE-B5B4-E6C78EDDECCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3675" yWindow="765" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="88">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -585,6 +586,61 @@
       </rPr>
       <t>未定</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ完了</t>
+    <rPh sb="4" eb="6">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、変身時モーション、ジャンプモーション実装</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ヘンシンジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細、変更</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラが変身する方法は敵を倒した後に宣言で変身</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヘンシン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1963,6 +2019,30 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
+  <dimension ref="B3:C4"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3309F7D1-9E11-4871-B9F4-4548CC9271F7}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2106,7 +2186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB307D3-D8E6-40F6-9514-43EB28D76C56}">
   <dimension ref="B2:I4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2152,9 +2232,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C4"/>
+  <dimension ref="B2:C6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="77.375" customWidth="1"/>
@@ -2178,6 +2258,19 @@
         <v>66</v>
       </c>
     </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B5" s="9">
+        <v>45965</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B41EC2-463F-43EE-B5B4-E6C78EDDECCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006A72BF-9AA6-4EBE-B203-89040FDE5902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="765" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="4" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -640,6 +640,88 @@
     </rPh>
     <rPh sb="21" eb="23">
       <t>ヘンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返信時モーション、ジャンプモーション、攻撃モーション実装</t>
+    <rPh sb="0" eb="3">
+      <t>ヘンシンジ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標、攻撃の当たり判定の実装、敵を倒せるようにする</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標、達成</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→変身の当たり判定、敵がやられた後の、ひかりの当たり判定を生成</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セイセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2234,7 +2316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C6"/>
+  <dimension ref="B2:C12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="77.375" customWidth="1"/>
@@ -2271,6 +2353,32 @@
         <v>85</v>
       </c>
     </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B8" s="9">
+        <v>45966</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B10" s="9">
+        <v>45967</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006A72BF-9AA6-4EBE-B203-89040FDE5902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E597DB8-7370-4F24-9512-3D8A31E81BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="4" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="95">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -722,6 +722,75 @@
     </rPh>
     <rPh sb="33" eb="35">
       <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→川野先生のInputclassに置き換える、前回の目標</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>カワノセンセイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゼンカイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Inputくらすに置き換え完了、敵がやられた後の判定生成途中</t>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>ハンテイセイセイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→光の判定生成、それを取ったらキャラが切り替わる</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ハンテイセイセイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2316,7 +2385,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C12"/>
+  <dimension ref="B2:C15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="77.375" customWidth="1"/>
@@ -2379,6 +2448,24 @@
         <v>91</v>
       </c>
     </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B13" s="9">
+        <v>45968</v>
+      </c>
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E597DB8-7370-4F24-9512-3D8A31E81BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572099E6-8E4A-4BCF-9E3E-C1B7CA43E747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="4" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="97">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -791,6 +791,26 @@
     </rPh>
     <rPh sb="23" eb="24">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部活のちカラオケだったためなし</t>
+    <rPh sb="0" eb="2">
+      <t>ブカツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>７日の目標を達成する</t>
+    <rPh sb="1" eb="2">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タッセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2385,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C15"/>
+  <dimension ref="B2:C19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="77.375" customWidth="1"/>
@@ -2466,6 +2486,22 @@
         <v>94</v>
       </c>
     </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B17" s="9">
+        <v>45969</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B19" s="9">
+        <v>45970</v>
+      </c>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572099E6-8E4A-4BCF-9E3E-C1B7CA43E747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C2C055-9C58-404C-846A-0FADDFE4449D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="4" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3675" yWindow="765" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -811,6 +811,48 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>タッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標を達成、変身後のキャラのモーションを次はやる</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タッセイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ヘンシンゴ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>判定はキャラの攻撃の種類文ある</t>
+    <rPh sb="0" eb="2">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>シュルイブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なので、Attackの時とかも、_typeで分ける必要がある</t>
+    <rPh sb="11" eb="12">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒツヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2191,10 +2233,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:C4"/>
+  <dimension ref="B3:C7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="3" max="3" width="49" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.4">
@@ -2205,6 +2247,16 @@
     <row r="4" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C7" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +2457,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C19"/>
+  <dimension ref="B2:C20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="77.375" customWidth="1"/>
@@ -2502,6 +2554,11 @@
         <v>96</v>
       </c>
     </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C2C055-9C58-404C-846A-0FADDFE4449D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4A8EB3-888D-4CAE-B60C-BFB423540674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="765" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="4" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="102">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -853,6 +853,44 @@
     </rPh>
     <rPh sb="25" eb="27">
       <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変身後のキャラのモーション終了。矢の実装</t>
+    <rPh sb="0" eb="3">
+      <t>ヘンシンゴ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→矢が敵に当たったときの判定、マップ作る</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2233,30 +2271,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:C7"/>
+  <dimension ref="B3:D7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C7" t="s">
         <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2457,9 +2504,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C20"/>
+  <dimension ref="B2:C23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2559,6 +2607,19 @@
         <v>97</v>
       </c>
     </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B22" s="9">
+        <v>45971</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4A8EB3-888D-4CAE-B60C-BFB423540674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC196BA-2CA4-46FF-946A-A07410BCFD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="2895" windowWidth="23130" windowHeight="15345" activeTab="4" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3510" yWindow="0" windowWidth="21600" windowHeight="15585" activeTab="4" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -873,7 +873,17 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>目標→矢が敵に当たったときの判定、マップ作る</t>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>方向指定、チャージはまだ</t>
+    <rPh sb="0" eb="4">
+      <t>ホウコウシテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→矢が敵に当たったときの判定、敵の攻撃、移動、をした後、マップ</t>
     <rPh sb="0" eb="2">
       <t>モクヒョウ</t>
     </rPh>
@@ -889,8 +899,33 @@
     <rPh sb="14" eb="16">
       <t>ハンテイ</t>
     </rPh>
-    <rPh sb="20" eb="21">
-      <t>ツク</t>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢は完了、次は馬</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウマ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -960,7 +995,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1009,13 +1044,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1050,6 +1096,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1393,6 +1442,7 @@
     <col min="3" max="3" width="36.625" customWidth="1"/>
     <col min="4" max="4" width="42.375" customWidth="1"/>
     <col min="5" max="5" width="16.25" customWidth="1"/>
+    <col min="7" max="7" width="24.75" customWidth="1"/>
     <col min="12" max="12" width="15.625" customWidth="1"/>
     <col min="13" max="13" width="47.375" customWidth="1"/>
     <col min="15" max="15" width="15.75" customWidth="1"/>
@@ -1471,9 +1521,11 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="F16" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
@@ -1482,9 +1534,11 @@
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="F17" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
@@ -1495,7 +1549,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
         <v>44</v>
       </c>
@@ -1508,9 +1562,11 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="F19" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
         <v>45</v>
       </c>
@@ -1523,9 +1579,14 @@
       <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="F20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
         <v>46</v>
       </c>
@@ -1538,9 +1599,11 @@
       <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="F21" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
         <v>47</v>
       </c>
@@ -1555,28 +1618,28 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
@@ -1587,7 +1650,7 @@
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,7 +1661,7 @@
       </c>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
@@ -1607,23 +1670,25 @@
       <c r="E28" s="1">
         <v>3</v>
       </c>
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="F28" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
         <v>14</v>
@@ -1636,7 +1701,7 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
         <v>16</v>
@@ -2504,7 +2569,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C23"/>
+  <dimension ref="B2:C24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -2617,7 +2682,12 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C24" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC196BA-2CA4-46FF-946A-A07410BCFD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2CABE5-D016-4BCE-99A0-0CD950DAED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="0" windowWidth="21600" windowHeight="15585" activeTab="4" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3780" yWindow="1500" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="108">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -926,6 +927,48 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>ウマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>馬も完了</t>
+    <rPh sb="0" eb="1">
+      <t>ウマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景を適当に貼る、マップスクロールをキャラに反映させる(上田先輩のをもう一度復習)</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テキトウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="28" eb="32">
+      <t>ウエダセンパイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>フクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1098,7 +1141,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2335,49 +2378,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:D7"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="3" max="3" width="49" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3309F7D1-9E11-4871-B9F4-4548CC9271F7}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2521,7 +2521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB307D3-D8E6-40F6-9514-43EB28D76C56}">
   <dimension ref="B2:I4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2567,9 +2567,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C24"/>
+  <dimension ref="B2:C27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -2690,8 +2690,82 @@
         <v>104</v>
       </c>
     </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B25" s="9">
+        <v>45972</v>
+      </c>
+      <c r="C25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B26" s="9">
+        <v>45973</v>
+      </c>
+      <c r="C26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
+  <dimension ref="B3:D7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="49" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51BAFBE-B9D5-4C2F-AE01-E8A667EC2E24}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2CABE5-D016-4BCE-99A0-0CD950DAED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558B6176-6DF9-48EB-A072-A0293F530A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="1500" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="110">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -967,6 +967,20 @@
   </si>
   <si>
     <t>目標→</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップを作る</t>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標そのまま、</t>
     <rPh sb="0" eb="2">
       <t>モクヒョウ</t>
     </rPh>
@@ -2569,7 +2583,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C27"/>
+  <dimension ref="B2:C30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -2709,6 +2723,19 @@
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B29" s="9">
+        <v>45974</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C30" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558B6176-6DF9-48EB-A072-A0293F530A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59622AF3-BFDB-4770-8E9B-6EC76C93B04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="1680" yWindow="2385" windowWidth="21600" windowHeight="13140" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="111">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -980,9 +980,43 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>目標そのまま、</t>
+    <t>mapスクロールをキャラに反映、完了</t>
+    <rPh sb="13" eb="15">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→敵を倒したらアイテム化、バーニングの挙動が変わったので調整、アイテムの量を増やす</t>
     <rPh sb="0" eb="2">
       <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>フ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2583,7 +2617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C30"/>
+  <dimension ref="B2:C31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -2736,6 +2770,11 @@
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C31" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59622AF3-BFDB-4770-8E9B-6EC76C93B04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668CF099-CBD6-46C3-B03E-9011C8EA7F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="2385" windowWidth="21600" windowHeight="13140" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="112">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1017,6 +1017,19 @@
     </rPh>
     <rPh sb="40" eb="41">
       <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーニング完了、次はアイテム化</t>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2617,7 +2630,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C31"/>
+  <dimension ref="B2:C32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -2775,6 +2788,11 @@
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C32" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668CF099-CBD6-46C3-B03E-9011C8EA7F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D026C19-BF42-475C-BCF5-514645DF563A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="114">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1030,6 +1030,35 @@
     </rPh>
     <rPh sb="14" eb="15">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム化の途中</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラクラス実装、アイテム化完了、sharedpointer化完了</t>
+    <rPh sb="6" eb="8">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2630,7 +2659,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C32"/>
+  <dimension ref="B2:C34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -2793,6 +2822,22 @@
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B33" s="9">
+        <v>45975</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B34" s="9">
+        <v>45976</v>
+      </c>
+      <c r="C34" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D026C19-BF42-475C-BCF5-514645DF563A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63C3FF8-D104-4311-9B34-3AF70F9BF94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="119">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1044,7 +1044,36 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カメラクラス実装、アイテム化完了、sharedpointer化完了</t>
+    <t>敵の種類を増やす、敵の行動パターンを作る</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EnemyWizard.cppのAttackUpdateの途中、</t>
+    <rPh sb="29" eb="31">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラクラス実装、アイテム化完了、sharedpointer化完了(あとは、Arrow)</t>
     <rPh sb="6" eb="8">
       <t>ジッソウ</t>
     </rPh>
@@ -1059,6 +1088,51 @@
     </rPh>
     <rPh sb="31" eb="33">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の行動パターンの具体化</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>グタイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→Attackの実装終わり、敵の種類を増やす、or　てきを配置する</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ジッソウオ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムの種類を増やすというのをいつかやりたい</t>
+    <rPh sb="5" eb="7">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>フ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2659,7 +2733,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C34"/>
+  <dimension ref="B2:C39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -2837,7 +2911,32 @@
         <v>45976</v>
       </c>
       <c r="C34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C35" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C38" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C39" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63C3FF8-D104-4311-9B34-3AF70F9BF94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C86F81B-6AB2-4726-A415-36C6F0CF8455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="121">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1133,6 +1133,59 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今日やったこと、敵の攻撃パターンの実装</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明日やること、敵の種類を増やす、敵を配置、氷魔法の設置の仕方を誰かに聞く</t>
+    <rPh sb="0" eb="2">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>コオリマホウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シカタ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>キ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2733,7 +2786,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C39"/>
+  <dimension ref="B2:C42"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -2937,6 +2990,16 @@
     <row r="39" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C41" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C42" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C86F81B-6AB2-4726-A415-36C6F0CF8455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027B7C7E-A465-4980-9EAD-7D6872A99C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="1680" yWindow="2340" windowWidth="21600" windowHeight="13140" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="124">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1186,6 +1186,63 @@
     </rPh>
     <rPh sb="34" eb="35">
       <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カロンみたいな敵を用意するのもあり(氷だけ固めて倒せる)</t>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷魔法は最後のほうに後回し、今日はやられ判定を2つ作る(メインはアイス)</t>
+    <rPh sb="0" eb="3">
+      <t>コオリマホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>アトマワ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今、炎のやられモーションを描画するところの途中</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>トチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2786,7 +2843,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C42"/>
+  <dimension ref="B2:C45"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3002,6 +3059,19 @@
         <v>120</v>
       </c>
     </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B44" s="9">
+        <v>45977</v>
+      </c>
+      <c r="C44" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C45" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3010,10 +3080,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:D7"/>
+  <dimension ref="B3:D9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="49" customWidth="1"/>
+    <col min="3" max="3" width="53.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
@@ -3043,6 +3113,11 @@
       </c>
       <c r="D7" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C9" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027B7C7E-A465-4980-9EAD-7D6872A99C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB424AB-7F90-4177-AB19-ED514A2F48E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="2340" windowWidth="21600" windowHeight="13140" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="125">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1243,6 +1243,31 @@
     </rPh>
     <rPh sb="21" eb="23">
       <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎のやられモーション完了、炎と氷のvector配列化も完了</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2843,7 +2868,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C45"/>
+  <dimension ref="B2:C46"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3070,6 +3095,11 @@
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C46" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB424AB-7F90-4177-AB19-ED514A2F48E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8570565-8AF9-481D-8861-22B223ECC0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3285" yWindow="2415" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="128">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1268,6 +1268,45 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→敵の種類を増やす(3,4種)</t>
+    <rPh sb="0" eb="3">
+      <t>モクヒョウヤジルシ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のやられ判定を終わらせる</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>arrowのshared_ptrの途中</t>
+    <rPh sb="17" eb="19">
+      <t>トチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2868,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C46"/>
+  <dimension ref="B2:C50"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3100,6 +3139,24 @@
     <row r="46" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B48" s="9">
+        <v>45978</v>
+      </c>
+      <c r="C48" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C49" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C50" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8570565-8AF9-481D-8861-22B223ECC0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A2F42F-DDC7-4E3E-B27E-EC1183C382F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2415" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="132">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1304,9 +1304,82 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>arrowのshared_ptrの途中</t>
+    <t>オークライダーの氷に当たった時の途中</t>
+    <rPh sb="8" eb="9">
+      <t>コオリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>arrowのshared_ptrの途中→完了</t>
     <rPh sb="17" eb="19">
       <t>トチュウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢を完成、次は2番目の敵のやられ判定を終わらせる→完了</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バンメ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種類ごとにアイテムを変える作業を今からする→完了</t>
+    <rPh sb="0" eb="2">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今、敵のどくろアーチャーをクラスとcppを作ったところ(作っただけ)</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2907,7 +2980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C50"/>
+  <dimension ref="B2:C55"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3156,7 +3229,32 @@
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C50" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C51" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C52" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C54" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C55" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A2F42F-DDC7-4E3E-B27E-EC1183C382F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DA4725-622F-4344-9C12-F0E49DFD1581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1380,6 +1380,34 @@
     </rPh>
     <rPh sb="28" eb="29">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弓矢のやられ判定の途中、判定の実装はできて、あとは、通常の当たり判定など</t>
+    <rPh sb="0" eb="2">
+      <t>ユミヤ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2980,7 +3008,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C55"/>
+  <dimension ref="B2:C56"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3255,6 +3283,11 @@
     <row r="55" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C55" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C56" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DA4725-622F-4344-9C12-F0E49DFD1581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64488730-6FFD-4ECF-83E7-41E96EFD0854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="134">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1408,6 +1408,22 @@
     </rPh>
     <rPh sb="32" eb="34">
       <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の矢の実装完了</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3008,7 +3024,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C56"/>
+  <dimension ref="B2:C57"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3288,6 +3304,11 @@
     <row r="56" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C56" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C57" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64488730-6FFD-4ECF-83E7-41E96EFD0854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A6AD50-9959-48E7-8B84-3E742D3AAA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2550" yWindow="1125" windowWidth="23940" windowHeight="14100" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="136">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1424,6 +1424,53 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→レベルデザインを少し勉強、シーン遷移の実装、新しいマップ、リザルト画面の追加</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>割と余裕ありそうだから、ただの雑魚敵も2.3種作れそう</t>
+    <rPh sb="0" eb="1">
+      <t>ワリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヨユウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ザコテキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3024,7 +3071,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C57"/>
+  <dimension ref="B2:C60"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3266,49 +3313,62 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C49" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C50" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C51" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C52" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C53" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C54" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C55" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C56" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C57" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B59" s="9">
+        <v>45979</v>
+      </c>
+      <c r="C59" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C60" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A6AD50-9959-48E7-8B84-3E742D3AAA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855EE440-F657-4639-926F-299329EBDEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="1125" windowWidth="23940" windowHeight="14100" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="139">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1471,6 +1471,51 @@
     </rPh>
     <rPh sb="23" eb="24">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移の実装に半日かかった</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→1-1のようなステージを作る、実装、&amp; チュートリアル用のステージ作り直し</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その前にステージセレクトシーンを実装</t>
+    <rPh sb="2" eb="3">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3071,7 +3116,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C60"/>
+  <dimension ref="B2:C63"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3369,6 +3414,24 @@
     <row r="60" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C60" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C61" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B62" s="9">
+        <v>45980</v>
+      </c>
+      <c r="C62" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C63" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855EE440-F657-4639-926F-299329EBDEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160DC73E-D563-4F7B-9B34-42A8786A7A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="3240" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="7755" yWindow="3195" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="142">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1516,6 +1516,57 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージを作ったところ、バーニングの壁のめり込みが気になったため、直した、それに続いて</t>
+    <rPh sb="5" eb="6">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップとの当たり判定をプレイヤーが独自で持つやつを作ることに決定</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ドクジ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今からそれをします</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3116,7 +3167,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C63"/>
+  <dimension ref="B2:C66"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3432,6 +3483,21 @@
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C63" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C65" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C66" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160DC73E-D563-4F7B-9B34-42A8786A7A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3A38B4-5E1E-46D4-8B10-4B3C58D2C329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7755" yWindow="3195" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="149">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1567,6 +1567,79 @@
     <t>今からそれをします</t>
     <rPh sb="0" eb="1">
       <t>イマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やっぱあってたっぽいのでなし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明日の目標→実際にキャラを配置する</t>
+    <rPh sb="0" eb="2">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弓矢をレーザーとして使うか悩み中</t>
+    <rPh sb="0" eb="2">
+      <t>ユミヤ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナヤ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ固定もやりたい</t>
+    <rPh sb="3" eb="5">
+      <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワープスターのアニメーションもやりたい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中ボスも作りたい</t>
+    <rPh sb="0" eb="1">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【今回の休みですること】チュートリアルを作るor1-1を作る</t>
+    <rPh sb="1" eb="3">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヤス</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3167,7 +3240,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C66"/>
+  <dimension ref="B2:C73"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3498,6 +3571,41 @@
     <row r="66" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C66" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C67" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C68" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C69" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C70" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C71" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C72" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C73" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3A38B4-5E1E-46D4-8B10-4B3C58D2C329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A78A76-95FA-4746-8E11-36DF1EE4DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7755" yWindow="3195" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="150">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1640,6 +1640,34 @@
     </rPh>
     <rPh sb="28" eb="29">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今、配置をしているところ、要所要所に台を置いて移動しやすくしたいｌ、また、移動速度を落とす</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ヨウショヨウショ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="37" eb="41">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3240,11 +3268,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C73"/>
+  <dimension ref="B2:C75"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.375" customWidth="1"/>
+    <col min="3" max="3" width="81.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
@@ -3559,53 +3587,70 @@
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B64" s="9">
+        <v>45981</v>
+      </c>
       <c r="C64" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C65" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C66" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B67" s="9">
+        <v>45982</v>
+      </c>
       <c r="C67" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C68" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B69" s="9">
+        <v>45983</v>
+      </c>
       <c r="C69" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C70" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C71" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C72" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C73" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B75" s="9">
+        <v>45984</v>
+      </c>
+      <c r="C75" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A78A76-95FA-4746-8E11-36DF1EE4DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64874797-4A1E-4136-B2EB-F026CBCDA311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7755" yWindow="3195" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="158">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1668,6 +1668,89 @@
     </rPh>
     <rPh sb="42" eb="43">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>配置はそこそこ完了</t>
+    <rPh sb="0" eb="2">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度落とすのも完了</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップとの当たり判定も解決済み</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今から、敵のスポーンをカメラの場所によって決めるようにする</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、かめらのばしょによってdelete</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムのdrawがおかしい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペンギンだけリスポーンの処理のノーマルだけを完了</t>
+    <rPh sb="12" eb="14">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほかのEnemyのuPdateにSetCOlRectがないのがすごい気になる(明日追加してください)</t>
+    <rPh sb="34" eb="35">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>アシタツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3268,7 +3351,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C75"/>
+  <dimension ref="B2:C84"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3651,6 +3734,46 @@
       </c>
       <c r="C75" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C76" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C77" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C78" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C79" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C80" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C82" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C83" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C84" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64874797-4A1E-4136-B2EB-F026CBCDA311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AB8104-40D8-4AED-AA13-0133AC27ED15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7755" yWindow="3195" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -1731,10 +1731,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アイテムのdrawがおかしい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ペンギンだけリスポーンの処理のノーマルだけを完了</t>
     <rPh sb="12" eb="14">
       <t>ショリ</t>
@@ -1752,6 +1748,10 @@
     <rPh sb="39" eb="43">
       <t>アシタツイカ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムのdrawがおかしい→直した</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3763,17 +3763,17 @@
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C82" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C83" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C84" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AB8104-40D8-4AED-AA13-0133AC27ED15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3650DC-E71B-45DA-AE5A-0BCC2F654A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7755" yWindow="3195" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="159">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1727,31 +1727,65 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>そのあと、かめらのばしょによってdelete</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ペンギンだけリスポーンの処理のノーマルだけを完了</t>
+    <t>アイテムのdrawがおかしい→直した</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほかのEnemyのuPdateにSetCOlRectがないのがすごい気になる(明日追加してください)→追加しました</t>
+    <rPh sb="34" eb="35">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>アシタツイカ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペンギンだけリスポーンの処理のノーマルだけを完了→ペンギンは全部完了</t>
     <rPh sb="12" eb="14">
       <t>ショリ</t>
     </rPh>
     <rPh sb="22" eb="24">
       <t>カンリョウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ほかのEnemyのuPdateにSetCOlRectがないのがすごい気になる(明日追加してください)</t>
-    <rPh sb="34" eb="35">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="39" eb="43">
-      <t>アシタツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アイテムのdrawがおかしい→直した</t>
+    <rPh sb="30" eb="32">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、かめらのばしょによってdelete→完了</t>
+    <rPh sb="23" eb="25">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→扉を用意する、(そこに入ると、次のステージ)</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>トビラ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツギ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3351,7 +3385,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C84"/>
+  <dimension ref="B2:C85"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3758,22 +3792,27 @@
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C80" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C82" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C83" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C84" t="s">
-        <v>156</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C85" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3650DC-E71B-45DA-AE5A-0BCC2F654A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998420E5-A960-477A-A881-587FA2B295BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="4665" yWindow="1785" windowWidth="21600" windowHeight="12735" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="162">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1785,6 +1785,42 @@
     </rPh>
     <rPh sb="20" eb="21">
       <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11月24</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→扉、台をしたから貫通できるようにする</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トビラ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンツウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>台を貫通できるようにする→完了</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2475,7 +2511,9 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
@@ -2507,7 +2545,9 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="1"/>
+      <c r="F26" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
@@ -2558,7 +2598,9 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B32" s="1"/>
@@ -2569,7 +2611,9 @@
       <c r="E32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B33" s="1"/>
@@ -2580,7 +2624,9 @@
       <c r="E33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="1"/>
@@ -2645,7 +2691,9 @@
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B41" s="1"/>
@@ -2658,7 +2706,9 @@
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B42" s="1"/>
@@ -2671,7 +2721,9 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="1"/>
+      <c r="F42" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B43" s="1"/>
@@ -2702,7 +2754,9 @@
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B46" s="1"/>
@@ -2713,7 +2767,9 @@
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="1"/>
+      <c r="F46" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B47" s="1"/>
@@ -2724,7 +2780,9 @@
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B48" s="2" t="s">
@@ -2842,7 +2900,9 @@
       <c r="E59" s="1">
         <v>3</v>
       </c>
-      <c r="F59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B60" s="1" t="s">
@@ -2853,7 +2913,9 @@
       <c r="E60" s="1">
         <v>3</v>
       </c>
-      <c r="F60" s="1"/>
+      <c r="F60" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B61" s="1" t="s">
@@ -3385,7 +3447,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C85"/>
+  <dimension ref="B2:C88"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3795,24 +3857,37 @@
         <v>157</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C82" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C83" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C84" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C85" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B87" t="s">
+        <v>159</v>
+      </c>
+      <c r="C87" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C88" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998420E5-A960-477A-A881-587FA2B295BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534E129F-CF18-4CEB-93C1-71233AF20348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4665" yWindow="1785" windowWidth="21600" windowHeight="12735" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5010" yWindow="2130" windowWidth="21600" windowHeight="12735" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="164">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1821,6 +1821,23 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扉を作る</t>
+    <rPh sb="0" eb="1">
+      <t>トビラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HitDirのCheckHitMapPlayerを作るところ</t>
+    <rPh sb="25" eb="26">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3447,7 +3464,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C88"/>
+  <dimension ref="B2:C91"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3888,6 +3905,19 @@
     <row r="88" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C88" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B90" s="9">
+        <v>45986</v>
+      </c>
+      <c r="C90" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C91" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534E129F-CF18-4CEB-93C1-71233AF20348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56FF319-7EF3-4183-9F68-96CEC4E5431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="2130" windowWidth="21600" windowHeight="12735" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="165">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1838,6 +1838,13 @@
     <t>HitDirのCheckHitMapPlayerを作るところ</t>
     <rPh sb="25" eb="26">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドア完成</t>
+    <rPh sb="2" eb="4">
+      <t>カンセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3464,7 +3471,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C91"/>
+  <dimension ref="B2:C92"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3918,6 +3925,11 @@
     <row r="91" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C91" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C92" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56FF319-7EF3-4183-9F68-96CEC4E5431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987AC64F-70D5-487D-9DC0-99D4A9C7E83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="167">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1845,6 +1845,38 @@
     <t>ドア完成</t>
     <rPh sb="2" eb="4">
       <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→ジャンプのやり直し、自分のやられ判定、ほかの敵のカメラ適用、ステージ2を作る</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HPの実装、</t>
+    <rPh sb="3" eb="5">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3471,7 +3503,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C92"/>
+  <dimension ref="B2:C94"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3930,6 +3962,16 @@
     <row r="92" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C92" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C93" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C94" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987AC64F-70D5-487D-9DC0-99D4A9C7E83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059C21DA-26B3-4BCF-B436-472EE4E41968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="168">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1878,6 +1878,10 @@
     <rPh sb="3" eb="5">
       <t>ジッソウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプできるようになった</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3503,7 +3507,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C94"/>
+  <dimension ref="B2:C96"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3972,6 +3976,11 @@
     <row r="94" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C94" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C96" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059C21DA-26B3-4BCF-B436-472EE4E41968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BC76EA-3197-42CC-88D4-474998D3CD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="170">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1882,6 +1882,44 @@
   </si>
   <si>
     <t>ジャンプできるようになった</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→ほかの敵のカメラ適用</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>モクヒョウヤジルシ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーニングの最初の攻撃のほうの当たり判定を出すようにした（大変だった）</t>
+    <rPh sb="6" eb="8">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>タイヘン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3507,7 +3545,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C96"/>
+  <dimension ref="B2:C98"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -3981,6 +4019,16 @@
     <row r="96" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C96" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C97" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C98" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BC76EA-3197-42CC-88D4-474998D3CD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B64F4F-D79D-4103-9CD7-D0BE420BCF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="172">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1919,6 +1919,32 @@
     </rPh>
     <rPh sb="29" eb="31">
       <t>タイヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほかの敵のカメラ適用→完了</t>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今日やること→自分のやられ判定</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3545,7 +3571,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C98"/>
+  <dimension ref="B2:C101"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4029,6 +4055,16 @@
     <row r="98" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C98" t="s">
         <v>169</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C99" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C101" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B64F4F-D79D-4103-9CD7-D0BE420BCF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C06EFB2-1A83-4DFF-B84D-C9955CF89D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="175">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1945,6 +1945,42 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペンギンとのやられ判定は完了</t>
+    <rPh sb="9" eb="11">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やられモーション結構渋い→直した</t>
+    <rPh sb="8" eb="10">
+      <t>ケッコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シブ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペンギンだけ適用だから全キャラ対応するだけ</t>
+    <rPh sb="6" eb="8">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タイオウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3571,7 +3607,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C101"/>
+  <dimension ref="B2:C104"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4065,6 +4101,21 @@
     <row r="101" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C101" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C102" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C103" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C104" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C06EFB2-1A83-4DFF-B84D-C9955CF89D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0E7439-4092-40FC-AAC8-86F593B84EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="182">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1981,6 +1981,124 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の矢の自分への当たり判定をする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11月28</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全キャラ適用完了</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が攻撃をくらったときのヒットバック(今である必要ない)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵、自分の矢は壁に当たったら消えるようにしたい(氷とは逆)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ギャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浮いてる敵を用意したい</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーニングの攻撃のクールタイムを入れる←突進中から入っているため、終わってから計算する</t>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>トッシンチュウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケイサン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3607,7 +3725,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C104"/>
+  <dimension ref="B2:C110"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4083,39 +4201,72 @@
         <v>167</v>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C97" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C98" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C99" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C101" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C102" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C103" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C104" t="s">
         <v>174</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B105" t="s">
+        <v>176</v>
+      </c>
+      <c r="C105" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C106" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C107" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C108" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C109" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C110" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0E7439-4092-40FC-AAC8-86F593B84EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157CF377-4781-4AFB-96EE-8B544D72A5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="185">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2099,6 +2099,45 @@
     </rPh>
     <rPh sb="39" eb="41">
       <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢のやられ判定完了</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いったん2個目のマップに行ける様にする</t>
+    <rPh sb="5" eb="7">
+      <t>コメ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検定対策のため進捗無し</t>
+    <rPh sb="0" eb="2">
+      <t>ケンテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイサク</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>シンチョクナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3725,7 +3764,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C110"/>
+  <dimension ref="B2:C114"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4267,6 +4306,35 @@
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C110" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B111" s="9">
+        <v>45990</v>
+      </c>
+      <c r="C111" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B112" s="9">
+        <v>45991</v>
+      </c>
+      <c r="C112" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B113" s="9">
+        <v>45992</v>
+      </c>
+      <c r="C113" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C114" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157CF377-4781-4AFB-96EE-8B544D72A5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7874C50-EC5E-4A1F-9E00-9703F483E06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="186">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2116,19 +2116,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>いったん2個目のマップに行ける様にする</t>
-    <rPh sb="5" eb="7">
-      <t>コメ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>検定対策のため進捗無し</t>
     <rPh sb="0" eb="2">
       <t>ケンテイ</t>
@@ -2138,6 +2125,38 @@
     </rPh>
     <rPh sb="7" eb="10">
       <t>シンチョクナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いったん2個目のマップに行ける様にする←完了</t>
+    <rPh sb="5" eb="7">
+      <t>コメ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵埋め込み途中です</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3764,7 +3783,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C114"/>
+  <dimension ref="B2:C115"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4313,7 +4332,7 @@
         <v>45990</v>
       </c>
       <c r="C111" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
@@ -4321,7 +4340,7 @@
         <v>45991</v>
       </c>
       <c r="C112" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
@@ -4334,7 +4353,12 @@
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C114" t="s">
-        <v>183</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C115" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7874C50-EC5E-4A1F-9E00-9703F483E06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49784DC9-34D3-4680-8894-768E7D6B0C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="190">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2157,6 +2157,85 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→ステージ2の配置完了後、ゲームクリアシーン、ステージUI、敵の体力云々かんぬんをやる</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カンリョウゴ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ウンヌン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の体力、敵の体力（ボス用）、何に変身しているか、をUIとして入れる</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ2一旦完了</t>
+    <rPh sb="5" eb="7">
+      <t>イッタン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はステージ3の設置→その後、上の目標をする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>モクヒョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3783,7 +3862,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C115"/>
+  <dimension ref="B2:C119"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4359,6 +4438,26 @@
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C115" t="s">
         <v>185</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C116" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C117" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C118" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C119" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49784DC9-34D3-4680-8894-768E7D6B0C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE708DD-1B94-4414-9F42-872D96A5B363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="195">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2236,6 +2236,71 @@
     </rPh>
     <rPh sb="17" eb="19">
       <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stage3完了</t>
+    <rPh sb="6" eb="8">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームクリアシーン、死んだときのリスポーン、ステージUIをする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ遷移時の変身の移行完了</t>
+    <rPh sb="4" eb="6">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁の判定を終わった後は、リスポーンをする</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁の判定終わったので、リスポーン処理を今からする</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イマ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3862,7 +3927,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C119"/>
+  <dimension ref="B2:C124"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4458,6 +4523,31 @@
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C119" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C120" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C121" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C122" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C123" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C124" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE708DD-1B94-4414-9F42-872D96A5B363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8574299-7FD2-42F4-B43A-2456A2B92664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="200">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2301,6 +2301,59 @@
     </rPh>
     <rPh sb="19" eb="20">
       <t>イマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なんかフェードできてなくね？？？？？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラの揺れ完了</t>
+    <rPh sb="4" eb="5">
+      <t>ユ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵に当たったときの揺れはまだなし←完了</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ユ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→ゲームクリアシーン、ステージUI,敵の体力、フェード、ステージセレクト、</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あと、ステージ2と3の敵配置</t>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハイチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3927,7 +3980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C124"/>
+  <dimension ref="B2:C129"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4548,6 +4601,31 @@
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C124" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C125" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C126" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C127" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C128" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C129" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8574299-7FD2-42F4-B43A-2456A2B92664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197A7062-FEC8-499B-8680-92B911FD235B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="201">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2354,6 +2354,22 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameClearScene作成感y労、次はUI</t>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ロウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3980,7 +3996,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C129"/>
+  <dimension ref="B2:C130"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4626,6 +4642,11 @@
     <row r="129" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C129" t="s">
         <v>199</v>
+      </c>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C130" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197A7062-FEC8-499B-8680-92B911FD235B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B807A7-E23E-4A06-ADBD-29C7306C4948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2358,17 +2358,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>GameClearScene作成感y労、次はUI</t>
+    <t>GameClearScene作成完了、次はUI</t>
     <rPh sb="14" eb="16">
       <t>サクセイ</t>
     </rPh>
-    <rPh sb="16" eb="17">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ロウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
+    <rPh sb="16" eb="18">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
       <t>ツギ</t>
     </rPh>
     <phoneticPr fontId="1"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B807A7-E23E-4A06-ADBD-29C7306C4948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8D10B4-42B9-44E9-88C5-1C0DE6882870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="206">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2367,6 +2367,92 @@
     </rPh>
     <rPh sb="19" eb="20">
       <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIの途中まで完了</t>
+    <rPh sb="3" eb="5">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIはいったん完了</t>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、敵配置、のち、クリアシーンの細部、そのあと、弓、通常の能力調整</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>透過床のカックンを少し減らせた、あとは、m_colRectの下側まで当たったかどうかをして、上下のカックンをなくす</t>
+    <rPh sb="0" eb="2">
+      <t>トウカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シタガワ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ジョウゲ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stage遷移の時のhp関連終了</t>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュウリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3993,7 +4079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C130"/>
+  <dimension ref="B2:C135"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4644,6 +4730,31 @@
     <row r="130" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C130" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C131" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C132" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C133" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C134" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C135" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8D10B4-42B9-44E9-88C5-1C0DE6882870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4890BFBC-30FB-4BFE-B0BD-44A3BC593DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="3225" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5685" yWindow="1965" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="211">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2453,6 +2453,83 @@
     </rPh>
     <rPh sb="14" eb="16">
       <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ1_2,1_3の敵配置を完了</t>
+    <rPh sb="12" eb="15">
+      <t>テキハイチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢を壁に当たったら消えるように完了</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が攻撃するときにこちら側を向くように変更</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、クリアシーンの細部を作る</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PS.弓は意外と強いので、もっと使いやすくするだけでちょうどいいかも、</t>
+    <rPh sb="3" eb="4">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4079,7 +4156,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C135"/>
+  <dimension ref="B2:C140"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4722,39 +4799,67 @@
         <v>198</v>
       </c>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="129" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C129" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C130" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="131" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C131" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="132" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C132" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="133" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C133" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="134" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C134" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="135" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C135" t="s">
         <v>205</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B136" s="9">
+        <v>45995</v>
+      </c>
+      <c r="C136" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C137" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C138" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C139" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C140" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4890BFBC-30FB-4BFE-B0BD-44A3BC593DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C895BFA-F22F-4D6C-B4FA-7B3BEF6EB0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="1965" windowWidth="23130" windowHeight="15345" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="218">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2486,7 +2486,76 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>敵が攻撃するときにこちら側を向くように変更</t>
+    <t>次は、クリアシーンの細部を作る</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全部の行動を早くする←完了</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>細部編</t>
+    <rPh sb="0" eb="2">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変身のモーションの時間を作る</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>着地、歩き中、のエフェクトをつける</t>
+    <rPh sb="0" eb="2">
+      <t>チャクチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュをつける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が攻撃するときにこちら側を向くように変更←完了</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
     </rPh>
@@ -2502,23 +2571,13 @@
     <rPh sb="19" eb="21">
       <t>ヘンコウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>次は、クリアシーンの細部を作る</t>
-    <rPh sb="0" eb="1">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>サイブ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PS.弓は意外と強いので、もっと使いやすくするだけでちょうどいいかも、</t>
+    <rPh sb="21" eb="24">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PS.弓は意外と強いので、もっと使いやすくするだけでちょうどいいかも、←完了</t>
     <rPh sb="3" eb="4">
       <t>ユミ</t>
     </rPh>
@@ -2531,6 +2590,20 @@
     <rPh sb="16" eb="17">
       <t>ツカ</t>
     </rPh>
+    <rPh sb="35" eb="38">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やられ判定のクールタイムをつける</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージをくらったときに、アイテムがドロップアウトするようにする</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2561,7 +2634,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2595,6 +2668,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2665,7 +2750,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2703,6 +2788,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4156,7 +4247,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C140"/>
+  <dimension ref="B2:C147"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4820,12 +4911,12 @@
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C133" t="s">
+      <c r="C133" s="14" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C134" t="s">
+      <c r="C134" s="14" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4849,17 +4940,55 @@
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C138" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C139" s="14" t="s">
         <v>208</v>
-      </c>
-    </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C139" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C140" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B141" s="9">
+        <v>45996</v>
+      </c>
+      <c r="C141" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C142" s="13" t="s">
         <v>210</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C143" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C144" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C145" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C146" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C147" s="13" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C895BFA-F22F-4D6C-B4FA-7B3BEF6EB0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31D0CAF-0D44-4AAF-AF5D-730E9DBBC9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="7380" yWindow="3060" windowWidth="23130" windowHeight="16200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="220">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2604,6 +2604,53 @@
   </si>
   <si>
     <t>ダメージをくらったときに、アイテムがドロップアウトするようにする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→カックンを治す←今の俺では無理(先輩案件)</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オレ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ムリ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>アンケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→変身のモーションの時間、クリアシーンの細部、やられ判定のクールタイム</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ハンテイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2750,7 +2797,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2794,6 +2841,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4247,7 +4297,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C147"/>
+  <dimension ref="B2:C150"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -4976,19 +5026,34 @@
         <v>212</v>
       </c>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="145" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C145" s="13" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="146" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C146" s="13" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="147" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C147" s="13" t="s">
         <v>217</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C148" s="15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C149" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B150" s="9">
+        <v>45997</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31D0CAF-0D44-4AAF-AF5D-730E9DBBC9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B340905A-F655-4A04-A8CF-B93ED6C6592D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="3060" windowWidth="23130" windowHeight="16200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-26025" yWindow="3075" windowWidth="17955" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="222">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2650,6 +2650,35 @@
     </rPh>
     <rPh sb="30" eb="32">
       <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→やられ判定のクールタイム、変身のモーションの時間の確保</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カクホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先にクリアシーンの細部する</t>
+    <rPh sb="0" eb="1">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サイブ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4297,7 +4326,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C150"/>
+  <dimension ref="B2:C152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5054,6 +5083,16 @@
     <row r="150" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B150" s="9">
         <v>45997</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C151" s="15" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C152" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B340905A-F655-4A04-A8CF-B93ED6C6592D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640C3321-84A5-41F1-AA4D-65A27F7A56AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26025" yWindow="3075" windowWidth="17955" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-25515" yWindow="3270" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="223">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2679,6 +2679,16 @@
     </rPh>
     <rPh sb="9" eb="11">
       <t>サイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアシーン大雑把に完成</t>
+    <rPh sb="6" eb="9">
+      <t>オオザッパ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4326,7 +4336,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C152"/>
+  <dimension ref="B2:C153"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5093,6 +5103,11 @@
     <row r="152" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C152" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C153" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640C3321-84A5-41F1-AA4D-65A27F7A56AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4430BB1C-DDC7-4929-AEEB-0585AAFF5CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25515" yWindow="3270" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="9360" yWindow="3690" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="225">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2689,6 +2689,41 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大砲のアニメーション完了</t>
+    <rPh sb="0" eb="2">
+      <t>タイホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はキャラの最初の自動化、着地後のアニメーションの変化、ゴールの文字表記</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ジドウカ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>チャクチゴ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4336,7 +4371,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C153"/>
+  <dimension ref="B2:C155"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5108,6 +5143,19 @@
     <row r="153" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C153" t="s">
         <v>222</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B154" s="9">
+        <v>45998</v>
+      </c>
+      <c r="C154" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C155" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4430BB1C-DDC7-4929-AEEB-0585AAFF5CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F678FF-7456-4C53-BBBE-A21D52579891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="3690" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="8835" yWindow="4395" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="229">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2724,6 +2724,70 @@
     </rPh>
     <rPh sb="34" eb="36">
       <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いま、キャラの最初の自動化の途中</t>
+    <rPh sb="7" eb="9">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ジドウカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さらなる目標→変身のモーションの時間、クリアシーンの細部、やられ判定のクールタイム</t>
+    <rPh sb="4" eb="6">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラの自動化完了、着地後のあにめーしょん完了</t>
+    <rPh sb="4" eb="6">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チャクチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、さらなる目標のところをする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>モクヒョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4371,7 +4435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C155"/>
+  <dimension ref="B2:C159"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5156,6 +5220,26 @@
     <row r="155" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C155" t="s">
         <v>224</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C156" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C157" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C158" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C159" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F678FF-7456-4C53-BBBE-A21D52579891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2E422F-31E1-46E3-9FC4-6929C7987598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8835" yWindow="4395" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="234">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2788,6 +2788,83 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新たな目標→バーニングが壁に当たった時、画面が揺れるようにして、モーションできるように</t>
+    <rPh sb="0" eb="1">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ユ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑難しそうだからだいぶ最後のほう</t>
+    <rPh sb="1" eb="2">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さらなる目標→変身のモーションの時間、やられ判定のクールタイム</t>
+    <rPh sb="4" eb="6">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>走っているときのエフェクトとか、ジャンプ着地のエフェクトとか、</t>
+    <rPh sb="0" eb="1">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チャクチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムをドロップアウトする←システム的にする意味はないからエフェクトだけ外に出す演出を出す</t>
+    <rPh sb="19" eb="20">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ソト</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ダ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4435,7 +4512,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C159"/>
+  <dimension ref="B2:C164"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5240,6 +5317,34 @@
     <row r="159" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C159" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B160" s="9">
+        <v>45999</v>
+      </c>
+      <c r="C160" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C161" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C162" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C163" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C164" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2E422F-31E1-46E3-9FC4-6929C7987598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FAFF4B-B9AE-4638-8BD8-3AD7BB37C1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="8835" yWindow="4395" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="239">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2865,6 +2865,62 @@
     </rPh>
     <rPh sb="44" eb="45">
       <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変身のモーションの時間←達成</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→やられ判定のクールタイム</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーニングの弱体化←完了←実装はしたけど、つけるのはやめてる</t>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあとの目標→エフェクトor背景orタイトルシーン</t>
+    <rPh sb="5" eb="7">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>update_が切り替わるごとにちかちかなるのが気になる（CloarSceneはならない）</t>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>キ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4512,7 +4568,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C164"/>
+  <dimension ref="B2:C169"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5345,6 +5401,31 @@
     <row r="164" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C164" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C165" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C166" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C167" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C168" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C169" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FAFF4B-B9AE-4638-8BD8-3AD7BB37C1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B061C6AA-0081-4D60-9D7D-6945B589FE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8835" yWindow="4395" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6930" yWindow="3270" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="241">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2912,7 +2912,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>update_が切り替わるごとにちかちかなるのが気になる（CloarSceneはならない）</t>
+    <t>update_が切り替わるごとにちかちかなるのが気になる（CloarSceneはならない）←完了</t>
     <rPh sb="8" eb="9">
       <t>キ</t>
     </rPh>
@@ -2921,6 +2921,32 @@
     </rPh>
     <rPh sb="24" eb="25">
       <t>キ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標←キーコンフィグシーンの実装←いったん完了</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、やられ判定のクールタイム</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4568,11 +4594,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C169"/>
+  <dimension ref="B2:C171"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.5" customWidth="1"/>
+    <col min="3" max="3" width="85.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
@@ -5383,49 +5409,62 @@
         <v>229</v>
       </c>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C161" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C162" s="13" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="163" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C163" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C164" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C165" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C166" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="167" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C167" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C168" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="169" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C169" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B170" s="9">
+        <v>46000</v>
+      </c>
+      <c r="C170" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C171" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B061C6AA-0081-4D60-9D7D-6945B589FE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC288F6-295F-4AC6-B619-4A757A46493E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6930" yWindow="3270" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="242">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2941,12 +2941,31 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>次は、やられ判定のクールタイム</t>
+    <t>次は、やられ判定のクールタイム←完了</t>
     <rPh sb="0" eb="1">
       <t>ツギ</t>
     </rPh>
     <rPh sb="6" eb="8">
       <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→エフェクト、or背景,アイテムをドロップアウトの演出</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>エンシュツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4594,7 +4613,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C171"/>
+  <dimension ref="B2:C172"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5465,6 +5484,11 @@
     <row r="171" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C171" t="s">
         <v>240</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C172" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC288F6-295F-4AC6-B619-4A757A46493E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCDB574-B985-4B10-AE14-0D0D4DE9ED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6930" yWindow="3270" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3360" yWindow="1605" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="247">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2966,6 +2966,71 @@
     </rPh>
     <rPh sb="29" eb="31">
       <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→アイテムをドロップアウトする演出</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動に慣性(加速度をつける)、プレイヤーの毎秒0更新のところを減速にする</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゲンソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミーライダーの当たり判定を広げる</t>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>着地のエフェクト←完了</t>
+    <rPh sb="0" eb="2">
+      <t>チャクチ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムをドロップアウトする演出の途中</t>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4613,7 +4678,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C172"/>
+  <dimension ref="B2:C177"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5439,12 +5504,12 @@
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C163" t="s">
+      <c r="C163" s="13" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C164" t="s">
+      <c r="C164" s="13" t="s">
         <v>233</v>
       </c>
     </row>
@@ -5464,7 +5529,7 @@
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C168" t="s">
+      <c r="C168" s="13" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5489,6 +5554,34 @@
     <row r="172" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C172" t="s">
         <v>241</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B173" s="9">
+        <v>46001</v>
+      </c>
+      <c r="C173" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C174" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C175" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C176" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C177" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCDB574-B985-4B10-AE14-0D0D4DE9ED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72284959-0DFD-4F3A-9F1E-45C980C7EBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="1605" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6930" yWindow="3270" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="250">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2980,41 +2980,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>移動に慣性(加速度をつける)、プレイヤーの毎秒0更新のところを減速にする</t>
-    <rPh sb="0" eb="2">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>カソクド</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>マイビョウ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ゲンソク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エネミーライダーの当たり判定を広げる</t>
-    <rPh sb="9" eb="10">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ヒロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>着地のエフェクト←完了</t>
     <rPh sb="0" eb="2">
       <t>チャクチ</t>
@@ -3031,6 +2996,86 @@
     </rPh>
     <rPh sb="17" eb="19">
       <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムをドロップアウトする演出完了</t>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミーアーチャーの範囲拡大完了</t>
+    <rPh sb="10" eb="12">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクダイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミーライダーの当たり判定を広げる完了</t>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動に慣性(加速度をつける)、プレイヤーの毎秒0更新のところを減速にする←完了</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゲンソク</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→タイトルシーンの細部、背景をする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハイケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4678,7 +4723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C177"/>
+  <dimension ref="B2:C180"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5560,28 +5605,43 @@
       <c r="B173" s="9">
         <v>46001</v>
       </c>
-      <c r="C173" s="13" t="s">
+      <c r="C173" s="15" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C174" t="s">
-        <v>243</v>
+      <c r="C174" s="14" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C175" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C176" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="177" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C177" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C178" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C179" t="s">
         <v>246</v>
+      </c>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C180" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72284959-0DFD-4F3A-9F1E-45C980C7EBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA406DB6-F414-46B8-ABD4-BAF6613C3738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6930" yWindow="3270" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="254">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3076,6 +3076,52 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑金曜日、学校で</t>
+    <rPh sb="1" eb="4">
+      <t>キンヨウビ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→背景、エフェクト、</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景ループの設定は完了</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの慣性はlerpでしたら良いらしい</t>
+    <rPh sb="6" eb="8">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4723,7 +4769,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C180"/>
+  <dimension ref="B2:C184"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5642,6 +5688,26 @@
     <row r="180" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C180" t="s">
         <v>249</v>
+      </c>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C181" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C182" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C183" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C184" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA406DB6-F414-46B8-ABD4-BAF6613C3738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCABD98-0280-4472-A258-B63F8A692282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6930" yWindow="3270" windowWidth="22170" windowHeight="13200" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5220" yWindow="3870" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="262">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3122,6 +3122,92 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクトをする、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>走ってるときに定期的に土誇りのエフェクト、</t>
+    <rPh sb="0" eb="1">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>テイキテキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツチホコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンの関数化をやって、2_1をつくりやすくする</t>
+    <rPh sb="4" eb="7">
+      <t>カンスウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェード処理、背景を家にいるうちに作るのもあり</t>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土誇りエフェクト完了←いったん</t>
+    <rPh sb="0" eb="2">
+      <t>ツチホコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、フェード処理</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あとで、フェードインdrawとフェードアウトdraw、死んだときの処理を分ける</t>
+    <rPh sb="27" eb="28">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（現在のは、死んだときの処理にする）</t>
+    <rPh sb="1" eb="3">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4769,7 +4855,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C184"/>
+  <dimension ref="B2:C192"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5670,44 +5756,87 @@
         <v>243</v>
       </c>
     </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C177" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C178" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C179" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C180" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C181" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C182" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="183" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C183" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C184" t="s">
         <v>253</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B185" s="9">
+        <v>46002</v>
+      </c>
+      <c r="C185" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C186" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C187" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C188" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C189" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C190" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C191" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C192" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCABD98-0280-4472-A258-B63F8A692282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFF1708-FCC1-4AD6-9C30-661420DA9D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="3870" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="273">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3186,19 +3186,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>あとで、フェードインdrawとフェードアウトdraw、死んだときの処理を分ける</t>
-    <rPh sb="27" eb="28">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>（現在のは、死んだときの処理にする）</t>
     <rPh sb="1" eb="3">
       <t>ゲンザイ</t>
@@ -3208,6 +3195,102 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入るとき→FadeInDraw,FadeInUpdate</t>
+    <rPh sb="0" eb="1">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死んだとき、再入場→FadeDraw,DyingUpdate(),</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>サイニュウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扉に入るとき→FadeOutDraw,FadeOutUpdate()</t>
+    <rPh sb="0" eb="1">
+      <t>トビラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NormalUpdate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NormalDraw</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>playerのをいけないようにする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あとで、フェードインdrawとフェードアウトdraw、死んだときの処理を分ける→完了</t>
+    <rPh sb="27" eb="28">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラの生成がおかしい気がする</t>
+    <rPh sb="4" eb="6">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペンギンがWalkとAttackがういてる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が当たったときはDyingActをしてからけすようにする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Releaseように補助線とかをちゃんと#ifDebugにいれる←完了</t>
+    <rPh sb="10" eb="13">
+      <t>ホジョセン</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ヤジルシカンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4855,7 +4938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C192"/>
+  <dimension ref="B2:C197"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5831,12 +5914,37 @@
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C191" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C192" t="s">
-        <v>261</v>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C193" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C194" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C195" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="196" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C196" s="14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="197" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C197" s="14" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -5847,18 +5955,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:D9"/>
+  <dimension ref="B3:E14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="53.625" customWidth="1"/>
+    <col min="4" max="4" width="14.375" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>87</v>
       </c>
@@ -5866,7 +5976,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
         <v>98</v>
       </c>
@@ -5874,7 +5984,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C7" t="s">
         <v>99</v>
       </c>
@@ -5882,9 +5992,33 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C9" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFF1708-FCC1-4AD6-9C30-661420DA9D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA7606B-1DB9-4A4C-8AA1-CB2C0A297EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3360" yWindow="1605" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="279">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3290,6 +3290,90 @@
       <t>ホジョセン</t>
     </rPh>
     <rPh sb="32" eb="35">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のY座標もいつか合わせる</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーマル剣にエフェクトをつける</t>
+    <rPh sb="4" eb="5">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブロック一個おきのところを見た目を変える</t>
+    <rPh sb="4" eb="6">
+      <t>イチコ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリア演出に回転を追加</t>
+    <rPh sb="3" eb="5">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアシーン→大砲で飛んでいるとき、途中で一回転をくるりんってさせるといい←完了</t>
+    <rPh sb="7" eb="9">
+      <t>タイホウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イッカイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→プレイヤーのダッシュを作る←完了</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="16" eb="19">
       <t>ヤジルシカンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4938,7 +5022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C197"/>
+  <dimension ref="B2:C203"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -5922,29 +6006,62 @@
         <v>260</v>
       </c>
     </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C193" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C194" s="14" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C195" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="196" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C196" s="14" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="197" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C197" s="14" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B198" s="9">
+        <v>46003</v>
+      </c>
+      <c r="C198" s="14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C199" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C200" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C201" s="14" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C202" s="14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C203" s="15" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA7606B-1DB9-4A4C-8AA1-CB2C0A297EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05092FC4-F45B-46ED-8958-1FEEEA64459A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="1605" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="282">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3375,6 +3375,60 @@
     </rPh>
     <rPh sb="16" eb="19">
       <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→ステージ2を作り始める</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムが出た時のエフェクトや描画順を調整、追加</t>
+    <rPh sb="5" eb="6">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→敵が当たったらノックバックして、エフェクトをつける←やっぱりエフェクトだけつける←完了</t>
+    <rPh sb="0" eb="3">
+      <t>モクヒョウヤジルシ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3406,7 +3460,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3452,6 +3506,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3522,7 +3582,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3569,6 +3629,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5022,7 +5085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C203"/>
+  <dimension ref="B2:C206"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6012,7 +6075,7 @@
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C194" s="14" t="s">
+      <c r="C194" s="15" t="s">
         <v>269</v>
       </c>
     </row>
@@ -6040,12 +6103,12 @@
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C199" s="14" t="s">
+      <c r="C199" s="15" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C200" s="14" t="s">
+      <c r="C200" s="15" t="s">
         <v>277</v>
       </c>
     </row>
@@ -6062,6 +6125,24 @@
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C203" s="15" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B204" s="9">
+        <v>46004</v>
+      </c>
+      <c r="C204" s="15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C205" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C206" s="16" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05092FC4-F45B-46ED-8958-1FEEEA64459A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D0E719-00EE-41C9-B481-E2A9FDCBB7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="293">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3429,6 +3429,140 @@
     </rPh>
     <rPh sb="44" eb="46">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ2の敵配置半分完了</t>
+    <rPh sb="6" eb="9">
+      <t>テキハイチ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファまでにあとすること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ボスを作る</t>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・チュートリアルを作る</t>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスのところのカメラフレーム固定</t>
+    <rPh sb="14" eb="16">
+      <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスを倒したフラグを作って、解除で元に戻る</t>
+    <rPh sb="3" eb="4">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの挙動</t>
+    <rPh sb="3" eb="5">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回転攻撃、ものを投げてくる攻撃、変な挙動の移動、</t>
+    <rPh sb="0" eb="2">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヘン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの導入完了</t>
+    <rPh sb="3" eb="5">
+      <t>ドウニュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスにおけるカメラワークも完了</t>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ボスの攻撃方法、移動方法の多様化、プレイヤーの当たり判定との一致、体力をつける</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>コウゲキホウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>イドウホウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>タヨウカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>タイリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5085,7 +5219,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C206"/>
+  <dimension ref="B2:C210"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6145,6 +6279,32 @@
         <v>280</v>
       </c>
     </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B207" s="9">
+        <v>46006</v>
+      </c>
+      <c r="C207" s="15" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B208" s="9">
+        <v>46007</v>
+      </c>
+      <c r="C208" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="209" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C209" s="15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="210" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C210" s="15" t="s">
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6153,9 +6313,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:E14"/>
+  <dimension ref="B3:E22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.625" customWidth="1"/>
     <col min="4" max="4" width="14.375" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
@@ -6217,6 +6378,44 @@
     <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
         <v>264</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B16" s="9">
+        <v>46006</v>
+      </c>
+      <c r="C16" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C17" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C19" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C20" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C21" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C22" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D0E719-00EE-41C9-B481-E2A9FDCBB7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF0845A-3144-447A-A443-6A5D98DA2BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="298">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3563,6 +3563,47 @@
     </rPh>
     <rPh sb="36" eb="38">
       <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーがカメラの外にいけないようにしないといけない</t>
+    <rPh sb="10" eb="11">
+      <t>ソト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーがカメラの外にいけないようにしないといけない←完了</t>
+    <rPh sb="10" eb="11">
+      <t>ソト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EnemyEliteのジャンプのためにcharacterのupdateをもう一つ作って、そっちでEliteを動かす</t>
+    <rPh sb="54" eb="55">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今日はボスの挙動、体力をつける←体力完了</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの重力をもう少し緩やかにする</t>
+    <rPh sb="6" eb="8">
+      <t>ジュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ユル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5219,7 +5260,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C210"/>
+  <dimension ref="B2:C215"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6295,14 +6336,42 @@
         <v>290</v>
       </c>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="209" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C209" s="15" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C210" s="15" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C211" s="15" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B212" s="9">
+        <v>46008</v>
+      </c>
+      <c r="C212" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C213" s="15" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C214" s="14" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C215" s="14" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF0845A-3144-447A-A443-6A5D98DA2BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB2D7C4-AFE7-47CD-A5F9-800751F61FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="303">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3604,6 +3604,74 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>ユル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス攻撃2完了</t>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あとは、攻撃2は波動を出す</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハドウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先に体力バーをつける</t>
+    <rPh sb="0" eb="1">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体力バー完了</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残りのボスのやることは、攻撃3の実装、波動、カメラを被ダメと攻撃の要所要所でつけること</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="33" eb="37">
+      <t>ヨウショヨウショ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5260,7 +5328,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C215"/>
+  <dimension ref="B2:C220"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6372,6 +6440,31 @@
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C215" s="14" t="s">
         <v>295</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C216" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C217" s="15" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C218" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C219" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C220" s="15" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB2D7C4-AFE7-47CD-A5F9-800751F61FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891E351D-4957-478A-858F-ADCF867CB4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="1050" yWindow="330" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="304">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3651,7 +3651,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>残りのボスのやることは、攻撃3の実装、波動、カメラを被ダメと攻撃の要所要所でつけること</t>
+    <t>残りのボスのやることは、攻撃3の実装、波動、カメラの振動を被ダメと攻撃の要所要所でつけること</t>
     <rPh sb="0" eb="1">
       <t>ノコ</t>
     </rPh>
@@ -3664,14 +3664,30 @@
     <rPh sb="19" eb="21">
       <t>ハドウ</t>
     </rPh>
-    <rPh sb="26" eb="27">
+    <rPh sb="26" eb="28">
+      <t>シンドウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
       <t>ヒ</t>
     </rPh>
-    <rPh sb="30" eb="32">
+    <rPh sb="33" eb="35">
       <t>コウゲキ</t>
     </rPh>
-    <rPh sb="33" eb="37">
+    <rPh sb="36" eb="40">
       <t>ヨウショヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃3の弾だし完了</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5328,7 +5344,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C220"/>
+  <dimension ref="B2:C221"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6465,6 +6481,11 @@
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C220" s="15" t="s">
         <v>302</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C221" s="15" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891E351D-4957-478A-858F-ADCF867CB4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77101377-05D4-4BFD-B94E-D65A49A783AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="330" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="312">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3679,14 +3679,154 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃3の弾だし完了</t>
+    <t>ぐるぐる攻撃の前に無敵をつける演出をつける</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ムテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾だし、角度をつけるor軌道を変化させる(爆発エフェクト内のもったいない気がする)</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WaveManagerのcppつくるところ←完了</t>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーが被弾した後、何秒かは無敵でちかちかさせる</t>
+    <rPh sb="6" eb="8">
+      <t>ヒダン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナンビョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ムテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃3の弾だし←完了</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
     </rPh>
     <rPh sb="4" eb="5">
       <t>タマ</t>
     </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃1の当たり判定、攻撃3のボムを氷にできるようにする</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
     <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コオリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷と弓が当たったら弓が消えるように</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタンのやつを雑に実装したから、ちゃんと、stateで変わるように変更する（星がくるくる回るようにしたい）</t>
+    <rPh sb="7" eb="8">
+      <t>ザツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>マワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の目標→ボスの実装完了</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
       <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -5344,7 +5484,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C221"/>
+  <dimension ref="B2:C229"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6454,7 +6594,7 @@
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C215" s="14" t="s">
+      <c r="C215" s="15" t="s">
         <v>295</v>
       </c>
     </row>
@@ -6485,7 +6625,47 @@
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C221" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C222" s="14" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C223" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C224" s="15" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="225" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C225" s="16" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="226" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C226" s="14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="227" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C227" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="228" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C228" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="229" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C229" s="15" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77101377-05D4-4BFD-B94E-D65A49A783AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D446A540-C2AA-4A91-8F08-74004C33080C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="319">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3651,34 +3651,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>残りのボスのやることは、攻撃3の実装、波動、カメラの振動を被ダメと攻撃の要所要所でつけること</t>
-    <rPh sb="0" eb="1">
-      <t>ノコ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ハドウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>シンドウ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="36" eb="40">
-      <t>ヨウショヨウショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ぐるぐる攻撃の前に無敵をつける演出をつける</t>
     <rPh sb="4" eb="6">
       <t>コウゲキ</t>
@@ -3775,25 +3747,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>氷と弓が当たったら弓が消えるように</t>
-    <rPh sb="0" eb="1">
-      <t>コオリ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ユミ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ユミ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スタンのやつを雑に実装したから、ちゃんと、stateで変わるように変更する（星がくるくる回るようにしたい）</t>
     <rPh sb="7" eb="8">
       <t>ザツ</t>
@@ -3829,6 +3782,129 @@
     <rPh sb="10" eb="12">
       <t>カンリョウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスが死亡アニメーションに入る→isDeadがtrue</t>
+    <rPh sb="3" eb="5">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの爆弾をこおりづけにする←完了</t>
+    <rPh sb="3" eb="5">
+      <t>バクダン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷と弓が当たったら弓が消えるように←完了</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残りのボスのやることは、攻撃3の実装、波動、カメラの振動を被ダメと攻撃の要所要所でつけること←完了</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハドウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シンドウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="36" eb="40">
+      <t>ヨウショヨウショ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの攻撃一旦完了</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イッタン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ステージセレクトシーンを作る←完了</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーニングのctをつける（すべての攻撃にct）</t>
+    <rPh sb="17" eb="19">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの攻撃のランダム化←完了</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダウンはランダムじゃないほうがいいかもしれない（やりかたはよくわからない）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5484,7 +5560,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C229"/>
+  <dimension ref="B2:C235"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6620,52 +6696,85 @@
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C220" s="15" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C221" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C222" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C223" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C224" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C225" s="16" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C225" s="16" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="226" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C226" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C227" s="15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C228" s="14" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C227" s="14" t="s">
+    <row r="229" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C229" s="15" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C228" s="14" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C229" s="15" t="s">
+    <row r="230" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B230" s="9">
+        <v>46009</v>
+      </c>
+      <c r="C230" s="15" t="s">
         <v>311</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C231" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C232" s="15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C233" s="13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C234" s="15" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C235" s="15" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -6676,7 +6785,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:E22"/>
+  <dimension ref="B3:E24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6751,34 +6860,42 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C18" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C19" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C21" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
         <v>289</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B24" s="9">
+        <v>46009</v>
+      </c>
+      <c r="C24" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D446A540-C2AA-4A91-8F08-74004C33080C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8CAB35-8C7C-4AD3-A6EE-68253808B9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -3728,25 +3728,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃1の当たり判定、攻撃3のボムを氷にできるようにする</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>コオリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スタンのやつを雑に実装したから、ちゃんと、stateで変わるように変更する（星がくるくる回るようにしたい）</t>
     <rPh sb="7" eb="8">
       <t>ザツ</t>
@@ -3884,13 +3865,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>バーニングのctをつける（すべての攻撃にct）</t>
-    <rPh sb="17" eb="19">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ボスの攻撃のランダム化←完了</t>
     <rPh sb="3" eb="5">
       <t>コウゲキ</t>
@@ -3905,6 +3879,38 @@
   </si>
   <si>
     <t>ダウンはランダムじゃないほうがいいかもしれない（やりかたはよくわからない）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーニングのctをつける（すべての攻撃にct）←完了</t>
+    <rPh sb="17" eb="19">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃1の当たり判定、攻撃3のボムを氷にできるようにする←完了</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6696,7 +6702,7 @@
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C220" s="15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
@@ -6725,23 +6731,23 @@
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C226" s="14" t="s">
-        <v>307</v>
+      <c r="C226" s="15" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C227" s="15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C228" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C229" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="230" spans="2:3" x14ac:dyDescent="0.4">
@@ -6749,32 +6755,32 @@
         <v>46009</v>
       </c>
       <c r="C230" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="231" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C231" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="232" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C232" s="15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="233" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C233" s="13" t="s">
-        <v>316</v>
+      <c r="C233" s="15" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C234" s="15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C235" s="15" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -6895,7 +6901,7 @@
         <v>46009</v>
       </c>
       <c r="C24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8CAB35-8C7C-4AD3-A6EE-68253808B9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D89A14C-41AF-47F9-A0A2-6A6EB7422037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="5610" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="329">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -3910,6 +3910,139 @@
     </rPh>
     <rPh sb="27" eb="30">
       <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの慣性をつけた(攻撃中も)</t>
+    <rPh sb="6" eb="8">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーマル以外で変身をできなくした</t>
+    <rPh sb="4" eb="6">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドアの位置調整</t>
+    <rPh sb="3" eb="5">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【課題】弓の操作性が悪すぎる</t>
+    <rPh sb="1" eb="3">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ソウサセイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスを右側の上限をつける←完了</t>
+    <rPh sb="3" eb="5">
+      <t>ミギガワ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウゲン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの爆弾と通常攻撃が当たったら爆弾が消えるようにする</t>
+    <rPh sb="3" eb="5">
+      <t>バクダン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バクダン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変身のモーションで吸い込みを入れるのはあり</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを画面外なら消す、nullptrになったら消す処理をUpdateでする</t>
+    <rPh sb="5" eb="8">
+      <t>ガメンガイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復アイテムを作る</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムをいつ倒してもドロップするようにする→完了</t>
+    <rPh sb="7" eb="8">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3941,7 +4074,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3993,6 +4126,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4063,7 +4202,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4113,6 +4252,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5566,7 +5708,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C235"/>
+  <dimension ref="B2:C245"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6781,6 +6923,59 @@
     <row r="235" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C235" s="15" t="s">
         <v>316</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B236" s="9">
+        <v>46010</v>
+      </c>
+      <c r="C236" s="15" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C237" s="15" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C238" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C239" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C240" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="241" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C241" s="17" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="242" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C242" s="13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="243" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C243" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="244" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C244" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="245" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C245" s="14" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D89A14C-41AF-47F9-A0A2-6A6EB7422037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8336091D-CEA9-49ED-8BD1-28A25470A745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-26190" yWindow="3510" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="330">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4027,21 +4027,40 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>回復アイテムを作る</t>
-    <rPh sb="0" eb="2">
-      <t>カイフク</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アイテムをいつ倒してもドロップするようにする→完了</t>
     <rPh sb="7" eb="8">
       <t>タオ</t>
     </rPh>
     <rPh sb="23" eb="25">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残りの課題→タイトルシーン、ステージセレクトシーン、背景、ゴールシーンの細部</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>サイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復アイテムを作る→完了</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
       <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -5708,7 +5727,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C245"/>
+  <dimension ref="B2:C246"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6940,7 +6959,7 @@
     </row>
     <row r="238" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C238" s="15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="239" spans="2:3" x14ac:dyDescent="0.4">
@@ -6975,7 +6994,12 @@
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C245" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="246" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C246" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8336091D-CEA9-49ED-8BD1-28A25470A745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA5B36D-A0CB-4C28-9AD0-6E5A5234148F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26190" yWindow="3510" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-25005" yWindow="3570" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="332">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4062,6 +4062,29 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスを倒したらコピーできるようにする(攻撃は波動orぐるぐる)</t>
+    <rPh sb="3" eb="4">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーンを途中まで作った</t>
+    <rPh sb="8" eb="10">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5727,7 +5750,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C246"/>
+  <dimension ref="B2:C248"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -6972,34 +6995,47 @@
         <v>321</v>
       </c>
     </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="241" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C241" s="17" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="242" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C242" s="13" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="243" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C243" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C244" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C245" s="14" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="246" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C246" t="s">
         <v>328</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C247" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B248" s="9">
+        <v>46011</v>
+      </c>
+      <c r="C248" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA5B36D-A0CB-4C28-9AD0-6E5A5234148F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A503E6-BEE2-4EBE-B626-66C04286218F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25005" yWindow="3570" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="337">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4085,6 +4085,50 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→タイトルシーンをもっとする</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーンあらかた完了</t>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ゴールシーンの細部、</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そして、ボスシーンの細部を作るための研究</t>
+    <rPh sb="10" eb="12">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ケンキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴールシーンは看板をたてた</t>
+    <rPh sb="7" eb="9">
+      <t>カンバン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5750,7 +5794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C248"/>
+  <dimension ref="B2:C253"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7036,6 +7080,34 @@
       </c>
       <c r="C248" t="s">
         <v>331</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B249" s="9">
+        <v>46012</v>
+      </c>
+      <c r="C249" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C250" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C251" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C252" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C253" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A503E6-BEE2-4EBE-B626-66C04286218F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A972837-E0E5-40CB-8FE2-B66E37C1BC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25005" yWindow="3570" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3600" yWindow="4725" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="339">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4129,6 +4129,35 @@
     <t>ゴールシーンは看板をたてた</t>
     <rPh sb="7" eb="9">
       <t>カンバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの構成、熊と狼の二匹構成</t>
+    <rPh sb="3" eb="5">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>クマ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニヒキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、背景</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハイケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5794,7 +5823,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C253"/>
+  <dimension ref="B2:C254"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7110,6 +7139,11 @@
         <v>336</v>
       </c>
     </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C254" t="s">
+        <v>338</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7118,7 +7152,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:E24"/>
+  <dimension ref="B3:E26"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7229,6 +7263,11 @@
       </c>
       <c r="C24" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C26" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A972837-E0E5-40CB-8FE2-B66E37C1BC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363EC52D-C627-4DDE-A12F-25968F7027A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="4725" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-24555" yWindow="5490" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5823,7 +5823,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C254"/>
+  <dimension ref="B2:C255"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7142,6 +7142,11 @@
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C254" t="s">
         <v>338</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B255" s="9">
+        <v>46013</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363EC52D-C627-4DDE-A12F-25968F7027A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1471B1C7-C963-49CE-83FB-4E3C2D98A645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24555" yWindow="5490" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="8595" yWindow="5565" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="342">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4158,6 +4158,39 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→背景、残機</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ザンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景完了</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は残機</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ザンキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5823,7 +5856,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C255"/>
+  <dimension ref="B2:C257"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7147,6 +7180,19 @@
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="9">
         <v>46013</v>
+      </c>
+      <c r="C255" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C256" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="257" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C257" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1471B1C7-C963-49CE-83FB-4E3C2D98A645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0303303B-A2E9-4FF2-BE0B-B30243FC1411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8595" yWindow="5565" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="347">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4191,6 +4191,80 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ザンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→残機実装、ステージセレクトの細部化</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ザンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアシーンでhpと残機を渡して、体力、残機はステージ引継ぎにする</t>
+    <rPh sb="10" eb="12">
+      <t>ザンキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ザンキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒキツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次することは、残機数をUIに表示させること</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ザンキスウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残機を実装完了</t>
+    <rPh sb="0" eb="2">
+      <t>ザンキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はステージセレクトの細部化</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>サイブカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5856,7 +5930,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C257"/>
+  <dimension ref="B2:C262"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7190,9 +7264,37 @@
         <v>340</v>
       </c>
     </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C257" t="s">
         <v>341</v>
+      </c>
+    </row>
+    <row r="258" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B258" s="9">
+        <v>46015</v>
+      </c>
+      <c r="C258" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C259" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C260" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C261" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="262" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C262" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0303303B-A2E9-4FF2-BE0B-B30243FC1411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F4CFE5-354B-42CF-B42D-128A09DE9D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8595" yWindow="5565" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="353">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4265,6 +4265,90 @@
     </rPh>
     <rPh sb="11" eb="14">
       <t>サイブカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクトの大まかなの完了</t>
+    <rPh sb="9" eb="10">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ボスシーン</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先にステージクリアシーンにステージUIを実装←完了</t>
+    <rPh sb="0" eb="1">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスシーン、キャラの皮だけなら実装完了</t>
+    <rPh sb="10" eb="11">
+      <t>カワ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、中身</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナカミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>狼は善逸みたいな感じで、熊はそのまま、別のボス戦で魚を出してもよい</t>
+    <rPh sb="0" eb="1">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>クマ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ダ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5930,7 +6014,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C262"/>
+  <dimension ref="B2:C268"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7295,6 +7379,39 @@
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C262" t="s">
         <v>346</v>
+      </c>
+    </row>
+    <row r="263" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B263" s="9">
+        <v>45955</v>
+      </c>
+      <c r="C263" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="264" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C264" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="265" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C265" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="266" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C266" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="267" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C267" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="268" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C268" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F4CFE5-354B-42CF-B42D-128A09DE9D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57CC6A0-1CB6-40A7-9744-332E883913CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8595" yWindow="5565" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="8055" yWindow="4320" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="361">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4349,6 +4349,101 @@
     </rPh>
     <rPh sb="27" eb="28">
       <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>狼のディティール</t>
+    <rPh sb="0" eb="1">
+      <t>オオカミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3fで止まって、目を光らせる</t>
+    <rPh sb="3" eb="4">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その後ワープさせて、斬撃を出す（プレイヤーを移動させてもよい）</t>
+    <rPh sb="2" eb="3">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ザンゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その時、雷のようなエフェクトを出す</t>
+    <rPh sb="2" eb="3">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カミナリ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>狼の攻撃1のアニメーション完了</t>
+    <rPh sb="0" eb="1">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後は攻撃2したら終わり</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熊はほぼテコ入れなし</t>
+    <rPh sb="0" eb="1">
+      <t>クマ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあとの魚を考える</t>
+    <rPh sb="5" eb="6">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カンガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6014,7 +6109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C268"/>
+  <dimension ref="B2:C272"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7414,6 +7509,26 @@
         <v>352</v>
       </c>
     </row>
+    <row r="269" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C269" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="270" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C270" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="271" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C271" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="272" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C272" t="s">
+        <v>360</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7422,7 +7537,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:E26"/>
+  <dimension ref="B3:E30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7538,6 +7653,26 @@
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
         <v>337</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C27" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C28" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C29" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C30" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57CC6A0-1CB6-40A7-9744-332E883913CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A91A7B-51DA-4800-BF24-239208F80606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8055" yWindow="4320" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="373">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4444,6 +4444,180 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの当たり判定を大きくする</t>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の種類によって、波動の種類を変える</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハドウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚の挙動→</t>
+    <rPh sb="0" eb="1">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1体ずつ歩くだけの敵、</t>
+    <rPh sb="1" eb="2">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何体か倒したら、全員集合して、攻撃してくる、</t>
+    <rPh sb="0" eb="2">
+      <t>ナンタイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ゼンインシュウゴウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、ばらばらになって、そこを攻撃したら、フェーズ1完了</t>
+    <rPh sb="17" eb="19">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全員集合の時のイメージは大車輪の中に本命がいるイメージ</t>
+    <rPh sb="0" eb="4">
+      <t>ゼンインシュウゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ダイシャリン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ホンメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熊の攻撃に合わせて、サーモンが跳ねるようにする←完了</t>
+    <rPh sb="0" eb="1">
+      <t>クマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぼすとプレイヤーの当たり判定関連もしないといけない←完了</t>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ハンテイカンレン</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先に熊と狼の判定を終わらせる←完了</t>
+    <rPh sb="0" eb="1">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>クマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ヤジルシカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーコンフィグシーンのステージセレクトをするために</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SceneControllerにplayer情報を持つstructを持たせて、更新させるようにする</t>
+    <rPh sb="22" eb="24">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>コウシン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6109,7 +6283,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C272"/>
+  <dimension ref="B2:C279"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7529,6 +7703,44 @@
         <v>360</v>
       </c>
     </row>
+    <row r="273" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B273" s="9">
+        <v>46018</v>
+      </c>
+      <c r="C273" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C274" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C275" s="13" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C276" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C277" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C278" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C279" t="s">
+        <v>372</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7537,11 +7749,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C900D9B4-3F19-49AA-ADBB-4B1B36CB5C48}">
-  <dimension ref="B3:E30"/>
+  <dimension ref="B3:E36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.625" customWidth="1"/>
+    <col min="3" max="3" width="60.125" customWidth="1"/>
     <col min="4" max="4" width="14.375" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
@@ -7673,6 +7885,31 @@
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
         <v>356</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C32" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C33" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C34" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C35" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C36" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A91A7B-51DA-4800-BF24-239208F80606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B77DAC-36B5-4D70-BF75-1D998C359B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8055" yWindow="4320" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="375">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4618,6 +4618,20 @@
     </rPh>
     <rPh sb="39" eb="41">
       <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクトシーンに戻れるようにした</t>
+    <rPh sb="12" eb="13">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つぎは、魚のボスをする</t>
+    <rPh sb="4" eb="5">
+      <t>サカナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6283,7 +6297,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C279"/>
+  <dimension ref="B2:C281"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7739,6 +7753,19 @@
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C279" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B280" s="9">
+        <v>46019</v>
+      </c>
+      <c r="C280" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C281" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B77DAC-36B5-4D70-BF75-1D998C359B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9E65A4-FC76-474D-A390-478AF2DDD75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8055" yWindow="4320" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="377">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4632,6 +4632,35 @@
     <t>つぎは、魚のボスをする</t>
     <rPh sb="4" eb="5">
       <t>サカナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→魚を3,4体でてきて、歩いて、できるようにする</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さかなの合体の画像を作った</t>
+    <rPh sb="4" eb="6">
+      <t>ガッタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6297,7 +6326,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C281"/>
+  <dimension ref="B2:C283"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7766,6 +7795,19 @@
     <row r="281" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C281" t="s">
         <v>374</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B282" s="9">
+        <v>46020</v>
+      </c>
+      <c r="C282" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C283" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9E65A4-FC76-474D-A390-478AF2DDD75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71BE71B-A596-4317-A6D7-D6B07C5A62BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8055" yWindow="4320" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="381">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4661,6 +4661,73 @@
     </rPh>
     <rPh sb="10" eb="11">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤はそのまま、走る、緑はいって、ちょっと戻ってくる、青はジャンプする</t>
+    <rPh sb="0" eb="1">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミドリ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→魚を3,4体でてきて、歩いて、できるようにする←達成</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>タッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それぞれの挙動は完成</t>
+    <rPh sb="5" eb="7">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、一体倒したら、次のやつが出てきて、、、っていうループを完成させる</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>イッタイタオ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6326,7 +6393,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C283"/>
+  <dimension ref="B2:C287"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7808,6 +7875,29 @@
     <row r="283" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C283" t="s">
         <v>376</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B284" s="9">
+        <v>46021</v>
+      </c>
+      <c r="C284" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C285" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C286" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C287" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71BE71B-A596-4317-A6D7-D6B07C5A62BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A075BED0-1804-4BCA-A840-9FFEB7F7BBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8055" yWindow="4320" windowWidth="22170" windowHeight="11595" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="385">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4728,6 +4728,49 @@
     </rPh>
     <rPh sb="30" eb="32">
       <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今日の目標→このゲームループを完成させる</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームループを完成</t>
+    <rPh sb="7" eb="9">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、死ぬアニメーションをしてから</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後、魚に体力いるかも</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6393,7 +6436,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C287"/>
+  <dimension ref="B2:C291"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7898,6 +7941,29 @@
     <row r="287" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C287" t="s">
         <v>380</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B288" s="9">
+        <v>46022</v>
+      </c>
+      <c r="C288" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="289" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C289" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="290" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C290" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="291" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C291" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A075BED0-1804-4BCA-A840-9FFEB7F7BBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A12ED94-A9FC-4057-BAE7-F3006114F42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="388">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4771,6 +4771,57 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの無敵時間の描画やシステムの関係を完了</t>
+    <rPh sb="6" eb="8">
+      <t>ムテキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス出現までのループを完成</t>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後は、上の二つと、合体させる演出を考える</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガッタイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カンガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6436,7 +6487,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C291"/>
+  <dimension ref="B2:C294"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -7596,7 +7647,7 @@
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C225" s="16" t="s">
+      <c r="C225" s="15" t="s">
         <v>305</v>
       </c>
     </row>
@@ -7702,7 +7753,7 @@
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C245" s="14" t="s">
+      <c r="C245" s="15" t="s">
         <v>329</v>
       </c>
     </row>
@@ -7957,13 +8008,28 @@
       </c>
     </row>
     <row r="290" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C290" t="s">
+      <c r="C290" s="14" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="291" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C291" t="s">
+      <c r="C291" s="14" t="s">
         <v>384</v>
+      </c>
+    </row>
+    <row r="292" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C292" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="293" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C293" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="294" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C294" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A12ED94-A9FC-4057-BAE7-F3006114F42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732A919D-D8D7-4C1B-9441-4C24BB435094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="390">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4822,6 +4822,38 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爆散のアニメーション一回目の途中</t>
+    <rPh sb="0" eb="2">
+      <t>バクサン</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>イッカイメ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→今日で子のボスの挙動全部終わらせる</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ゼンブオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6487,7 +6519,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C294"/>
+  <dimension ref="B2:C296"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -8002,34 +8034,47 @@
         <v>381</v>
       </c>
     </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="289" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C289" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="290" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C290" s="14" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="291" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C291" s="14" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="292" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C292" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="293" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="293" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C293" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="294" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C294" t="s">
         <v>387</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B295" s="9">
+        <v>46024</v>
+      </c>
+      <c r="C295" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C296" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732A919D-D8D7-4C1B-9441-4C24BB435094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D438479C-F42F-4A44-BC88-81FA91DCF18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="395">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4854,6 +4854,65 @@
     </rPh>
     <rPh sb="13" eb="16">
       <t>ゼンブオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後は、合体するところの演出のみ</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガッタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスほぼ完成</t>
+    <rPh sb="4" eb="6">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後は、当たり判定系列</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ケイレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初の出現のうんぬんかんぬんはあとででいい</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュツゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合体したやつの挙動を加える</t>
+    <rPh sb="0" eb="2">
+      <t>ガッタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>クワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6519,7 +6578,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C296"/>
+  <dimension ref="B2:C301"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -8075,6 +8134,31 @@
     <row r="296" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C296" t="s">
         <v>389</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C297" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C298" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C299" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C300" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C301" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D438479C-F42F-4A44-BC88-81FA91DCF18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4108A4E-681E-4C5F-89B1-7F5A1211620D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="398">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4915,6 +4915,38 @@
       <t>クワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合体したやつの挙動を完成</t>
+    <rPh sb="0" eb="2">
+      <t>ガッタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ステージセレクトのだんだん解放だったり、音をつけたり、エフェクトの仕上げ、</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カイホウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オープニングとゲームオーバーの仕上げ</t>
   </si>
 </sst>
 </file>
@@ -6578,7 +6610,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C301"/>
+  <dimension ref="B2:C304"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -8159,6 +8191,24 @@
     <row r="301" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C301" t="s">
         <v>394</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B302" s="9">
+        <v>46025</v>
+      </c>
+      <c r="C302" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C303" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C304" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4108A4E-681E-4C5F-89B1-7F5A1211620D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22FF61F-F915-47FF-82D3-3A31B5587A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="420">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4947,6 +4947,178 @@
   </si>
   <si>
     <t>オープニングとゲームオーバーの仕上げ</t>
+  </si>
+  <si>
+    <t>残りのやること</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音管理をつくる</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音をつくる</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクトを追加していく</t>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚のキャラの当たり判定をする</t>
+    <rPh sb="0" eb="1">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・タイトルシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音をつける</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像差し替え</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>映画のようなアニメーション切り替え</t>
+    <rPh sb="0" eb="2">
+      <t>エイガ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴールシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>細部化までする</t>
+    <rPh sb="0" eb="3">
+      <t>サイブカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GOALフォントをつける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像の差し替え</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景差し替え</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップをつくる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームおーばシーンをつくる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプション画面を細部化</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>サイブカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・すべてのシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵配置</t>
+    <rPh sb="0" eb="3">
+      <t>テキハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスのhpのUI表示</t>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先順位</t>
+    <rPh sb="0" eb="2">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジュンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -8390,9 +8562,144 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51BAFBE-B9D5-4C2F-AE01-E8A667EC2E24}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:C29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="25.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B2" s="9">
+        <v>46026</v>
+      </c>
+      <c r="C2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C8" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C15" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C17" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C18" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C19" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C21" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C27" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C29" t="s">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22FF61F-F915-47FF-82D3-3A31B5587A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B94619-0A9E-499E-BB5E-A3561A199B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="421">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4980,19 +4980,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>魚のキャラの当たり判定をする</t>
-    <rPh sb="0" eb="1">
-      <t>サカナ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・ゲームシーン</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -5117,6 +5104,20 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ジュンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1終了</t>
+    <rPh sb="1" eb="3">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【終わったこと】</t>
+    <rPh sb="1" eb="2">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8562,15 +8563,24 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51BAFBE-B9D5-4C2F-AE01-E8A667EC2E24}">
-  <dimension ref="A2:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" t="s">
+        <v>419</v>
+      </c>
+    </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B2" s="9">
         <v>46026</v>
@@ -8581,7 +8591,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -8590,61 +8600,58 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>402</v>
+      <c r="C5" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C7" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C8" t="s">
-        <v>418</v>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>4</v>
-      </c>
       <c r="C11" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C16" t="s">
         <v>407</v>
       </c>
     </row>
@@ -8668,34 +8675,29 @@
         <v>411</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C21" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22">
         <v>2</v>
       </c>
-      <c r="C23" s="17" t="s">
-        <v>414</v>
+      <c r="C22" s="17" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C26" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>5</v>
+      </c>
       <c r="C27" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28">
-        <v>5</v>
-      </c>
       <c r="C28" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C29" t="s">
         <v>400</v>
       </c>
     </row>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B94619-0A9E-499E-BB5E-A3561A199B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83717B9-2BD1-4EDB-9187-408EF643783B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -5066,10 +5066,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゲームおーばシーンをつくる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>オプション画面を細部化</t>
     <rPh sb="5" eb="7">
       <t>ガメン</t>
@@ -5118,6 +5114,16 @@
     <t>【終わったこと】</t>
     <rPh sb="1" eb="2">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームおーばシーンを細部まで作る</t>
+    <rPh sb="11" eb="13">
+      <t>サイブ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8572,15 +8578,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B2" s="9">
         <v>46026</v>
@@ -8606,12 +8612,12 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
@@ -8627,7 +8633,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -8680,12 +8686,12 @@
         <v>2</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83717B9-2BD1-4EDB-9187-408EF643783B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E586A7-94AB-408F-94AA-9BA01D2B803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2760" yWindow="-14175" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="423">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5124,6 +5124,26 @@
     </rPh>
     <rPh sb="15" eb="16">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを消えるようにする</t>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚のhpは全体で共通にする</t>
+    <rPh sb="0" eb="1">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キョウツウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8569,14 +8589,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51BAFBE-B9D5-4C2F-AE01-E8A667EC2E24}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="25.75" customWidth="1"/>
+    <col min="3" max="3" width="34.625" customWidth="1"/>
+    <col min="4" max="4" width="37.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
         <v>419</v>
       </c>
@@ -8584,7 +8605,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>417</v>
       </c>
@@ -8595,115 +8616,126 @@
         <v>398</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>1</v>
+      </c>
       <c r="C7" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9">
+      <c r="D7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C11" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C13" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C14" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C15" t="s">
         <v>406</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C16" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C18" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C19" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C21" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23">
         <v>2</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C23" s="17" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C26" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C27" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28">
         <v>5</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C28" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C29" t="s">
         <v>400</v>
       </c>
     </row>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E586A7-94AB-408F-94AA-9BA01D2B803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A3C386-8184-4D5B-A259-31BFA0834A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="-14175" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="424">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5144,6 +5144,16 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>キョウツウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後、ステージ2個分</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コブン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8659,6 +8669,9 @@
       <c r="C10" t="s">
         <v>412</v>
       </c>
+      <c r="D10" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A3C386-8184-4D5B-A259-31BFA0834A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F9DE3C-4E37-4FAA-84FE-12AC68DC3647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8400" yWindow="3360" windowWidth="22170" windowHeight="12195" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-24180" yWindow="3225" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="427">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5154,6 +5154,39 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>コブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚のhpの実装を完了</t>
+    <rPh sb="0" eb="1">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを消えるようにした</t>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムが出た時にちょっと上がるようにした</t>
+    <rPh sb="5" eb="6">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6819,7 +6852,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C304"/>
+  <dimension ref="B2:C307"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -8418,6 +8451,27 @@
     <row r="304" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C304" t="s">
         <v>397</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B305" s="9">
+        <v>46028</v>
+      </c>
+      <c r="C305" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B306" s="9">
+        <v>46029</v>
+      </c>
+      <c r="C306" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C307" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F9DE3C-4E37-4FAA-84FE-12AC68DC3647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1020B90-0A21-41CF-8F59-FC57A8EA86F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24180" yWindow="3225" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="8040" yWindow="4470" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="429">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5104,13 +5104,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1終了</t>
-    <rPh sb="1" eb="3">
-      <t>シュウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【終わったこと】</t>
     <rPh sb="1" eb="2">
       <t>オ</t>
@@ -5187,6 +5180,39 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイ映像を流す</t>
+    <rPh sb="3" eb="5">
+      <t>エイゾウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚の攻撃ヒット後のヒットバック</t>
+    <rPh sb="0" eb="1">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバーシーンを大まかに作った</t>
+    <rPh sb="11" eb="12">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6852,7 +6878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C307"/>
+  <dimension ref="B2:C308"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -8458,7 +8484,7 @@
         <v>46028</v>
       </c>
       <c r="C305" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="306" spans="2:3" x14ac:dyDescent="0.4">
@@ -8466,12 +8492,20 @@
         <v>46029</v>
       </c>
       <c r="C306" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="307" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C307" t="s">
-        <v>426</v>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B308" s="9">
+        <v>46031</v>
+      </c>
+      <c r="C308" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -8653,7 +8687,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51BAFBE-B9D5-4C2F-AE01-E8A667EC2E24}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
@@ -8663,9 +8697,6 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C1" t="s">
         <v>418</v>
       </c>
     </row>
@@ -8686,123 +8717,146 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="C4" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>2</v>
+      </c>
       <c r="C5" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
       <c r="C6" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C8" t="s">
         <v>416</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>1.5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C10" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C11" t="s">
+        <v>412</v>
+      </c>
+      <c r="D11" t="s">
         <v>422</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C9" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>412</v>
-      </c>
-      <c r="D10" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C13" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C14" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C15" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C16" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C17" t="s">
-        <v>407</v>
+      <c r="D16" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C18" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C19" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
         <v>409</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C20" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C21" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C22" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23">
-        <v>2</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C27" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C28" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29">
         <v>5</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C29" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C30" t="s">
         <v>400</v>
       </c>
     </row>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1020B90-0A21-41CF-8F59-FC57A8EA86F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEE48A8-E0C3-42E7-AE68-3827B331DDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8040" yWindow="4470" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="448">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -4980,14 +4981,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゲームシーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・タイトルシーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>音をつける</t>
     <rPh sb="0" eb="1">
       <t>オト</t>
@@ -5021,10 +5014,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゴールシーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>細部化までする</t>
     <rPh sb="0" eb="3">
       <t>サイブカ</t>
@@ -5076,10 +5065,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・すべてのシーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>敵配置</t>
     <rPh sb="0" eb="3">
       <t>テキハイチ</t>
@@ -5141,16 +5126,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>後、ステージ2個分</t>
-    <rPh sb="0" eb="1">
-      <t>アト</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>魚のhpの実装を完了</t>
     <rPh sb="0" eb="1">
       <t>サカナ</t>
@@ -5213,6 +5188,207 @@
     </rPh>
     <rPh sb="15" eb="16">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーマルの攻撃エフェクト、敵のやられたときのエフェクト</t>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバーシーンの文字</t>
+    <rPh sb="11" eb="13">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドア、変身のUi,変身のカード、残機,playerとbossの文字,hpの枠</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ザンキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ワク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・【ステージセレクトシーン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドア付近の華やかさ</t>
+    <rPh sb="2" eb="4">
+      <t>フキン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セレクトシーンのマップ（原作を再現）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ポーズシーン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像のサイズ感などの調整、画像を用意</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変身についての豆知識、音マネジメントのオプション</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>マメチシキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【タイトルシーン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ゲームオーバーシーン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ゲームシーン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【すべてにおいて】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの攻撃にも</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後、ステージ2個分←後回し</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コブン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>アトマワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←完了</t>
+    <rPh sb="1" eb="3">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ゴールシーン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中村先生の授業で同時進行</t>
+    <rPh sb="0" eb="4">
+      <t>ナカムラセンセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジュギョウ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ドウジシンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pressAnybutton</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタン押したらタイトルが出てくるように</t>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームおーばは三機にする</t>
+    <rPh sb="7" eb="9">
+      <t>サンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェードを真っ黒にして数秒待ってから表示する</t>
+    <rPh sb="5" eb="6">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>スウビョウマ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ、フェード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大砲、看板の文字フォント</t>
+    <rPh sb="3" eb="5">
+      <t>カンバン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5372,7 +5548,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5425,6 +5601,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6882,7 +7061,7 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.625" customWidth="1"/>
+    <col min="3" max="3" width="87.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
@@ -8484,7 +8663,7 @@
         <v>46028</v>
       </c>
       <c r="C305" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="306" spans="2:3" x14ac:dyDescent="0.4">
@@ -8492,12 +8671,12 @@
         <v>46029</v>
       </c>
       <c r="C306" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="307" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C307" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="308" spans="2:3" x14ac:dyDescent="0.4">
@@ -8505,7 +8684,7 @@
         <v>46031</v>
       </c>
       <c r="C308" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -8687,22 +8866,24 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51BAFBE-B9D5-4C2F-AE01-E8A667EC2E24}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
+    <col min="3" max="3" width="50.5" customWidth="1"/>
     <col min="4" max="4" width="37.125" customWidth="1"/>
+    <col min="5" max="5" width="57" customWidth="1"/>
+    <col min="6" max="6" width="50.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B2" s="9">
         <v>46026</v>
@@ -8711,153 +8892,257 @@
         <v>398</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C3" s="18" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>407</v>
+      </c>
+      <c r="E7" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>412</v>
+      </c>
+      <c r="D10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>416</v>
+      </c>
+      <c r="D12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>409</v>
+      </c>
+      <c r="D13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C15" s="18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>1.5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>403</v>
+      </c>
+      <c r="E16" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C17" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C8" t="s">
-        <v>416</v>
-      </c>
-      <c r="D8" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C18" t="s">
+        <v>404</v>
+      </c>
+      <c r="D18" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <v>1.5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C10" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C11" t="s">
-        <v>412</v>
-      </c>
-      <c r="D11" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C12" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C13" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C19" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C21" s="18" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C22" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A15">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C16" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
         <v>406</v>
       </c>
-      <c r="D16" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C18" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>7</v>
-      </c>
-      <c r="C19" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>8</v>
-      </c>
-      <c r="C20" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C21" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C22" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C28" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29">
-        <v>5</v>
-      </c>
+      <c r="C24" t="s">
+        <v>407</v>
+      </c>
+      <c r="E24" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C25" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C26" s="18" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="E27" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C28" s="18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
+        <v>446</v>
+      </c>
+      <c r="E29" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>403</v>
+      </c>
+      <c r="E30" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C31" s="18" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C32" t="s">
+        <v>431</v>
+      </c>
+      <c r="E32" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C33" s="18" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C30" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
         <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043CC552-7D3A-4DC6-8319-C35A74AECC01}">
+  <dimension ref="B1:D4"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="48.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D4" t="s">
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEE48A8-E0C3-42E7-AE68-3827B331DDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F60F1E-FBE7-415C-9D89-65106921BBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-27885" yWindow="3165" windowWidth="22170" windowHeight="12195" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F60F1E-FBE7-415C-9D89-65106921BBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C34F9F-F8E9-4158-9151-6C58B2044E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27885" yWindow="3165" windowWidth="22170" windowHeight="12195" activeTab="5" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="455">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5389,6 +5389,85 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーニングのUI完了、</t>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後は、ノーマル、弓のUI</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ユミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムにしたら変だったので、カードはUiだけにして、アイテムは別の画像を探す</t>
+    <rPh sb="8" eb="9">
+      <t>ヘン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変身のカード</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残機完了</t>
+    <rPh sb="0" eb="2">
+      <t>ザンキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三種完了、ノーマルも完了</t>
+    <rPh sb="0" eb="2">
+      <t>サンシュ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hpバー、残機、カードのUIを終わらせて、音マネージャーを作った</t>
+    <rPh sb="5" eb="7">
+      <t>ザンキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7057,7 +7136,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C308"/>
+  <dimension ref="B2:C312"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -8685,6 +8764,32 @@
       </c>
       <c r="C308" t="s">
         <v>423</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B309" s="9">
+        <v>46032</v>
+      </c>
+      <c r="C309" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C310" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C311" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="312" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B312" s="9">
+        <v>46033</v>
+      </c>
+      <c r="C312" t="s">
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -8866,7 +8971,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51BAFBE-B9D5-4C2F-AE01-E8A667EC2E24}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
@@ -8921,105 +9026,108 @@
       <c r="E7" t="s">
         <v>426</v>
       </c>
+      <c r="F7" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8">
+      <c r="E8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F8" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B10" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
         <v>82</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>412</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12">
         <v>3</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>422</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C12" t="s">
-        <v>416</v>
-      </c>
-      <c r="D12" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C13" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
+        <v>409</v>
+      </c>
+      <c r="D14" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C15" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C15" s="18" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C16" s="18" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17">
         <v>1.5</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>403</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>441</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C17" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C18" t="s">
-        <v>404</v>
-      </c>
-      <c r="D18" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C19" t="s">
+        <v>404</v>
+      </c>
+      <c r="D19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C20" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C21" s="18" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C22" s="18" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C22" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C23" t="s">
         <v>405</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.4">
@@ -9027,88 +9135,96 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>407</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C25" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C26" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C26" s="18" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C27" s="18" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B27" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C28" s="17" t="s">
         <v>415</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C28" s="18" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C29" s="18" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C29" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C30" t="s">
         <v>446</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A30">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31">
         <v>1</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>403</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C31" s="18" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C32" s="18" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C32" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C33" t="s">
         <v>431</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C33" s="18" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C34" s="18" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
         <v>400</v>
       </c>
     </row>
@@ -9120,19 +9236,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043CC552-7D3A-4DC6-8319-C35A74AECC01}">
-  <dimension ref="B1:D4"/>
+  <dimension ref="B1:E4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="4" max="4" width="48.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D1" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>29</v>
       </c>
@@ -9140,7 +9259,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D4" t="s">
         <v>445</v>
       </c>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C34F9F-F8E9-4158-9151-6C58B2044E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C97045-9C63-45F3-93FA-B77061E6B5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,9 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId7"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="509">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5468,6 +5470,369 @@
     </rPh>
     <rPh sb="29" eb="30">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標→音、エフェクトを順次追加</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュンジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>タスク名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開始日</t>
+    <rPh sb="0" eb="3">
+      <t>カイシビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終了日</t>
+    <rPh sb="0" eb="3">
+      <t>シュウリョウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先度</t>
+    <rPh sb="0" eb="3">
+      <t>ユウセンド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進捗状況</t>
+    <rPh sb="0" eb="2">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>列1</t>
+  </si>
+  <si>
+    <t>列2</t>
+  </si>
+  <si>
+    <t>列3</t>
+  </si>
+  <si>
+    <t>列4</t>
+  </si>
+  <si>
+    <t>列5</t>
+  </si>
+  <si>
+    <t>未完了</t>
+  </si>
+  <si>
+    <t>タスク1</t>
+  </si>
+  <si>
+    <t>タスク2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エクセル練習</t>
+    <rPh sb="4" eb="6">
+      <t>レンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク名(親)</t>
+    <rPh sb="5" eb="6">
+      <t>オヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク名(子)</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先順位</t>
+    <rPh sb="0" eb="4">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進捗度合い</t>
+    <rPh sb="0" eb="4">
+      <t>シンチョクドア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PressAnyButton</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未着手</t>
+  </si>
+  <si>
+    <t>スキップ昨日の追加</t>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像の差しかえ</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーマルの斬撃</t>
+    <rPh sb="5" eb="7">
+      <t>ザンゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フローズンのエフェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢が見ずらいので修正</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のやられ演出</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの攻撃</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変身のUI</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hpの枠</t>
+    <rPh sb="3" eb="4">
+      <t>ワク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスのヒットバック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ作成</t>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加のステージ作成</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進行中</t>
+  </si>
+  <si>
+    <t>【ステージセレクトシーン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入ったドアから出るようにする</t>
+    <rPh sb="0" eb="1">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドアにわかりやすく数字を乗っける</t>
+    <rPh sb="9" eb="11">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何か見栄えをよくする</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ミバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴール後の報酬(hpを増やす等)</t>
+    <rPh sb="3" eb="4">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大砲</t>
+    <rPh sb="0" eb="2">
+      <t>タイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>看板の文字</t>
+    <rPh sb="0" eb="2">
+      <t>カンバン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像差し替え</t>
+    <rPh sb="0" eb="3">
+      <t>ガゾウサ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GAMEOVERの文字</t>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GOALの文字</t>
+    <rPh sb="5" eb="7">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェードを対応する</t>
+    <rPh sb="5" eb="7">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>持ってくるだけ</t>
+    <rPh sb="0" eb="1">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの攻撃にカメラを揺らすようにする</t>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ユ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5700,6 +6065,52 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G38" totalsRowShown="0">
+  <autoFilter ref="C2:G38" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="高"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="進行中"/>
+        <filter val="未着手"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{AEEE3D2C-A18A-41D8-9661-9EDBA523BEE2}" name="列1"/>
+    <tableColumn id="2" xr3:uid="{37E0AAF8-D097-4400-971D-4F6F6B236A7B}" name="列2"/>
+    <tableColumn id="3" xr3:uid="{E928A0C4-0CC9-47D2-A61A-91CB8DF54FA2}" name="列3"/>
+    <tableColumn id="4" xr3:uid="{E3E4E73E-6900-4BFD-A32F-57FFF716B0BB}" name="列4"/>
+    <tableColumn id="5" xr3:uid="{36F84575-9D8B-4C25-871E-CEAF326E01E2}" name="列5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5814694B-B1B0-4655-8275-CA9217E4D27F}" name="テーブル3" displayName="テーブル3" ref="B2:F4" totalsRowShown="0">
+  <autoFilter ref="B2:F4" xr:uid="{5814694B-B1B0-4655-8275-CA9217E4D27F}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="低"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{FE95F1C6-D62A-4D9A-983F-333BB81F8841}" name="タスク名"/>
+    <tableColumn id="2" xr3:uid="{9867DE28-00FB-4030-9AAB-6BE2A0ABE7D6}" name="開始日"/>
+    <tableColumn id="3" xr3:uid="{77D16931-2E3B-46D1-9B35-95A897EAE8A7}" name="終了日"/>
+    <tableColumn id="4" xr3:uid="{0626C141-E220-40EF-93A6-61507D10D1BD}" name="優先度"/>
+    <tableColumn id="5" xr3:uid="{BCEAD21F-F4A7-4F8E-8A6F-3A1AE5008041}" name="進捗状況"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7136,7 +7547,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C312"/>
+  <dimension ref="B2:C313"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -8786,10 +9197,18 @@
     </row>
     <row r="312" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B312" s="9">
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="C312" t="s">
         <v>454</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B313" s="9">
+        <v>46035</v>
+      </c>
+      <c r="C313" t="s">
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -9009,11 +9428,19 @@
       <c r="C5" t="s">
         <v>401</v>
       </c>
+      <c r="D5" t="s">
+        <v>458</v>
+      </c>
       <c r="E5" t="s">
         <v>424</v>
       </c>
       <c r="F5" t="s">
         <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D6" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
@@ -9230,11 +9657,521 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D6" xr:uid="{F9CEBFA8-001B-4940-8B28-535DD42B1EDD}">
+      <formula1>"高,中,低"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
+  <dimension ref="C2:G38"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="33.5" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="5" max="5" width="32.125" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F2" t="s">
+        <v>467</v>
+      </c>
+      <c r="G2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E3" t="s">
+        <v>474</v>
+      </c>
+      <c r="F3" t="s">
+        <v>475</v>
+      </c>
+      <c r="G3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="4" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F4" t="s">
+        <v>456</v>
+      </c>
+      <c r="G4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>421</v>
+      </c>
+      <c r="F5" t="s">
+        <v>458</v>
+      </c>
+      <c r="G5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>480</v>
+      </c>
+      <c r="F6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G6" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C7" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>482</v>
+      </c>
+      <c r="F7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F8" t="s">
+        <v>456</v>
+      </c>
+      <c r="G8" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>484</v>
+      </c>
+      <c r="F9" t="s">
+        <v>457</v>
+      </c>
+      <c r="G9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>485</v>
+      </c>
+      <c r="F10" t="s">
+        <v>456</v>
+      </c>
+      <c r="G10" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>486</v>
+      </c>
+      <c r="F11" t="s">
+        <v>457</v>
+      </c>
+      <c r="G11" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D12" t="s">
+        <v>481</v>
+      </c>
+      <c r="E12" t="s">
+        <v>487</v>
+      </c>
+      <c r="F12" t="s">
+        <v>457</v>
+      </c>
+      <c r="G12" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D13" t="s">
+        <v>481</v>
+      </c>
+      <c r="E13" t="s">
+        <v>488</v>
+      </c>
+      <c r="F13" t="s">
+        <v>456</v>
+      </c>
+      <c r="G13" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D14" t="s">
+        <v>481</v>
+      </c>
+      <c r="E14" t="s">
+        <v>489</v>
+      </c>
+      <c r="F14" t="s">
+        <v>456</v>
+      </c>
+      <c r="G14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D15" t="s">
+        <v>508</v>
+      </c>
+      <c r="F15" t="s">
+        <v>456</v>
+      </c>
+      <c r="G15" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D16" t="s">
+        <v>490</v>
+      </c>
+      <c r="F16" t="s">
+        <v>456</v>
+      </c>
+      <c r="G16" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D17" t="s">
+        <v>492</v>
+      </c>
+      <c r="F17" t="s">
+        <v>458</v>
+      </c>
+      <c r="G17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D18" t="s">
+        <v>503</v>
+      </c>
+      <c r="F18" t="s">
+        <v>456</v>
+      </c>
+      <c r="G18" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D19" t="s">
+        <v>504</v>
+      </c>
+      <c r="F19" t="s">
+        <v>456</v>
+      </c>
+      <c r="G19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C20" t="s">
+        <v>494</v>
+      </c>
+      <c r="D20" t="s">
+        <v>491</v>
+      </c>
+      <c r="F20" t="s">
+        <v>456</v>
+      </c>
+      <c r="G20" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D21" t="s">
+        <v>407</v>
+      </c>
+      <c r="E21" t="s">
+        <v>487</v>
+      </c>
+      <c r="F21" t="s">
+        <v>456</v>
+      </c>
+      <c r="G21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D22" t="s">
+        <v>495</v>
+      </c>
+      <c r="F22" t="s">
+        <v>458</v>
+      </c>
+      <c r="G22" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D23" t="s">
+        <v>496</v>
+      </c>
+      <c r="F23" t="s">
+        <v>456</v>
+      </c>
+      <c r="G23" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D24" t="s">
+        <v>503</v>
+      </c>
+      <c r="F24" t="s">
+        <v>456</v>
+      </c>
+      <c r="G24" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D25" t="s">
+        <v>504</v>
+      </c>
+      <c r="F25" t="s">
+        <v>456</v>
+      </c>
+      <c r="G25" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C26" t="s">
+        <v>440</v>
+      </c>
+      <c r="D26" t="s">
+        <v>497</v>
+      </c>
+      <c r="F26" t="s">
+        <v>456</v>
+      </c>
+      <c r="G26" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="27" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D27" t="s">
+        <v>498</v>
+      </c>
+      <c r="F27" t="s">
+        <v>456</v>
+      </c>
+      <c r="G27" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D28" t="s">
+        <v>506</v>
+      </c>
+      <c r="E28" t="s">
+        <v>507</v>
+      </c>
+      <c r="F28" t="s">
+        <v>456</v>
+      </c>
+      <c r="G28" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D29" t="s">
+        <v>407</v>
+      </c>
+      <c r="E29" t="s">
+        <v>499</v>
+      </c>
+      <c r="F29" t="s">
+        <v>456</v>
+      </c>
+      <c r="G29" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="30" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D30" t="s">
+        <v>407</v>
+      </c>
+      <c r="E30" t="s">
+        <v>500</v>
+      </c>
+      <c r="F30" t="s">
+        <v>456</v>
+      </c>
+      <c r="G30" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="31" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D31" t="s">
+        <v>407</v>
+      </c>
+      <c r="E31" t="s">
+        <v>505</v>
+      </c>
+      <c r="F31" t="s">
+        <v>456</v>
+      </c>
+      <c r="G31" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="32" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D32" t="s">
+        <v>408</v>
+      </c>
+      <c r="F32" t="s">
+        <v>456</v>
+      </c>
+      <c r="G32" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D33" t="s">
+        <v>503</v>
+      </c>
+      <c r="F33" t="s">
+        <v>456</v>
+      </c>
+      <c r="G33" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="34" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D34" t="s">
+        <v>504</v>
+      </c>
+      <c r="F34" t="s">
+        <v>456</v>
+      </c>
+      <c r="G34" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C35" t="s">
+        <v>434</v>
+      </c>
+      <c r="D35" t="s">
+        <v>501</v>
+      </c>
+      <c r="E35" t="s">
+        <v>502</v>
+      </c>
+      <c r="F35" t="s">
+        <v>456</v>
+      </c>
+      <c r="G35" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D36" t="s">
+        <v>503</v>
+      </c>
+      <c r="F36" t="s">
+        <v>456</v>
+      </c>
+      <c r="G36" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D37" t="s">
+        <v>504</v>
+      </c>
+      <c r="F37" t="s">
+        <v>456</v>
+      </c>
+      <c r="G37" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G37" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+      <formula1>"完了,進行中,未着手"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F37" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+      <formula1>"高,中,低"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043CC552-7D3A-4DC6-8319-C35A74AECC01}">
   <dimension ref="B1:E4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -9268,4 +10205,81 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BAAB0F-3A46-421A-8FF2-23EA3AC6BEF8}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="17.625" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="22.625" customWidth="1"/>
+    <col min="6" max="6" width="19.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>470</v>
+      </c>
+      <c r="E3" t="s">
+        <v>458</v>
+      </c>
+      <c r="F3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>471</v>
+      </c>
+      <c r="E4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4" xr:uid="{B5A4B4FB-EA43-42D8-A5BD-89B48D5F38A7}">
+      <formula1>"タスク1,タスク2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E4" xr:uid="{2F18CB7E-504E-4A33-A61C-04E992926A3B}">
+      <formula1>"高,中,低"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F4" xr:uid="{547CA2C8-732B-457A-B17C-8502248092C2}">
+      <formula1>"完了,未完了"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C97045-9C63-45F3-93FA-B77061E6B5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D2ABD0-51E2-4682-922E-E4023EF45A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5940" yWindow="1695" windowWidth="22170" windowHeight="12195" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6078,7 +6078,6 @@
     <filterColumn colId="4">
       <filters>
         <filter val="進行中"/>
-        <filter val="未着手"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9713,7 +9712,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>433</v>
       </c>
@@ -9772,10 +9771,10 @@
         <v>456</v>
       </c>
       <c r="G7" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D8" t="s">
         <v>3</v>
       </c>
@@ -9845,7 +9844,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
         <v>481</v>
       </c>
@@ -9873,7 +9872,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
         <v>508</v>
       </c>
@@ -9884,7 +9883,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D16" t="s">
         <v>490</v>
       </c>
@@ -9906,7 +9905,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D18" t="s">
         <v>503</v>
       </c>
@@ -9917,7 +9916,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
         <v>504</v>
       </c>
@@ -9928,7 +9927,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>494</v>
       </c>
@@ -9942,7 +9941,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
         <v>407</v>
       </c>
@@ -9967,7 +9966,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D23" t="s">
         <v>496</v>
       </c>
@@ -9978,7 +9977,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D24" t="s">
         <v>503</v>
       </c>
@@ -9989,7 +9988,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D25" t="s">
         <v>504</v>
       </c>
@@ -10000,7 +9999,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
         <v>440</v>
       </c>
@@ -10014,7 +10013,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D27" t="s">
         <v>498</v>
       </c>
@@ -10025,7 +10024,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D28" t="s">
         <v>506</v>
       </c>
@@ -10039,7 +10038,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D29" t="s">
         <v>407</v>
       </c>
@@ -10053,7 +10052,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D30" t="s">
         <v>407</v>
       </c>
@@ -10067,7 +10066,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D31" t="s">
         <v>407</v>
       </c>
@@ -10081,7 +10080,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D32" t="s">
         <v>408</v>
       </c>
@@ -10092,7 +10091,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D33" t="s">
         <v>503</v>
       </c>
@@ -10103,7 +10102,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D34" t="s">
         <v>504</v>
       </c>
@@ -10114,7 +10113,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
         <v>434</v>
       </c>
@@ -10131,7 +10130,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D36" t="s">
         <v>503</v>
       </c>
@@ -10142,7 +10141,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D37" t="s">
         <v>504</v>
       </c>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D2ABD0-51E2-4682-922E-E4023EF45A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B53FC9-982F-4726-A6A7-ED157A4E2B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="1695" windowWidth="22170" windowHeight="12195" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-27000" yWindow="3795" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="511">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5833,6 +5833,23 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>ユ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージとカメラとの関係性</t>
+    <rPh sb="10" eb="12">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクトのマップ完成</t>
+    <rPh sb="12" eb="14">
+      <t>カンセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6068,8 +6085,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G38" totalsRowShown="0">
-  <autoFilter ref="C2:G38" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G39" totalsRowShown="0">
+  <autoFilter ref="C2:G39" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
     <filterColumn colId="3">
       <filters>
         <filter val="高"/>
@@ -7546,7 +7563,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C313"/>
+  <dimension ref="B2:C314"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -9208,6 +9225,14 @@
       </c>
       <c r="C313" t="s">
         <v>455</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B314" s="9">
+        <v>46036</v>
+      </c>
+      <c r="C314" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -9668,7 +9693,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G38"/>
+  <dimension ref="C2:G39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
@@ -9757,7 +9782,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C7" t="s">
         <v>435</v>
       </c>
@@ -9938,40 +9963,40 @@
         <v>456</v>
       </c>
       <c r="G20" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
-        <v>407</v>
-      </c>
-      <c r="E21" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="F21" t="s">
         <v>456</v>
       </c>
       <c r="G21" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="22" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" x14ac:dyDescent="0.4">
       <c r="D22" t="s">
-        <v>495</v>
+        <v>407</v>
+      </c>
+      <c r="E22" t="s">
+        <v>487</v>
       </c>
       <c r="F22" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
     </row>
     <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D23" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F23" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G23" t="s">
         <v>479</v>
@@ -9979,7 +10004,7 @@
     </row>
     <row r="24" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D24" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="F24" t="s">
         <v>456</v>
@@ -9990,7 +10015,7 @@
     </row>
     <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D25" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F25" t="s">
         <v>456</v>
@@ -10000,11 +10025,8 @@
       </c>
     </row>
     <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="C26" t="s">
-        <v>440</v>
-      </c>
       <c r="D26" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F26" t="s">
         <v>456</v>
@@ -10014,8 +10036,11 @@
       </c>
     </row>
     <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C27" t="s">
+        <v>440</v>
+      </c>
       <c r="D27" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F27" t="s">
         <v>456</v>
@@ -10026,10 +10051,7 @@
     </row>
     <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E28" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="F28" t="s">
         <v>456</v>
@@ -10040,10 +10062,10 @@
     </row>
     <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D29" t="s">
-        <v>407</v>
+        <v>506</v>
       </c>
       <c r="E29" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="F29" t="s">
         <v>456</v>
@@ -10057,7 +10079,7 @@
         <v>407</v>
       </c>
       <c r="E30" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F30" t="s">
         <v>456</v>
@@ -10071,7 +10093,7 @@
         <v>407</v>
       </c>
       <c r="E31" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F31" t="s">
         <v>456</v>
@@ -10082,7 +10104,10 @@
     </row>
     <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D32" t="s">
-        <v>408</v>
+        <v>407</v>
+      </c>
+      <c r="E32" t="s">
+        <v>505</v>
       </c>
       <c r="F32" t="s">
         <v>456</v>
@@ -10093,7 +10118,7 @@
     </row>
     <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D33" t="s">
-        <v>503</v>
+        <v>408</v>
       </c>
       <c r="F33" t="s">
         <v>456</v>
@@ -10104,7 +10129,7 @@
     </row>
     <row r="34" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D34" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F34" t="s">
         <v>456</v>
@@ -10114,14 +10139,8 @@
       </c>
     </row>
     <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="C35" t="s">
-        <v>434</v>
-      </c>
       <c r="D35" t="s">
-        <v>501</v>
-      </c>
-      <c r="E35" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F35" t="s">
         <v>456</v>
@@ -10131,8 +10150,14 @@
       </c>
     </row>
     <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C36" t="s">
+        <v>434</v>
+      </c>
       <c r="D36" t="s">
-        <v>503</v>
+        <v>501</v>
+      </c>
+      <c r="E36" t="s">
+        <v>502</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
@@ -10143,7 +10168,7 @@
     </row>
     <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D37" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F37" t="s">
         <v>456</v>
@@ -10152,14 +10177,25 @@
         <v>479</v>
       </c>
     </row>
-    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="D38" t="s">
+        <v>504</v>
+      </c>
+      <c r="F38" t="s">
+        <v>456</v>
+      </c>
+      <c r="G38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G37" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G38" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F37" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F38" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B53FC9-982F-4726-A6A7-ED157A4E2B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF75C371-804D-40C7-B79E-06E0BDB91F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27000" yWindow="3795" windowWidth="22170" windowHeight="12195" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="14085" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="512">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5850,6 +5850,22 @@
     <t>ステージセレクトのマップ完成</t>
     <rPh sb="12" eb="14">
       <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復と変身の追加のドアを増やす</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘンシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6085,8 +6101,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G39" totalsRowShown="0">
-  <autoFilter ref="C2:G39" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G40" totalsRowShown="0">
+  <autoFilter ref="C2:G40" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
     <filterColumn colId="3">
       <filters>
         <filter val="高"/>
@@ -6095,6 +6111,7 @@
     <filterColumn colId="4">
       <filters>
         <filter val="進行中"/>
+        <filter val="未着手"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9693,7 +9710,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G39"/>
+  <dimension ref="C2:G40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
@@ -9737,7 +9754,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="4" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>433</v>
       </c>
@@ -9799,7 +9816,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C8" t="s">
+        <v>435</v>
+      </c>
       <c r="D8" t="s">
         <v>3</v>
       </c>
@@ -9828,6 +9848,9 @@
       </c>
     </row>
     <row r="10" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C10" t="s">
+        <v>435</v>
+      </c>
       <c r="D10" t="s">
         <v>3</v>
       </c>
@@ -9869,7 +9892,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="13" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>435</v>
+      </c>
       <c r="D13" t="s">
         <v>481</v>
       </c>
@@ -9884,6 +9910,9 @@
       </c>
     </row>
     <row r="14" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>435</v>
+      </c>
       <c r="D14" t="s">
         <v>481</v>
       </c>
@@ -9897,7 +9926,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C15" t="s">
+        <v>435</v>
+      </c>
       <c r="D15" t="s">
         <v>508</v>
       </c>
@@ -9905,10 +9937,13 @@
         <v>456</v>
       </c>
       <c r="G15" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="16" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C16" t="s">
+        <v>435</v>
+      </c>
       <c r="D16" t="s">
         <v>490</v>
       </c>
@@ -9930,7 +9965,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C18" t="s">
+        <v>435</v>
+      </c>
       <c r="D18" t="s">
         <v>503</v>
       </c>
@@ -9941,7 +9979,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="19" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C19" t="s">
+        <v>435</v>
+      </c>
       <c r="D19" t="s">
         <v>504</v>
       </c>
@@ -9967,6 +10008,9 @@
       </c>
     </row>
     <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C21" t="s">
+        <v>494</v>
+      </c>
       <c r="D21" t="s">
         <v>509</v>
       </c>
@@ -9977,7 +10021,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C22" t="s">
+        <v>494</v>
+      </c>
       <c r="D22" t="s">
         <v>407</v>
       </c>
@@ -9988,7 +10035,7 @@
         <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>493</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10003,6 +10050,9 @@
       </c>
     </row>
     <row r="24" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C24" t="s">
+        <v>494</v>
+      </c>
       <c r="D24" t="s">
         <v>496</v>
       </c>
@@ -10010,10 +10060,13 @@
         <v>456</v>
       </c>
       <c r="G24" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C25" t="s">
+        <v>494</v>
+      </c>
       <c r="D25" t="s">
         <v>503</v>
       </c>
@@ -10021,10 +10074,13 @@
         <v>456</v>
       </c>
       <c r="G25" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C26" t="s">
+        <v>494</v>
+      </c>
       <c r="D26" t="s">
         <v>504</v>
       </c>
@@ -10035,7 +10091,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
         <v>440</v>
       </c>
@@ -10049,7 +10105,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C28" t="s">
+        <v>440</v>
+      </c>
       <c r="D28" t="s">
         <v>498</v>
       </c>
@@ -10060,7 +10119,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C29" t="s">
+        <v>440</v>
+      </c>
       <c r="D29" t="s">
         <v>506</v>
       </c>
@@ -10074,7 +10136,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C30" t="s">
+        <v>440</v>
+      </c>
       <c r="D30" t="s">
         <v>407</v>
       </c>
@@ -10088,7 +10153,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C31" t="s">
+        <v>440</v>
+      </c>
       <c r="D31" t="s">
         <v>407</v>
       </c>
@@ -10102,7 +10170,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C32" t="s">
+        <v>440</v>
+      </c>
       <c r="D32" t="s">
         <v>407</v>
       </c>
@@ -10116,7 +10187,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C33" t="s">
+        <v>440</v>
+      </c>
       <c r="D33" t="s">
         <v>408</v>
       </c>
@@ -10127,7 +10201,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="34" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C34" t="s">
+        <v>440</v>
+      </c>
       <c r="D34" t="s">
         <v>503</v>
       </c>
@@ -10138,7 +10215,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C35" t="s">
+        <v>440</v>
+      </c>
       <c r="D35" t="s">
         <v>504</v>
       </c>
@@ -10149,7 +10229,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
         <v>434</v>
       </c>
@@ -10166,7 +10246,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C37" t="s">
+        <v>434</v>
+      </c>
       <c r="D37" t="s">
         <v>503</v>
       </c>
@@ -10177,7 +10260,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C38" t="s">
+        <v>434</v>
+      </c>
       <c r="D38" t="s">
         <v>504</v>
       </c>
@@ -10189,13 +10275,27 @@
       </c>
     </row>
     <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C40" t="s">
+        <v>494</v>
+      </c>
+      <c r="D40" t="s">
+        <v>511</v>
+      </c>
+      <c r="F40" t="s">
+        <v>457</v>
+      </c>
+      <c r="G40" t="s">
+        <v>479</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G38" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G38 G40" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F38" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F38 F40" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF75C371-804D-40C7-B79E-06E0BDB91F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2475DEA0-3E03-4C62-B128-48190F302B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="14085" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2475" yWindow="4830" windowWidth="22170" windowHeight="12195" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9714,7 +9714,7 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
-    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="4" max="4" width="39.5" customWidth="1"/>
     <col min="5" max="5" width="32.125" customWidth="1"/>
     <col min="6" max="6" width="19.25" customWidth="1"/>
     <col min="7" max="7" width="15.375" customWidth="1"/>
@@ -10063,7 +10063,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C25" t="s">
         <v>494</v>
       </c>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2475DEA0-3E03-4C62-B128-48190F302B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C53731-89B0-4D89-934D-2057B7472A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2475" yWindow="4830" windowWidth="22170" windowHeight="12195" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3720" yWindow="870" windowWidth="21600" windowHeight="14610" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C53731-89B0-4D89-934D-2057B7472A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2E7A07-26B8-48D0-9869-E75275090845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="870" windowWidth="21600" windowHeight="14610" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="765" yWindow="-12825" windowWidth="21600" windowHeight="11295" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="514">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5611,16 +5611,6 @@
     <t>未着手</t>
   </si>
   <si>
-    <t>スキップ昨日の追加</t>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>画像の差しかえ</t>
     <rPh sb="0" eb="2">
       <t>ガゾウ</t>
@@ -5866,6 +5856,27 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの波動のUI</t>
+    <rPh sb="3" eb="5">
+      <t>ハドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>barningのエフェクト(lightning)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキップ機能の追加</t>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6101,11 +6112,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G40" totalsRowShown="0">
-  <autoFilter ref="C2:G40" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
-    <filterColumn colId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G42" totalsRowShown="0">
+  <autoFilter ref="C2:G42" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+    <filterColumn colId="1">
       <filters>
-        <filter val="高"/>
+        <filter val="BGM"/>
       </filters>
     </filterColumn>
     <filterColumn colId="4">
@@ -9249,7 +9260,7 @@
         <v>46036</v>
       </c>
       <c r="C314" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -9710,7 +9721,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G40"/>
+  <dimension ref="C2:G42"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
@@ -9754,7 +9765,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>433</v>
       </c>
@@ -9768,7 +9779,7 @@
         <v>456</v>
       </c>
       <c r="G4" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -9790,7 +9801,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>480</v>
+        <v>513</v>
       </c>
       <c r="F6" t="s">
         <v>457</v>
@@ -9807,7 +9818,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F7" t="s">
         <v>456</v>
@@ -9816,7 +9827,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C8" t="s">
         <v>435</v>
       </c>
@@ -9824,7 +9835,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F8" t="s">
         <v>456</v>
@@ -9838,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F9" t="s">
         <v>457</v>
@@ -9847,7 +9858,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C10" t="s">
         <v>435</v>
       </c>
@@ -9855,35 +9866,38 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="F10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G10" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C11" t="s">
+        <v>435</v>
+      </c>
       <c r="D11" t="s">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G11" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
-        <v>481</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F12" t="s">
         <v>457</v>
@@ -9892,21 +9906,18 @@
         <v>479</v>
       </c>
     </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C13" t="s">
-        <v>435</v>
-      </c>
+    <row r="13" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F13" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G13" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -9914,80 +9925,86 @@
         <v>435</v>
       </c>
       <c r="D14" t="s">
-        <v>481</v>
+        <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>489</v>
+        <v>511</v>
       </c>
       <c r="F14" t="s">
         <v>456</v>
       </c>
       <c r="G14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.4">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
         <v>435</v>
       </c>
       <c r="D15" t="s">
-        <v>508</v>
+        <v>480</v>
+      </c>
+      <c r="E15" t="s">
+        <v>487</v>
       </c>
       <c r="F15" t="s">
         <v>456</v>
       </c>
       <c r="G15" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.4">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C16" t="s">
         <v>435</v>
       </c>
       <c r="D16" t="s">
-        <v>490</v>
+        <v>480</v>
+      </c>
+      <c r="E16" t="s">
+        <v>488</v>
       </c>
       <c r="F16" t="s">
         <v>456</v>
       </c>
       <c r="G16" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C17" t="s">
+        <v>435</v>
+      </c>
       <c r="D17" t="s">
+        <v>507</v>
+      </c>
+      <c r="F17" t="s">
+        <v>456</v>
+      </c>
+      <c r="G17" t="s">
         <v>492</v>
       </c>
-      <c r="F17" t="s">
-        <v>458</v>
-      </c>
-      <c r="G17" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C18" t="s">
         <v>435</v>
       </c>
       <c r="D18" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="F18" t="s">
         <v>456</v>
       </c>
       <c r="G18" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C19" t="s">
-        <v>435</v>
-      </c>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="F19" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G19" t="s">
         <v>479</v>
@@ -9995,10 +10012,10 @@
     </row>
     <row r="20" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="D20" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F20" t="s">
         <v>456</v>
@@ -10009,27 +10026,24 @@
     </row>
     <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C21" t="s">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F21" t="s">
         <v>456</v>
       </c>
       <c r="G21" t="s">
-        <v>101</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D22" t="s">
-        <v>407</v>
-      </c>
-      <c r="E22" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F22" t="s">
         <v>456</v>
@@ -10039,22 +10053,28 @@
       </c>
     </row>
     <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C23" t="s">
+        <v>493</v>
+      </c>
       <c r="D23" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="F23" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G23" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D24" t="s">
-        <v>496</v>
+        <v>407</v>
+      </c>
+      <c r="E24" t="s">
+        <v>486</v>
       </c>
       <c r="F24" t="s">
         <v>456</v>
@@ -10064,53 +10084,50 @@
       </c>
     </row>
     <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>494</v>
       </c>
-      <c r="D25" t="s">
-        <v>503</v>
-      </c>
       <c r="F25" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.4">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D26" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="F26" t="s">
         <v>456</v>
       </c>
       <c r="G26" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="D27" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F27" t="s">
         <v>456</v>
       </c>
       <c r="G27" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="D28" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="F28" t="s">
         <v>456</v>
@@ -10119,15 +10136,12 @@
         <v>479</v>
       </c>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
         <v>440</v>
       </c>
       <c r="D29" t="s">
-        <v>506</v>
-      </c>
-      <c r="E29" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="F29" t="s">
         <v>456</v>
@@ -10136,15 +10150,12 @@
         <v>479</v>
       </c>
     </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
         <v>440</v>
       </c>
       <c r="D30" t="s">
-        <v>407</v>
-      </c>
-      <c r="E30" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F30" t="s">
         <v>456</v>
@@ -10153,15 +10164,15 @@
         <v>479</v>
       </c>
     </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
         <v>440</v>
       </c>
       <c r="D31" t="s">
-        <v>407</v>
+        <v>505</v>
       </c>
       <c r="E31" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F31" t="s">
         <v>456</v>
@@ -10170,7 +10181,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
         <v>440</v>
       </c>
@@ -10178,7 +10189,7 @@
         <v>407</v>
       </c>
       <c r="E32" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="F32" t="s">
         <v>456</v>
@@ -10187,12 +10198,15 @@
         <v>479</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
         <v>440</v>
       </c>
       <c r="D33" t="s">
-        <v>408</v>
+        <v>407</v>
+      </c>
+      <c r="E33" t="s">
+        <v>499</v>
       </c>
       <c r="F33" t="s">
         <v>456</v>
@@ -10201,26 +10215,29 @@
         <v>479</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C34" t="s">
         <v>440</v>
       </c>
       <c r="D34" t="s">
-        <v>503</v>
+        <v>407</v>
+      </c>
+      <c r="E34" t="s">
+        <v>504</v>
       </c>
       <c r="F34" t="s">
         <v>456</v>
       </c>
       <c r="G34" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
         <v>440</v>
       </c>
       <c r="D35" t="s">
-        <v>504</v>
+        <v>408</v>
       </c>
       <c r="F35" t="s">
         <v>456</v>
@@ -10229,26 +10246,23 @@
         <v>479</v>
       </c>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D36" t="s">
-        <v>501</v>
-      </c>
-      <c r="E36" t="s">
         <v>502</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
       </c>
       <c r="G36" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D37" t="s">
         <v>503</v>
@@ -10260,12 +10274,15 @@
         <v>479</v>
       </c>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
         <v>434</v>
       </c>
       <c r="D38" t="s">
-        <v>504</v>
+        <v>500</v>
+      </c>
+      <c r="E38" t="s">
+        <v>501</v>
       </c>
       <c r="F38" t="s">
         <v>456</v>
@@ -10274,28 +10291,56 @@
         <v>479</v>
       </c>
     </row>
-    <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C39" t="s">
+        <v>434</v>
+      </c>
+      <c r="D39" t="s">
+        <v>502</v>
+      </c>
+      <c r="F39" t="s">
+        <v>456</v>
+      </c>
+      <c r="G39" t="s">
+        <v>492</v>
+      </c>
+    </row>
     <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="D40" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="F40" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G40" t="s">
         <v>479</v>
+      </c>
+    </row>
+    <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="42" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C42" t="s">
+        <v>493</v>
+      </c>
+      <c r="D42" t="s">
+        <v>510</v>
+      </c>
+      <c r="F42" t="s">
+        <v>457</v>
+      </c>
+      <c r="G42" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G38 G40" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G40 G42" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F38 F40" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F42 F4:F40" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2E7A07-26B8-48D0-9869-E75275090845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5B9B45-CC79-4390-AD31-7DF35E2936DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="765" yWindow="-12825" windowWidth="21600" windowHeight="11295" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2475" yWindow="4830" windowWidth="22170" windowHeight="12195" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6115,12 +6115,22 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G42" totalsRowShown="0">
   <autoFilter ref="C2:G42" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
     <filterColumn colId="1">
-      <filters>
-        <filter val="BGM"/>
+      <filters blank="1">
+        <filter val="エフェクト"/>
+        <filter val="ゴール後の報酬(hpを増やす等)"/>
+        <filter val="フェードを対応する"/>
+        <filter val="演出"/>
+        <filter val="何か見栄えをよくする"/>
+        <filter val="画像の差しかえ"/>
+        <filter val="画像の差し替え"/>
+        <filter val="画像差し替え"/>
+        <filter val="追加のステージ作成"/>
+        <filter val="入ったドアから出るようにする"/>
+        <filter val="背景差し替え"/>
       </filters>
     </filterColumn>
     <filterColumn colId="4">
-      <filters>
+      <filters blank="1">
         <filter val="進行中"/>
         <filter val="未着手"/>
       </filters>
@@ -9782,7 +9792,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.4">
       <c r="D5" t="s">
         <v>4</v>
       </c>
@@ -9796,7 +9806,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="6" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:7" x14ac:dyDescent="0.4">
       <c r="D6" t="s">
         <v>4</v>
       </c>
@@ -9827,7 +9837,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C8" t="s">
         <v>435</v>
       </c>
@@ -9844,7 +9854,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="9" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:7" x14ac:dyDescent="0.4">
       <c r="D9" t="s">
         <v>3</v>
       </c>
@@ -9858,7 +9868,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="10" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C10" t="s">
         <v>435</v>
       </c>
@@ -9875,7 +9885,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
         <v>435</v>
       </c>
@@ -9892,7 +9902,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="12" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="3:7" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
         <v>3</v>
       </c>
@@ -9920,7 +9930,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
         <v>435</v>
       </c>
@@ -9937,7 +9947,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="15" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
         <v>435</v>
       </c>
@@ -9982,7 +9992,7 @@
         <v>456</v>
       </c>
       <c r="G17" t="s">
-        <v>492</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -9999,7 +10009,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:7" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
         <v>491</v>
       </c>
@@ -10083,7 +10093,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:7" x14ac:dyDescent="0.4">
       <c r="D25" t="s">
         <v>494</v>
       </c>
@@ -10136,7 +10146,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
         <v>440</v>
       </c>
@@ -10150,7 +10160,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
         <v>440</v>
       </c>
@@ -10164,7 +10174,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
         <v>440</v>
       </c>
@@ -10181,7 +10191,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
         <v>440</v>
       </c>
@@ -10198,7 +10208,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
         <v>440</v>
       </c>
@@ -10232,7 +10242,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
         <v>440</v>
       </c>
@@ -10274,7 +10284,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
         <v>434</v>
       </c>
@@ -10291,7 +10301,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
         <v>434</v>
       </c>
@@ -10319,7 +10329,6 @@
         <v>479</v>
       </c>
     </row>
-    <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C42" t="s">
         <v>493</v>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5B9B45-CC79-4390-AD31-7DF35E2936DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C500469C-6B5F-4F53-94F9-9511219FFF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2475" yWindow="4830" windowWidth="22170" windowHeight="12195" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2475" yWindow="4830" windowWidth="22170" windowHeight="12195" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="516">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5877,6 +5877,44 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音の優先順位→環境音、プレイヤー、敵の順番</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジュンイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジュンバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境音終わり</t>
+    <rPh sb="0" eb="2">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6115,24 +6153,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G42" totalsRowShown="0">
   <autoFilter ref="C2:G42" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
     <filterColumn colId="1">
-      <filters blank="1">
-        <filter val="エフェクト"/>
-        <filter val="ゴール後の報酬(hpを増やす等)"/>
-        <filter val="フェードを対応する"/>
-        <filter val="演出"/>
-        <filter val="何か見栄えをよくする"/>
-        <filter val="画像の差しかえ"/>
-        <filter val="画像の差し替え"/>
-        <filter val="画像差し替え"/>
-        <filter val="追加のステージ作成"/>
-        <filter val="入ったドアから出るようにする"/>
-        <filter val="背景差し替え"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters blank="1">
-        <filter val="進行中"/>
-        <filter val="未着手"/>
+      <filters>
+        <filter val="BGM"/>
+        <filter val="SE"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -7601,7 +7624,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C314"/>
+  <dimension ref="B2:C316"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -9271,6 +9294,19 @@
       </c>
       <c r="C314" t="s">
         <v>509</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B315" s="9">
+        <v>46039</v>
+      </c>
+      <c r="C315" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C316" t="s">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -9792,7 +9828,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C5" t="s">
+        <v>433</v>
+      </c>
       <c r="D5" t="s">
         <v>4</v>
       </c>
@@ -9806,7 +9845,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C6" t="s">
+        <v>433</v>
+      </c>
       <c r="D6" t="s">
         <v>4</v>
       </c>
@@ -9837,7 +9879,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C8" t="s">
         <v>435</v>
       </c>
@@ -9854,7 +9896,10 @@
         <v>479</v>
       </c>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C9" t="s">
+        <v>435</v>
+      </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
@@ -9868,7 +9913,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C10" t="s">
         <v>435</v>
       </c>
@@ -9885,7 +9930,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
         <v>435</v>
       </c>
@@ -9902,7 +9947,10 @@
         <v>492</v>
       </c>
     </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>435</v>
+      </c>
       <c r="D12" t="s">
         <v>3</v>
       </c>
@@ -9917,6 +9965,9 @@
       </c>
     </row>
     <row r="13" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>435</v>
+      </c>
       <c r="D13" t="s">
         <v>480</v>
       </c>
@@ -9930,7 +9981,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
         <v>435</v>
       </c>
@@ -9947,7 +9998,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
         <v>435</v>
       </c>
@@ -10009,7 +10060,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C19" t="s">
+        <v>435</v>
+      </c>
       <c r="D19" t="s">
         <v>491</v>
       </c>
@@ -10020,7 +10074,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="20" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>435</v>
       </c>
@@ -10034,7 +10088,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C21" t="s">
         <v>435</v>
       </c>
@@ -10045,7 +10099,7 @@
         <v>456</v>
       </c>
       <c r="G21" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10093,7 +10147,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C25" t="s">
+        <v>493</v>
+      </c>
       <c r="D25" t="s">
         <v>494</v>
       </c>
@@ -10118,7 +10175,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
         <v>493</v>
       </c>
@@ -10132,7 +10189,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
         <v>493</v>
       </c>
@@ -10143,10 +10200,10 @@
         <v>456</v>
       </c>
       <c r="G28" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
         <v>440</v>
       </c>
@@ -10160,7 +10217,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
         <v>440</v>
       </c>
@@ -10174,7 +10231,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
         <v>440</v>
       </c>
@@ -10191,7 +10248,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
         <v>440</v>
       </c>
@@ -10208,7 +10265,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
         <v>440</v>
       </c>
@@ -10242,7 +10299,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
         <v>440</v>
       </c>
@@ -10256,7 +10313,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
         <v>440</v>
       </c>
@@ -10270,7 +10327,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
         <v>440</v>
       </c>
@@ -10281,10 +10338,10 @@
         <v>456</v>
       </c>
       <c r="G37" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.4">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
         <v>434</v>
       </c>
@@ -10301,7 +10358,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
         <v>434</v>
       </c>
@@ -10312,10 +10369,10 @@
         <v>456</v>
       </c>
       <c r="G39" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
         <v>434</v>
       </c>
@@ -10326,9 +10383,10 @@
         <v>456</v>
       </c>
       <c r="G40" t="s">
-        <v>479</v>
-      </c>
-    </row>
+        <v>492</v>
+      </c>
+    </row>
+    <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C42" t="s">
         <v>493</v>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C500469C-6B5F-4F53-94F9-9511219FFF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85139E26-2E37-49D3-B1AC-AA4AC18BA0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2475" yWindow="4830" windowWidth="22170" windowHeight="12195" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="523">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5915,6 +5915,64 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景置き</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージの穴にキャラを入れる</t>
+    <rPh sb="5" eb="6">
+      <t>アナ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ステージクリアシーン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加のシーン</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業さんは最後までたぶんしないから需要低い</t>
+    <rPh sb="0" eb="2">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジュヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヒク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンドマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGMとSEを調整できるように</t>
+    <rPh sb="7" eb="9">
+      <t>チョウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6150,12 +6208,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G42" totalsRowShown="0">
-  <autoFilter ref="C2:G42" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
-    <filterColumn colId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G45" totalsRowShown="0">
+  <autoFilter ref="C2:G45" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+    <filterColumn colId="4">
       <filters>
-        <filter val="BGM"/>
-        <filter val="SE"/>
+        <filter val="進行中"/>
+        <filter val="進捗度合い"/>
+        <filter val="未着手"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9767,12 +9826,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G42"/>
+  <dimension ref="C2:G45"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
     <col min="4" max="4" width="39.5" customWidth="1"/>
-    <col min="5" max="5" width="32.125" customWidth="1"/>
+    <col min="5" max="5" width="39.875" customWidth="1"/>
     <col min="6" max="6" width="19.25" customWidth="1"/>
     <col min="7" max="7" width="15.375" customWidth="1"/>
   </cols>
@@ -9794,7 +9853,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="3" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
         <v>5</v>
       </c>
@@ -9828,7 +9887,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>433</v>
       </c>
@@ -9845,7 +9904,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="6" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
         <v>433</v>
       </c>
@@ -9879,7 +9938,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C8" t="s">
         <v>435</v>
       </c>
@@ -9896,7 +9955,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="9" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C9" t="s">
         <v>435</v>
       </c>
@@ -9913,7 +9972,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="10" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C10" t="s">
         <v>435</v>
       </c>
@@ -9930,7 +9989,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
         <v>435</v>
       </c>
@@ -9947,7 +10006,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="12" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
         <v>435</v>
       </c>
@@ -9981,7 +10040,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
         <v>435</v>
       </c>
@@ -9995,10 +10054,10 @@
         <v>456</v>
       </c>
       <c r="G14" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="15" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
         <v>435</v>
       </c>
@@ -10032,18 +10091,18 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
         <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="F17" t="s">
         <v>456</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10051,7 +10110,7 @@
         <v>435</v>
       </c>
       <c r="D18" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="F18" t="s">
         <v>456</v>
@@ -10065,13 +10124,13 @@
         <v>435</v>
       </c>
       <c r="D19" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G19" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="3:7" x14ac:dyDescent="0.4">
@@ -10079,41 +10138,41 @@
         <v>435</v>
       </c>
       <c r="D20" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F20" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.4">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C21" t="s">
         <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F21" t="s">
         <v>456</v>
       </c>
       <c r="G21" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="22" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
-        <v>493</v>
+        <v>435</v>
       </c>
       <c r="D22" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="F22" t="s">
         <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>101</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10121,7 +10180,7 @@
         <v>493</v>
       </c>
       <c r="D23" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="F23" t="s">
         <v>456</v>
@@ -10135,10 +10194,7 @@
         <v>493</v>
       </c>
       <c r="D24" t="s">
-        <v>407</v>
-      </c>
-      <c r="E24" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="F24" t="s">
         <v>456</v>
@@ -10152,27 +10208,27 @@
         <v>493</v>
       </c>
       <c r="D25" t="s">
-        <v>494</v>
+        <v>407</v>
+      </c>
+      <c r="E25" t="s">
+        <v>486</v>
       </c>
       <c r="F25" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G25" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
-        <v>493</v>
+        <v>430</v>
       </c>
       <c r="D26" t="s">
-        <v>495</v>
-      </c>
-      <c r="F26" t="s">
-        <v>456</v>
-      </c>
-      <c r="G26" t="s">
-        <v>101</v>
+        <v>521</v>
+      </c>
+      <c r="E26" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="27" spans="3:7" x14ac:dyDescent="0.4">
@@ -10180,66 +10236,63 @@
         <v>493</v>
       </c>
       <c r="D27" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="F27" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
         <v>493</v>
       </c>
       <c r="D28" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="F28" t="s">
         <v>456</v>
       </c>
       <c r="G28" t="s">
-        <v>492</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="D29" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="F29" t="s">
         <v>456</v>
       </c>
       <c r="G29" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="D30" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="F30" t="s">
         <v>456</v>
       </c>
       <c r="G30" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
         <v>440</v>
       </c>
       <c r="D31" t="s">
-        <v>505</v>
-      </c>
-      <c r="E31" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="F31" t="s">
         <v>456</v>
@@ -10248,15 +10301,12 @@
         <v>479</v>
       </c>
     </row>
-    <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
         <v>440</v>
       </c>
       <c r="D32" t="s">
-        <v>407</v>
-      </c>
-      <c r="E32" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F32" t="s">
         <v>456</v>
@@ -10265,15 +10315,15 @@
         <v>479</v>
       </c>
     </row>
-    <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
         <v>440</v>
       </c>
       <c r="D33" t="s">
-        <v>407</v>
+        <v>505</v>
       </c>
       <c r="E33" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="F33" t="s">
         <v>456</v>
@@ -10282,7 +10332,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="34" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C34" t="s">
         <v>440</v>
       </c>
@@ -10290,35 +10340,41 @@
         <v>407</v>
       </c>
       <c r="E34" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="F34" t="s">
         <v>456</v>
       </c>
       <c r="G34" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
         <v>440</v>
       </c>
       <c r="D35" t="s">
-        <v>408</v>
+        <v>407</v>
+      </c>
+      <c r="E35" t="s">
+        <v>499</v>
       </c>
       <c r="F35" t="s">
         <v>456</v>
       </c>
       <c r="G35" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.4">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
         <v>440</v>
       </c>
       <c r="D36" t="s">
-        <v>502</v>
+        <v>407</v>
+      </c>
+      <c r="E36" t="s">
+        <v>504</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
@@ -10332,44 +10388,41 @@
         <v>440</v>
       </c>
       <c r="D37" t="s">
-        <v>503</v>
+        <v>408</v>
       </c>
       <c r="F37" t="s">
         <v>456</v>
       </c>
       <c r="G37" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D38" t="s">
-        <v>500</v>
-      </c>
-      <c r="E38" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F38" t="s">
         <v>456</v>
       </c>
       <c r="G38" t="s">
-        <v>479</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D39" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F39" t="s">
         <v>456</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>492</v>
       </c>
     </row>
     <row r="40" spans="3:7" x14ac:dyDescent="0.4">
@@ -10377,37 +10430,98 @@
         <v>434</v>
       </c>
       <c r="D40" t="s">
-        <v>503</v>
+        <v>500</v>
+      </c>
+      <c r="E40" t="s">
+        <v>501</v>
       </c>
       <c r="F40" t="s">
         <v>456</v>
       </c>
       <c r="G40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C41" t="s">
+        <v>434</v>
+      </c>
+      <c r="D41" t="s">
+        <v>502</v>
+      </c>
+      <c r="F41" t="s">
+        <v>456</v>
+      </c>
+      <c r="G41" t="s">
+        <v>101</v>
+      </c>
+    </row>
     <row r="42" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C42" t="s">
-        <v>493</v>
+        <v>434</v>
       </c>
       <c r="D42" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="F42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C43" t="s">
+        <v>434</v>
+      </c>
+      <c r="D43" t="s">
+        <v>516</v>
+      </c>
+      <c r="F43" t="s">
+        <v>456</v>
+      </c>
+      <c r="G43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C44" t="s">
+        <v>493</v>
+      </c>
+      <c r="D44" t="s">
+        <v>510</v>
+      </c>
+      <c r="F44" t="s">
+        <v>457</v>
+      </c>
+      <c r="G44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C45" t="s">
+        <v>518</v>
+      </c>
+      <c r="D45" t="s">
+        <v>519</v>
+      </c>
+      <c r="E45" t="s">
+        <v>520</v>
+      </c>
+      <c r="F45" t="s">
+        <v>457</v>
+      </c>
+      <c r="G45" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G40 G42" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G45" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F42 F4:F40" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F45" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85139E26-2E37-49D3-B1AC-AA4AC18BA0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62931841-5FC7-4FE1-A88F-5D1F3FEDA3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2475" yWindow="4830" windowWidth="22170" windowHeight="12195" firstSheet="1" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="524">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5973,6 +5973,13 @@
     <t>BGMとSEを調整できるように</t>
     <rPh sb="7" eb="9">
       <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次にするのは、ゴールシーン</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6210,10 +6217,15 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G45" totalsRowShown="0">
   <autoFilter ref="C2:G45" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="高"/>
+        <filter val="中"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="4">
       <filters>
         <filter val="進行中"/>
-        <filter val="進捗度合い"/>
         <filter val="未着手"/>
       </filters>
     </filterColumn>
@@ -7683,7 +7695,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C316"/>
+  <dimension ref="B2:C317"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -9366,6 +9378,14 @@
     <row r="316" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C316" t="s">
         <v>515</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B317" s="9">
+        <v>46041</v>
+      </c>
+      <c r="C317" t="s">
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -9853,7 +9873,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
         <v>5</v>
       </c>
@@ -9887,7 +9907,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>433</v>
       </c>
@@ -10040,7 +10060,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
         <v>435</v>
       </c>
@@ -10133,7 +10153,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>435</v>
       </c>
@@ -10220,7 +10240,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
         <v>430</v>
       </c>
@@ -10231,7 +10251,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
         <v>493</v>
       </c>
@@ -10425,7 +10445,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
         <v>434</v>
       </c>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62931841-5FC7-4FE1-A88F-5D1F3FEDA3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1CE55E-73CE-4D2B-A05F-BDFE42143F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2475" yWindow="4830" windowWidth="22170" windowHeight="12195" firstSheet="1" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet9" sheetId="9" r:id="rId7"/>
     <sheet name="Sheet7" sheetId="7" r:id="rId8"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="515">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5499,44 +5498,6 @@
     <t>低</t>
   </si>
   <si>
-    <t>タスク名</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>開始日</t>
-    <rPh sb="0" eb="3">
-      <t>カイシビ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>終了日</t>
-    <rPh sb="0" eb="3">
-      <t>シュウリョウビ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>優先度</t>
-    <rPh sb="0" eb="3">
-      <t>ユウセンド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>進捗状況</t>
-    <rPh sb="0" eb="2">
-      <t>シンチョク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>列1</t>
   </si>
   <si>
@@ -5550,23 +5511,6 @@
   </si>
   <si>
     <t>列5</t>
-  </si>
-  <si>
-    <t>未完了</t>
-  </si>
-  <si>
-    <t>タスク1</t>
-  </si>
-  <si>
-    <t>タスク2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エクセル練習</t>
-    <rPh sb="4" eb="6">
-      <t>レンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>タスク名(親)</t>
@@ -6236,26 +6180,6 @@
     <tableColumn id="3" xr3:uid="{E928A0C4-0CC9-47D2-A61A-91CB8DF54FA2}" name="列3"/>
     <tableColumn id="4" xr3:uid="{E3E4E73E-6900-4BFD-A32F-57FFF716B0BB}" name="列4"/>
     <tableColumn id="5" xr3:uid="{36F84575-9D8B-4C25-871E-CEAF326E01E2}" name="列5"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5814694B-B1B0-4655-8275-CA9217E4D27F}" name="テーブル3" displayName="テーブル3" ref="B2:F4" totalsRowShown="0">
-  <autoFilter ref="B2:F4" xr:uid="{5814694B-B1B0-4655-8275-CA9217E4D27F}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="低"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FE95F1C6-D62A-4D9A-983F-333BB81F8841}" name="タスク名"/>
-    <tableColumn id="2" xr3:uid="{9867DE28-00FB-4030-9AAB-6BE2A0ABE7D6}" name="開始日"/>
-    <tableColumn id="3" xr3:uid="{77D16931-2E3B-46D1-9B35-95A897EAE8A7}" name="終了日"/>
-    <tableColumn id="4" xr3:uid="{0626C141-E220-40EF-93A6-61507D10D1BD}" name="優先度"/>
-    <tableColumn id="5" xr3:uid="{BCEAD21F-F4A7-4F8E-8A6F-3A1AE5008041}" name="進捗状況"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9364,7 +9288,7 @@
         <v>46036</v>
       </c>
       <c r="C314" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="315" spans="2:3" x14ac:dyDescent="0.4">
@@ -9372,12 +9296,12 @@
         <v>46039</v>
       </c>
       <c r="C315" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
     </row>
     <row r="316" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C316" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
     </row>
     <row r="317" spans="2:3" x14ac:dyDescent="0.4">
@@ -9385,7 +9309,7 @@
         <v>46041</v>
       </c>
       <c r="C317" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -9858,19 +9782,19 @@
   <sheetData>
     <row r="2" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="G2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -9878,16 +9802,16 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="E3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="F3" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="G3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -9895,10 +9819,10 @@
         <v>433</v>
       </c>
       <c r="D4" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E4" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F4" t="s">
         <v>456</v>
@@ -9921,7 +9845,7 @@
         <v>458</v>
       </c>
       <c r="G5" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.4">
@@ -9932,13 +9856,13 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="F6" t="s">
         <v>457</v>
       </c>
       <c r="G6" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -9949,7 +9873,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="F7" t="s">
         <v>456</v>
@@ -9966,13 +9890,13 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="F8" t="s">
         <v>456</v>
       </c>
       <c r="G8" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.4">
@@ -9983,13 +9907,13 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="F9" t="s">
         <v>457</v>
       </c>
       <c r="G9" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="3:7" x14ac:dyDescent="0.4">
@@ -10000,13 +9924,13 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="F10" t="s">
         <v>457</v>
       </c>
       <c r="G10" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="3:7" x14ac:dyDescent="0.4">
@@ -10017,13 +9941,13 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="F11" t="s">
         <v>456</v>
       </c>
       <c r="G11" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="3:7" x14ac:dyDescent="0.4">
@@ -10034,13 +9958,13 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="F12" t="s">
         <v>457</v>
       </c>
       <c r="G12" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10048,10 +9972,10 @@
         <v>435</v>
       </c>
       <c r="D13" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="E13" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="F13" t="s">
         <v>457</v>
@@ -10068,7 +9992,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="F14" t="s">
         <v>456</v>
@@ -10082,16 +10006,16 @@
         <v>435</v>
       </c>
       <c r="D15" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="E15" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="F15" t="s">
         <v>456</v>
       </c>
       <c r="G15" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10099,10 +10023,10 @@
         <v>435</v>
       </c>
       <c r="D16" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="E16" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="F16" t="s">
         <v>456</v>
@@ -10116,13 +10040,13 @@
         <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="F17" t="s">
         <v>456</v>
       </c>
       <c r="G17" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10130,7 +10054,7 @@
         <v>435</v>
       </c>
       <c r="D18" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="F18" t="s">
         <v>456</v>
@@ -10144,7 +10068,7 @@
         <v>435</v>
       </c>
       <c r="D19" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="F19" t="s">
         <v>456</v>
@@ -10158,13 +10082,13 @@
         <v>435</v>
       </c>
       <c r="D20" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="F20" t="s">
         <v>458</v>
       </c>
       <c r="G20" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10172,7 +10096,7 @@
         <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="F21" t="s">
         <v>456</v>
@@ -10186,21 +10110,21 @@
         <v>435</v>
       </c>
       <c r="D22" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F22" t="s">
         <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="D23" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="F23" t="s">
         <v>456</v>
@@ -10211,10 +10135,10 @@
     </row>
     <row r="24" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="D24" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="F24" t="s">
         <v>456</v>
@@ -10225,13 +10149,13 @@
     </row>
     <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C25" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="D25" t="s">
         <v>407</v>
       </c>
       <c r="E25" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="F25" t="s">
         <v>456</v>
@@ -10245,32 +10169,32 @@
         <v>430</v>
       </c>
       <c r="D26" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="E26" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
     </row>
     <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="D27" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="F27" t="s">
         <v>458</v>
       </c>
       <c r="G27" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="D28" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="F28" t="s">
         <v>456</v>
@@ -10281,10 +10205,10 @@
     </row>
     <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
+        <v>484</v>
+      </c>
+      <c r="D29" t="s">
         <v>493</v>
-      </c>
-      <c r="D29" t="s">
-        <v>502</v>
       </c>
       <c r="F29" t="s">
         <v>456</v>
@@ -10295,10 +10219,10 @@
     </row>
     <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="D30" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F30" t="s">
         <v>456</v>
@@ -10312,13 +10236,13 @@
         <v>440</v>
       </c>
       <c r="D31" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="F31" t="s">
         <v>456</v>
       </c>
       <c r="G31" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" spans="3:7" x14ac:dyDescent="0.4">
@@ -10326,13 +10250,13 @@
         <v>440</v>
       </c>
       <c r="D32" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F32" t="s">
         <v>456</v>
       </c>
       <c r="G32" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33" spans="3:7" x14ac:dyDescent="0.4">
@@ -10340,16 +10264,16 @@
         <v>440</v>
       </c>
       <c r="D33" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="E33" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="F33" t="s">
         <v>456</v>
       </c>
       <c r="G33" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="34" spans="3:7" x14ac:dyDescent="0.4">
@@ -10360,13 +10284,13 @@
         <v>407</v>
       </c>
       <c r="E34" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="F34" t="s">
         <v>456</v>
       </c>
       <c r="G34" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.4">
@@ -10377,13 +10301,13 @@
         <v>407</v>
       </c>
       <c r="E35" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="F35" t="s">
         <v>456</v>
       </c>
       <c r="G35" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10394,7 +10318,7 @@
         <v>407</v>
       </c>
       <c r="E36" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
@@ -10414,7 +10338,7 @@
         <v>456</v>
       </c>
       <c r="G37" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10422,7 +10346,7 @@
         <v>440</v>
       </c>
       <c r="D38" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="F38" t="s">
         <v>456</v>
@@ -10436,13 +10360,13 @@
         <v>440</v>
       </c>
       <c r="D39" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F39" t="s">
         <v>456</v>
       </c>
       <c r="G39" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10450,10 +10374,10 @@
         <v>434</v>
       </c>
       <c r="D40" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="E40" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="F40" t="s">
         <v>456</v>
@@ -10467,7 +10391,7 @@
         <v>434</v>
       </c>
       <c r="D41" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="F41" t="s">
         <v>456</v>
@@ -10481,7 +10405,7 @@
         <v>434</v>
       </c>
       <c r="D42" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F42" t="s">
         <v>456</v>
@@ -10495,7 +10419,7 @@
         <v>434</v>
       </c>
       <c r="D43" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="F43" t="s">
         <v>456</v>
@@ -10506,10 +10430,10 @@
     </row>
     <row r="44" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="D44" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="F44" t="s">
         <v>457</v>
@@ -10520,19 +10444,19 @@
     </row>
     <row r="45" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="D45" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E45" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="F45" t="s">
         <v>457</v>
       </c>
       <c r="G45" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -10586,81 +10510,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BAAB0F-3A46-421A-8FF2-23EA3AC6BEF8}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="2" max="2" width="17.625" customWidth="1"/>
-    <col min="3" max="3" width="20.375" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="22.625" customWidth="1"/>
-    <col min="6" max="6" width="19.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E3" t="s">
-        <v>458</v>
-      </c>
-      <c r="F3" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>471</v>
-      </c>
-      <c r="E4" t="s">
-        <v>457</v>
-      </c>
-      <c r="F4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4" xr:uid="{B5A4B4FB-EA43-42D8-A5BD-89B48D5F38A7}">
-      <formula1>"タスク1,タスク2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E4" xr:uid="{2F18CB7E-504E-4A33-A61C-04E992926A3B}">
-      <formula1>"高,中,低"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F4" xr:uid="{547CA2C8-732B-457A-B17C-8502248092C2}">
-      <formula1>"完了,未完了"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1CE55E-73CE-4D2B-A05F-BDFE42143F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B5868F-DA73-4640-8D36-62C2A29182C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="4230" yWindow="-13515" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="518">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5924,6 +5924,33 @@
     <t>次にするのは、ゴールシーン</t>
     <rPh sb="0" eb="1">
       <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細を作成</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアルも兼ねたものを作る</t>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクトシーン、ステージ1_2,ステージ2_2でエフェクトが出ない</t>
+    <rPh sb="34" eb="35">
+      <t>デ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6159,14 +6186,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G45" totalsRowShown="0">
-  <autoFilter ref="C2:G45" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="高"/>
-        <filter val="中"/>
-      </filters>
-    </filterColumn>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G47" totalsRowShown="0">
+  <autoFilter ref="C2:G47" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
     <filterColumn colId="4">
       <filters>
         <filter val="進行中"/>
@@ -7619,7 +7640,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C317"/>
+  <dimension ref="B2:C319"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -9310,6 +9331,14 @@
       </c>
       <c r="C317" t="s">
         <v>514</v>
+      </c>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B319" s="9">
+        <v>46042</v>
+      </c>
+      <c r="C319" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -9770,7 +9799,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G45"/>
+  <dimension ref="C2:G47"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
@@ -9831,7 +9860,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>433</v>
       </c>
@@ -10077,7 +10106,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>435</v>
       </c>
@@ -10110,27 +10139,27 @@
         <v>435</v>
       </c>
       <c r="D22" t="s">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="F22" t="s">
         <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
-        <v>484</v>
+        <v>435</v>
       </c>
       <c r="D23" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="F23" t="s">
         <v>456</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10138,7 +10167,7 @@
         <v>484</v>
       </c>
       <c r="D24" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="F24" t="s">
         <v>456</v>
@@ -10152,10 +10181,7 @@
         <v>484</v>
       </c>
       <c r="D25" t="s">
-        <v>407</v>
-      </c>
-      <c r="E25" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="F25" t="s">
         <v>456</v>
@@ -10166,41 +10192,44 @@
     </row>
     <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
       <c r="D26" t="s">
-        <v>512</v>
+        <v>407</v>
       </c>
       <c r="E26" t="s">
-        <v>513</v>
+        <v>477</v>
+      </c>
+      <c r="F26" t="s">
+        <v>456</v>
+      </c>
+      <c r="G26" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
-        <v>484</v>
+        <v>430</v>
       </c>
       <c r="D27" t="s">
-        <v>485</v>
-      </c>
-      <c r="F27" t="s">
-        <v>458</v>
-      </c>
-      <c r="G27" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>512</v>
+      </c>
+      <c r="E27" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
         <v>484</v>
       </c>
       <c r="D28" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F28" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10208,7 +10237,7 @@
         <v>484</v>
       </c>
       <c r="D29" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="F29" t="s">
         <v>456</v>
@@ -10222,7 +10251,7 @@
         <v>484</v>
       </c>
       <c r="D30" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F30" t="s">
         <v>456</v>
@@ -10231,32 +10260,32 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="D31" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F31" t="s">
         <v>456</v>
       </c>
       <c r="G31" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
         <v>440</v>
       </c>
       <c r="D32" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F32" t="s">
         <v>456</v>
       </c>
       <c r="G32" t="s">
-        <v>470</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="3:7" x14ac:dyDescent="0.4">
@@ -10264,16 +10293,13 @@
         <v>440</v>
       </c>
       <c r="D33" t="s">
-        <v>496</v>
-      </c>
-      <c r="E33" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F33" t="s">
         <v>456</v>
       </c>
       <c r="G33" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="34" spans="3:7" x14ac:dyDescent="0.4">
@@ -10281,10 +10307,10 @@
         <v>440</v>
       </c>
       <c r="D34" t="s">
-        <v>407</v>
+        <v>496</v>
       </c>
       <c r="E34" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F34" t="s">
         <v>456</v>
@@ -10301,13 +10327,13 @@
         <v>407</v>
       </c>
       <c r="E35" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F35" t="s">
         <v>456</v>
       </c>
       <c r="G35" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10318,7 +10344,7 @@
         <v>407</v>
       </c>
       <c r="E36" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
@@ -10327,63 +10353,63 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
         <v>440</v>
       </c>
       <c r="D37" t="s">
-        <v>408</v>
+        <v>407</v>
+      </c>
+      <c r="E37" t="s">
+        <v>495</v>
       </c>
       <c r="F37" t="s">
         <v>456</v>
       </c>
       <c r="G37" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
         <v>440</v>
       </c>
       <c r="D38" t="s">
-        <v>493</v>
+        <v>408</v>
       </c>
       <c r="F38" t="s">
         <v>456</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.4">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
         <v>440</v>
       </c>
       <c r="D39" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F39" t="s">
         <v>456</v>
       </c>
       <c r="G39" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D40" t="s">
-        <v>491</v>
-      </c>
-      <c r="E40" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F40" t="s">
         <v>456</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>483</v>
       </c>
     </row>
     <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10391,7 +10417,10 @@
         <v>434</v>
       </c>
       <c r="D41" t="s">
-        <v>493</v>
+        <v>491</v>
+      </c>
+      <c r="E41" t="s">
+        <v>492</v>
       </c>
       <c r="F41" t="s">
         <v>456</v>
@@ -10405,7 +10434,7 @@
         <v>434</v>
       </c>
       <c r="D42" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F42" t="s">
         <v>456</v>
@@ -10419,7 +10448,7 @@
         <v>434</v>
       </c>
       <c r="D43" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="F43" t="s">
         <v>456</v>
@@ -10430,42 +10459,70 @@
     </row>
     <row r="44" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
-        <v>484</v>
+        <v>434</v>
       </c>
       <c r="D44" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F44" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="D45" t="s">
-        <v>510</v>
-      </c>
-      <c r="E45" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="F45" t="s">
         <v>457</v>
       </c>
       <c r="G45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C46" t="s">
+        <v>509</v>
+      </c>
+      <c r="D46" t="s">
+        <v>510</v>
+      </c>
+      <c r="E46" t="s">
+        <v>511</v>
+      </c>
+      <c r="F46" t="s">
+        <v>457</v>
+      </c>
+      <c r="G46" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="47" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C47" t="s">
+        <v>430</v>
+      </c>
+      <c r="D47" t="s">
+        <v>515</v>
+      </c>
+      <c r="F47" t="s">
+        <v>456</v>
+      </c>
+      <c r="G47" t="s">
         <v>470</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G45" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G47" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F45" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F47" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B5868F-DA73-4640-8D36-62C2A29182C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290ED327-9DC5-4685-8722-C2A049875EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="-13515" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="7485" yWindow="5700" windowWidth="22170" windowHeight="12195" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="520">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5951,6 +5951,20 @@
     <t>ステージセレクトシーン、ステージ1_2,ステージ2_2でエフェクトが出ない</t>
     <rPh sb="34" eb="35">
       <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bear&amp;Wolfのhpバーを作る</t>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大砲のエフェクト</t>
+    <rPh sb="0" eb="2">
+      <t>タイホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6186,8 +6200,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G47" totalsRowShown="0">
-  <autoFilter ref="C2:G47" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G49" totalsRowShown="0">
+  <autoFilter ref="C2:G49" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
     <filterColumn colId="4">
       <filters>
         <filter val="進行中"/>
@@ -9799,7 +9813,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G47"/>
+  <dimension ref="C2:G49"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
@@ -9959,7 +9973,7 @@
         <v>457</v>
       </c>
       <c r="G10" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="3:7" x14ac:dyDescent="0.4">
@@ -10153,27 +10167,27 @@
         <v>435</v>
       </c>
       <c r="D23" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="F23" t="s">
         <v>456</v>
       </c>
       <c r="G23" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="24" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
-        <v>484</v>
+        <v>435</v>
       </c>
       <c r="D24" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="F24" t="s">
         <v>456</v>
       </c>
       <c r="G24" t="s">
-        <v>101</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10181,7 +10195,7 @@
         <v>484</v>
       </c>
       <c r="D25" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="F25" t="s">
         <v>456</v>
@@ -10195,10 +10209,7 @@
         <v>484</v>
       </c>
       <c r="D26" t="s">
-        <v>407</v>
-      </c>
-      <c r="E26" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="F26" t="s">
         <v>456</v>
@@ -10209,41 +10220,44 @@
     </row>
     <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
+        <v>484</v>
+      </c>
+      <c r="D27" t="s">
+        <v>407</v>
+      </c>
+      <c r="E27" t="s">
+        <v>477</v>
+      </c>
+      <c r="F27" t="s">
+        <v>456</v>
+      </c>
+      <c r="G27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C28" t="s">
         <v>430</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>512</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C28" t="s">
-        <v>484</v>
-      </c>
-      <c r="D28" t="s">
-        <v>485</v>
-      </c>
-      <c r="F28" t="s">
-        <v>458</v>
-      </c>
-      <c r="G28" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
         <v>484</v>
       </c>
       <c r="D29" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F29" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10251,7 +10265,7 @@
         <v>484</v>
       </c>
       <c r="D30" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="F30" t="s">
         <v>456</v>
@@ -10265,7 +10279,7 @@
         <v>484</v>
       </c>
       <c r="D31" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F31" t="s">
         <v>456</v>
@@ -10276,10 +10290,10 @@
     </row>
     <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="D32" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F32" t="s">
         <v>456</v>
@@ -10288,18 +10302,18 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
         <v>440</v>
       </c>
       <c r="D33" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F33" t="s">
         <v>456</v>
       </c>
       <c r="G33" t="s">
-        <v>483</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="3:7" x14ac:dyDescent="0.4">
@@ -10307,16 +10321,13 @@
         <v>440</v>
       </c>
       <c r="D34" t="s">
-        <v>496</v>
-      </c>
-      <c r="E34" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F34" t="s">
         <v>456</v>
       </c>
       <c r="G34" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.4">
@@ -10324,10 +10335,10 @@
         <v>440</v>
       </c>
       <c r="D35" t="s">
-        <v>407</v>
+        <v>496</v>
       </c>
       <c r="E35" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F35" t="s">
         <v>456</v>
@@ -10344,7 +10355,7 @@
         <v>407</v>
       </c>
       <c r="E36" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
@@ -10361,7 +10372,7 @@
         <v>407</v>
       </c>
       <c r="E37" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F37" t="s">
         <v>456</v>
@@ -10370,18 +10381,21 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
         <v>440</v>
       </c>
       <c r="D38" t="s">
-        <v>408</v>
+        <v>407</v>
+      </c>
+      <c r="E38" t="s">
+        <v>495</v>
       </c>
       <c r="F38" t="s">
         <v>456</v>
       </c>
       <c r="G38" t="s">
-        <v>470</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10389,7 +10403,7 @@
         <v>440</v>
       </c>
       <c r="D39" t="s">
-        <v>493</v>
+        <v>408</v>
       </c>
       <c r="F39" t="s">
         <v>456</v>
@@ -10398,29 +10412,26 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
         <v>440</v>
       </c>
       <c r="D40" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F40" t="s">
         <v>456</v>
       </c>
       <c r="G40" t="s">
-        <v>483</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C41" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D41" t="s">
-        <v>491</v>
-      </c>
-      <c r="E41" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F41" t="s">
         <v>456</v>
@@ -10434,7 +10445,10 @@
         <v>434</v>
       </c>
       <c r="D42" t="s">
-        <v>493</v>
+        <v>491</v>
+      </c>
+      <c r="E42" t="s">
+        <v>492</v>
       </c>
       <c r="F42" t="s">
         <v>456</v>
@@ -10448,7 +10462,7 @@
         <v>434</v>
       </c>
       <c r="D43" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F43" t="s">
         <v>456</v>
@@ -10462,7 +10476,7 @@
         <v>434</v>
       </c>
       <c r="D44" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="F44" t="s">
         <v>456</v>
@@ -10473,56 +10487,84 @@
     </row>
     <row r="45" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>484</v>
+        <v>434</v>
       </c>
       <c r="D45" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F45" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="D46" t="s">
-        <v>510</v>
-      </c>
-      <c r="E46" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="F46" t="s">
         <v>457</v>
       </c>
       <c r="G46" t="s">
-        <v>470</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C47" t="s">
+        <v>509</v>
+      </c>
+      <c r="D47" t="s">
+        <v>510</v>
+      </c>
+      <c r="E47" t="s">
+        <v>511</v>
+      </c>
+      <c r="F47" t="s">
+        <v>457</v>
+      </c>
+      <c r="G47" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="48" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C48" t="s">
         <v>430</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>515</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F48" t="s">
         <v>456</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G48" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="49" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C49" t="s">
+        <v>440</v>
+      </c>
+      <c r="D49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F49" t="s">
+        <v>457</v>
+      </c>
+      <c r="G49" t="s">
         <v>470</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G47" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G49" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F47" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F49" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290ED327-9DC5-4685-8722-C2A049875EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5738ADAC-1D66-4882-9D2C-7C1F58725151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7485" yWindow="5700" windowWidth="22170" windowHeight="12195" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="3720" yWindow="2160" windowWidth="21600" windowHeight="12015" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="525">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5965,6 +5965,49 @@
     <t>大砲のエフェクト</t>
     <rPh sb="0" eb="2">
       <t>タイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ゴールシーン】</t>
+  </si>
+  <si>
+    <t>大砲の演出</t>
+    <rPh sb="0" eb="2">
+      <t>タイホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラが乗ったら、拡大、撃つとき縮小など</t>
+    <rPh sb="4" eb="5">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カクダイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュクショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のSE</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアしていないシーンは表示しないように</t>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6200,10 +6243,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G49" totalsRowShown="0">
-  <autoFilter ref="C2:G49" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G52" totalsRowShown="0">
+  <autoFilter ref="C2:G52" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
     <filterColumn colId="4">
-      <filters>
+      <filters blank="1">
         <filter val="進行中"/>
         <filter val="未着手"/>
       </filters>
@@ -9813,7 +9856,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G49"/>
+  <dimension ref="C2:G52"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
@@ -9959,7 +10002,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C10" t="s">
         <v>435</v>
       </c>
@@ -9973,10 +10016,10 @@
         <v>457</v>
       </c>
       <c r="G10" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
         <v>435</v>
       </c>
@@ -9990,7 +10033,7 @@
         <v>456</v>
       </c>
       <c r="G11" t="s">
-        <v>483</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="3:7" x14ac:dyDescent="0.4">
@@ -10159,7 +10202,7 @@
         <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23" spans="3:7" x14ac:dyDescent="0.4">
@@ -10173,10 +10216,10 @@
         <v>456</v>
       </c>
       <c r="G23" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
         <v>435</v>
       </c>
@@ -10187,7 +10230,7 @@
         <v>456</v>
       </c>
       <c r="G24" t="s">
-        <v>483</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10235,7 +10278,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
         <v>430</v>
       </c>
@@ -10244,6 +10287,9 @@
       </c>
       <c r="E28" t="s">
         <v>513</v>
+      </c>
+      <c r="G28" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="29" spans="3:7" x14ac:dyDescent="0.4">
@@ -10318,84 +10364,66 @@
     </row>
     <row r="34" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C34" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="D34" t="s">
-        <v>488</v>
-      </c>
-      <c r="F34" t="s">
-        <v>456</v>
-      </c>
-      <c r="G34" t="s">
-        <v>483</v>
+        <v>524</v>
       </c>
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
-        <v>440</v>
+        <v>520</v>
       </c>
       <c r="D35" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="E35" t="s">
-        <v>497</v>
-      </c>
-      <c r="F35" t="s">
-        <v>456</v>
-      </c>
-      <c r="G35" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="36" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D36" t="s">
-        <v>407</v>
-      </c>
-      <c r="E36" t="s">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
       </c>
       <c r="G36" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
         <v>440</v>
       </c>
       <c r="D37" t="s">
-        <v>407</v>
-      </c>
-      <c r="E37" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F37" t="s">
         <v>456</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="38" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
         <v>440</v>
       </c>
       <c r="D38" t="s">
-        <v>407</v>
+        <v>496</v>
       </c>
       <c r="E38" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F38" t="s">
         <v>456</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>470</v>
       </c>
     </row>
     <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10403,7 +10431,10 @@
         <v>440</v>
       </c>
       <c r="D39" t="s">
-        <v>408</v>
+        <v>407</v>
+      </c>
+      <c r="E39" t="s">
+        <v>489</v>
       </c>
       <c r="F39" t="s">
         <v>456</v>
@@ -10417,7 +10448,10 @@
         <v>440</v>
       </c>
       <c r="D40" t="s">
-        <v>493</v>
+        <v>407</v>
+      </c>
+      <c r="E40" t="s">
+        <v>490</v>
       </c>
       <c r="F40" t="s">
         <v>456</v>
@@ -10431,7 +10465,10 @@
         <v>440</v>
       </c>
       <c r="D41" t="s">
-        <v>494</v>
+        <v>407</v>
+      </c>
+      <c r="E41" t="s">
+        <v>495</v>
       </c>
       <c r="F41" t="s">
         <v>456</v>
@@ -10442,13 +10479,10 @@
     </row>
     <row r="42" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C42" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D42" t="s">
-        <v>491</v>
-      </c>
-      <c r="E42" t="s">
-        <v>492</v>
+        <v>408</v>
       </c>
       <c r="F42" t="s">
         <v>456</v>
@@ -10459,7 +10493,7 @@
     </row>
     <row r="43" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C43" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D43" t="s">
         <v>493</v>
@@ -10473,7 +10507,7 @@
     </row>
     <row r="44" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D44" t="s">
         <v>494</v>
@@ -10490,7 +10524,10 @@
         <v>434</v>
       </c>
       <c r="D45" t="s">
-        <v>507</v>
+        <v>491</v>
+      </c>
+      <c r="E45" t="s">
+        <v>492</v>
       </c>
       <c r="F45" t="s">
         <v>456</v>
@@ -10501,70 +10538,112 @@
     </row>
     <row r="46" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
-        <v>484</v>
+        <v>434</v>
       </c>
       <c r="D46" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="F46" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C47" t="s">
-        <v>509</v>
+        <v>434</v>
       </c>
       <c r="D47" t="s">
-        <v>510</v>
-      </c>
-      <c r="E47" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="F47" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G47" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C48" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D48" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="F48" t="s">
         <v>456</v>
       </c>
       <c r="G48" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C49" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="D49" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="F49" t="s">
         <v>457</v>
       </c>
       <c r="G49" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C50" t="s">
+        <v>509</v>
+      </c>
+      <c r="D50" t="s">
+        <v>510</v>
+      </c>
+      <c r="E50" t="s">
+        <v>511</v>
+      </c>
+      <c r="F50" t="s">
+        <v>457</v>
+      </c>
+      <c r="G50" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C51" t="s">
+        <v>430</v>
+      </c>
+      <c r="D51" t="s">
+        <v>515</v>
+      </c>
+      <c r="F51" t="s">
+        <v>456</v>
+      </c>
+      <c r="G51" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C52" t="s">
+        <v>440</v>
+      </c>
+      <c r="D52" t="s">
+        <v>519</v>
+      </c>
+      <c r="F52" t="s">
+        <v>457</v>
+      </c>
+      <c r="G52" t="s">
         <v>470</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G49" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G52" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F49" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F52" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5738ADAC-1D66-4882-9D2C-7C1F58725151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276C6BC5-D923-4E3C-A373-486E45A0DAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2160" windowWidth="21600" windowHeight="12015" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="7485" yWindow="5700" windowWidth="22170" windowHeight="12195" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="526">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5998,17 +5998,21 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>敵のSE</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>クリアしていないシーンは表示しないように</t>
     <rPh sb="12" eb="14">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のSE,effect</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほどほどでいいかも</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6245,8 +6249,13 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G52" totalsRowShown="0">
   <autoFilter ref="C2:G52" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="高"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="4">
-      <filters blank="1">
+      <filters>
         <filter val="進行中"/>
         <filter val="未着手"/>
       </filters>
@@ -9917,7 +9926,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>433</v>
       </c>
@@ -9934,7 +9943,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
         <v>433</v>
       </c>
@@ -9985,7 +9994,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C9" t="s">
         <v>435</v>
       </c>
@@ -10036,7 +10045,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
         <v>435</v>
       </c>
@@ -10163,7 +10172,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>435</v>
       </c>
@@ -10205,7 +10214,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
         <v>435</v>
       </c>
@@ -10278,7 +10287,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
         <v>430</v>
       </c>
@@ -10288,11 +10297,14 @@
       <c r="E28" t="s">
         <v>513</v>
       </c>
+      <c r="F28" t="s">
+        <v>457</v>
+      </c>
       <c r="G28" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
         <v>484</v>
       </c>
@@ -10367,7 +10379,13 @@
         <v>484</v>
       </c>
       <c r="D34" t="s">
-        <v>524</v>
+        <v>523</v>
+      </c>
+      <c r="F34" t="s">
+        <v>456</v>
+      </c>
+      <c r="G34" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.4">
@@ -10380,13 +10398,22 @@
       <c r="E35" t="s">
         <v>522</v>
       </c>
+      <c r="F35" t="s">
+        <v>456</v>
+      </c>
+      <c r="G35" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="36" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
         <v>435</v>
       </c>
       <c r="D36" t="s">
-        <v>523</v>
+        <v>524</v>
+      </c>
+      <c r="E36" t="s">
+        <v>525</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
@@ -10592,7 +10619,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C50" t="s">
         <v>509</v>
       </c>
@@ -10609,7 +10636,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C51" t="s">
         <v>430</v>
       </c>
@@ -10620,10 +10647,10 @@
         <v>456</v>
       </c>
       <c r="G51" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C52" t="s">
         <v>440</v>
       </c>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276C6BC5-D923-4E3C-A373-486E45A0DAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2D1BB2-BA87-4469-AEB5-0373AA3EFD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7485" yWindow="5700" windowWidth="22170" windowHeight="12195" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="5265" yWindow="3435" windowWidth="22170" windowHeight="14535" firstSheet="1" activeTab="7" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="539">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5873,16 +5873,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ステージの穴にキャラを入れる</t>
-    <rPh sb="5" eb="6">
-      <t>アナ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【ステージクリアシーン】</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -6013,6 +6003,158 @@
   </si>
   <si>
     <t>ほどほどでいいかも</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【残っていること】</t>
+    <rPh sb="1" eb="2">
+      <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス戦などでのBgm変え</t>
+    <rPh sb="2" eb="3">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーンのタイトルロゴをパって出るのをやめる</t>
+    <rPh sb="18" eb="19">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハートの数を増やす</t>
+    <rPh sb="4" eb="5">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIの幅を調整</t>
+    <rPh sb="3" eb="4">
+      <t>ハバ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップのだんだん落ちてきちゃう場所を調整</t>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復した時の音が連続しているので、それをやめる</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>レンゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクトの初期化(川の先生の時に聞く)</t>
+    <rPh sb="6" eb="9">
+      <t>ショキカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カワ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤いステージクリアしたらステージクリアシーンに行くようにする</t>
+    <rPh sb="0" eb="1">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージクリアシーンを作る</t>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なくてもいい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズシーン起動時の音</t>
+    <rPh sb="6" eb="8">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズシーン終了時の音</t>
+    <rPh sb="6" eb="8">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は音量調節をできるようにする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>オンリョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チョウセツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6249,11 +6391,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G52" totalsRowShown="0">
   <autoFilter ref="C2:G52" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="高"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="4">
       <filters>
         <filter val="進行中"/>
@@ -7706,7 +7843,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7C460-8E59-4ECD-A44D-FCBDC7001F49}">
-  <dimension ref="B2:C319"/>
+  <dimension ref="B2:C321"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -9396,7 +9533,7 @@
         <v>46041</v>
       </c>
       <c r="C317" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="319" spans="2:3" x14ac:dyDescent="0.4">
@@ -9404,7 +9541,15 @@
         <v>46042</v>
       </c>
       <c r="C319" t="s">
-        <v>517</v>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B321" s="9">
+        <v>46044</v>
+      </c>
+      <c r="C321" t="s">
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -9869,7 +10014,7 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
-    <col min="4" max="4" width="39.5" customWidth="1"/>
+    <col min="4" max="4" width="40.625" customWidth="1"/>
     <col min="5" max="5" width="39.875" customWidth="1"/>
     <col min="6" max="6" width="19.25" customWidth="1"/>
     <col min="7" max="7" width="15.375" customWidth="1"/>
@@ -9926,7 +10071,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>433</v>
       </c>
@@ -9943,7 +10088,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="6" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
         <v>433</v>
       </c>
@@ -9994,7 +10139,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="9" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C9" t="s">
         <v>435</v>
       </c>
@@ -10045,7 +10190,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
         <v>435</v>
       </c>
@@ -10135,13 +10280,13 @@
         <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="F17" t="s">
         <v>456</v>
       </c>
       <c r="G17" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10172,7 +10317,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>435</v>
       </c>
@@ -10200,18 +10345,18 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
         <v>435</v>
       </c>
       <c r="D22" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F22" t="s">
         <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>483</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10219,7 +10364,7 @@
         <v>435</v>
       </c>
       <c r="D23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F23" t="s">
         <v>456</v>
@@ -10287,24 +10432,24 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
         <v>430</v>
       </c>
       <c r="D28" t="s">
+        <v>511</v>
+      </c>
+      <c r="E28" t="s">
         <v>512</v>
-      </c>
-      <c r="E28" t="s">
-        <v>513</v>
       </c>
       <c r="F28" t="s">
         <v>457</v>
       </c>
       <c r="G28" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
         <v>484</v>
       </c>
@@ -10379,7 +10524,7 @@
         <v>484</v>
       </c>
       <c r="D34" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F34" t="s">
         <v>456</v>
@@ -10390,13 +10535,13 @@
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
+        <v>519</v>
+      </c>
+      <c r="D35" t="s">
         <v>520</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>521</v>
-      </c>
-      <c r="E35" t="s">
-        <v>522</v>
       </c>
       <c r="F35" t="s">
         <v>456</v>
@@ -10410,10 +10555,10 @@
         <v>435</v>
       </c>
       <c r="D36" t="s">
+        <v>523</v>
+      </c>
+      <c r="E36" t="s">
         <v>524</v>
-      </c>
-      <c r="E36" t="s">
-        <v>525</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
@@ -10619,15 +10764,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C50" t="s">
+        <v>508</v>
+      </c>
+      <c r="D50" t="s">
         <v>509</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>510</v>
-      </c>
-      <c r="E50" t="s">
-        <v>511</v>
       </c>
       <c r="F50" t="s">
         <v>457</v>
@@ -10641,7 +10786,7 @@
         <v>430</v>
       </c>
       <c r="D51" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F51" t="s">
         <v>456</v>
@@ -10650,12 +10795,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C52" t="s">
         <v>440</v>
       </c>
       <c r="D52" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F52" t="s">
         <v>457</v>
@@ -10683,11 +10828,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043CC552-7D3A-4DC6-8319-C35A74AECC01}">
-  <dimension ref="B1:E4"/>
+  <dimension ref="B1:E17"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="4" max="4" width="48.125" customWidth="1"/>
+    <col min="3" max="3" width="18.625" customWidth="1"/>
+    <col min="4" max="4" width="61.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.4">
@@ -10711,6 +10857,73 @@
         <v>445</v>
       </c>
     </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>525</v>
+      </c>
+      <c r="D6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D7" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D8" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D9" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D10" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D11" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D12" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>535</v>
+      </c>
+      <c r="D14" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C15" t="s">
+        <v>535</v>
+      </c>
+      <c r="D15" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D16" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D17" t="s">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2D1BB2-BA87-4469-AEB5-0373AA3EFD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D715B32-24D4-402B-86FD-3C3EC423E831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5265" yWindow="3435" windowWidth="22170" windowHeight="14535" firstSheet="1" activeTab="7" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="540">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -6154,6 +6154,19 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>チョウセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェードの時間をもう少し長くする</t>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6389,8 +6402,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G52" totalsRowShown="0">
-  <autoFilter ref="C2:G52" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G53" totalsRowShown="0">
+  <autoFilter ref="C2:G53" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
     <filterColumn colId="4">
       <filters>
         <filter val="進行中"/>
@@ -10010,7 +10023,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G52"/>
+  <dimension ref="C2:G53"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33.5" customWidth="1"/>
@@ -10133,7 +10146,7 @@
         <v>473</v>
       </c>
       <c r="F8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G8" t="s">
         <v>470</v>
@@ -10434,47 +10447,47 @@
     </row>
     <row r="28" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D28" t="s">
-        <v>511</v>
-      </c>
-      <c r="E28" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="F28" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G28" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
-        <v>484</v>
+        <v>430</v>
       </c>
       <c r="D29" t="s">
-        <v>485</v>
+        <v>511</v>
+      </c>
+      <c r="E29" t="s">
+        <v>512</v>
       </c>
       <c r="F29" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G29" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="30" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
         <v>484</v>
       </c>
       <c r="D30" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F30" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G30" t="s">
-        <v>101</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10482,7 +10495,7 @@
         <v>484</v>
       </c>
       <c r="D31" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="F31" t="s">
         <v>456</v>
@@ -10496,7 +10509,7 @@
         <v>484</v>
       </c>
       <c r="D32" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F32" t="s">
         <v>456</v>
@@ -10507,10 +10520,10 @@
     </row>
     <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="D33" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F33" t="s">
         <v>456</v>
@@ -10519,29 +10532,26 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C34" t="s">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="D34" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="F34" t="s">
         <v>456</v>
       </c>
       <c r="G34" t="s">
-        <v>470</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
-        <v>519</v>
+        <v>484</v>
       </c>
       <c r="D35" t="s">
-        <v>520</v>
-      </c>
-      <c r="E35" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F35" t="s">
         <v>456</v>
@@ -10552,13 +10562,13 @@
     </row>
     <row r="36" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>435</v>
+        <v>519</v>
       </c>
       <c r="D36" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E36" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F36" t="s">
         <v>456</v>
@@ -10569,16 +10579,19 @@
     </row>
     <row r="37" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D37" t="s">
-        <v>488</v>
+        <v>523</v>
+      </c>
+      <c r="E37" t="s">
+        <v>524</v>
       </c>
       <c r="F37" t="s">
         <v>456</v>
       </c>
       <c r="G37" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
     </row>
     <row r="38" spans="3:7" x14ac:dyDescent="0.4">
@@ -10586,33 +10599,30 @@
         <v>440</v>
       </c>
       <c r="D38" t="s">
-        <v>496</v>
-      </c>
-      <c r="E38" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F38" t="s">
         <v>456</v>
       </c>
       <c r="G38" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="39" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
         <v>440</v>
       </c>
       <c r="D39" t="s">
-        <v>407</v>
+        <v>496</v>
       </c>
       <c r="E39" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F39" t="s">
         <v>456</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10623,7 +10633,7 @@
         <v>407</v>
       </c>
       <c r="E40" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F40" t="s">
         <v>456</v>
@@ -10640,7 +10650,7 @@
         <v>407</v>
       </c>
       <c r="E41" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F41" t="s">
         <v>456</v>
@@ -10654,7 +10664,10 @@
         <v>440</v>
       </c>
       <c r="D42" t="s">
-        <v>408</v>
+        <v>407</v>
+      </c>
+      <c r="E42" t="s">
+        <v>495</v>
       </c>
       <c r="F42" t="s">
         <v>456</v>
@@ -10668,7 +10681,7 @@
         <v>440</v>
       </c>
       <c r="D43" t="s">
-        <v>493</v>
+        <v>408</v>
       </c>
       <c r="F43" t="s">
         <v>456</v>
@@ -10682,7 +10695,7 @@
         <v>440</v>
       </c>
       <c r="D44" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F44" t="s">
         <v>456</v>
@@ -10693,13 +10706,10 @@
     </row>
     <row r="45" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D45" t="s">
-        <v>491</v>
-      </c>
-      <c r="E45" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F45" t="s">
         <v>456</v>
@@ -10713,7 +10723,10 @@
         <v>434</v>
       </c>
       <c r="D46" t="s">
-        <v>493</v>
+        <v>491</v>
+      </c>
+      <c r="E46" t="s">
+        <v>492</v>
       </c>
       <c r="F46" t="s">
         <v>456</v>
@@ -10727,7 +10740,7 @@
         <v>434</v>
       </c>
       <c r="D47" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F47" t="s">
         <v>456</v>
@@ -10741,7 +10754,7 @@
         <v>434</v>
       </c>
       <c r="D48" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="F48" t="s">
         <v>456</v>
@@ -10752,70 +10765,84 @@
     </row>
     <row r="49" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C49" t="s">
-        <v>484</v>
+        <v>434</v>
       </c>
       <c r="D49" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F49" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G49" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C50" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="D50" t="s">
-        <v>509</v>
-      </c>
-      <c r="E50" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="F50" t="s">
         <v>457</v>
       </c>
       <c r="G50" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C51" t="s">
+        <v>508</v>
+      </c>
+      <c r="D51" t="s">
+        <v>509</v>
+      </c>
+      <c r="E51" t="s">
+        <v>510</v>
+      </c>
+      <c r="F51" t="s">
+        <v>457</v>
+      </c>
+      <c r="G51" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="51" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="C51" t="s">
+    <row r="52" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C52" t="s">
         <v>430</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>514</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F52" t="s">
         <v>456</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G52" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C52" t="s">
+    <row r="53" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C53" t="s">
         <v>440</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>518</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F53" t="s">
         <v>457</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G53" t="s">
         <v>470</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G52" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G53" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F52" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F53" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D715B32-24D4-402B-86FD-3C3EC423E831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A36B6F-C840-451F-BFFD-659DA386ACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="7" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="543">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5364,22 +5364,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>フェードを真っ黒にして数秒待ってから表示する</t>
-    <rPh sb="5" eb="6">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>スウビョウマ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マップ、フェード</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -6050,54 +6034,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>マップのだんだん落ちてきちゃう場所を調整</t>
-    <rPh sb="8" eb="9">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>チョウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>回復した時の音が連続しているので、それをやめる</t>
-    <rPh sb="0" eb="2">
-      <t>カイフク</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>レンゾク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エフェクトの初期化(川の先生の時に聞く)</t>
-    <rPh sb="6" eb="9">
-      <t>ショキカ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>カワ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センセイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>赤いステージクリアしたらステージクリアシーンに行くようにする</t>
     <rPh sb="0" eb="1">
       <t>アカ</t>
@@ -6167,6 +6103,85 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスを倒したら、SEを入れる</t>
+    <rPh sb="3" eb="4">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→あとは、熊と狼の部屋だけ</t>
+    <rPh sb="5" eb="6">
+      <t>クマ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オオカミ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロゴ出るまでが長い</t>
+    <rPh sb="2" eb="3">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器庫のマークがわかりづらいので、変える</t>
+    <rPh sb="0" eb="3">
+      <t>ブキコ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>波動の位置が地面に埋まっている</t>
+    <rPh sb="0" eb="2">
+      <t>ハドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドアを出すときのエフェクト</t>
+    <rPh sb="3" eb="4">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドアの看板（上キー）がわかりにくいので修正したい</t>
+    <rPh sb="3" eb="5">
+      <t>カンバン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9491,17 +9506,17 @@
         <v>46032</v>
       </c>
       <c r="C309" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="310" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C310" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="311" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C311" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="312" spans="2:3" x14ac:dyDescent="0.4">
@@ -9509,7 +9524,7 @@
         <v>46034</v>
       </c>
       <c r="C312" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="313" spans="2:3" x14ac:dyDescent="0.4">
@@ -9517,7 +9532,7 @@
         <v>46035</v>
       </c>
       <c r="C313" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="314" spans="2:3" x14ac:dyDescent="0.4">
@@ -9525,7 +9540,7 @@
         <v>46036</v>
       </c>
       <c r="C314" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="315" spans="2:3" x14ac:dyDescent="0.4">
@@ -9533,12 +9548,12 @@
         <v>46039</v>
       </c>
       <c r="C315" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="316" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C316" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="317" spans="2:3" x14ac:dyDescent="0.4">
@@ -9546,7 +9561,7 @@
         <v>46041</v>
       </c>
       <c r="C317" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="319" spans="2:3" x14ac:dyDescent="0.4">
@@ -9554,7 +9569,7 @@
         <v>46042</v>
       </c>
       <c r="C319" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="321" spans="2:3" x14ac:dyDescent="0.4">
@@ -9562,7 +9577,7 @@
         <v>46044</v>
       </c>
       <c r="C321" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -9783,7 +9798,7 @@
         <v>401</v>
       </c>
       <c r="D5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E5" t="s">
         <v>424</v>
@@ -9794,7 +9809,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="D6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
@@ -9808,15 +9823,15 @@
         <v>426</v>
       </c>
       <c r="F7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
@@ -9927,7 +9942,7 @@
         <v>407</v>
       </c>
       <c r="E25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
@@ -9958,7 +9973,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E30" t="s">
         <v>429</v>
@@ -10026,6 +10041,8 @@
   <dimension ref="C2:G53"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="3" width="33.5" customWidth="1"/>
     <col min="4" max="4" width="40.625" customWidth="1"/>
     <col min="5" max="5" width="39.875" customWidth="1"/>
@@ -10035,19 +10052,19 @@
   <sheetData>
     <row r="2" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D2" t="s">
         <v>459</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>460</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>461</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>462</v>
-      </c>
-      <c r="G2" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="3" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10055,16 +10072,16 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E3" t="s">
         <v>464</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>465</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>466</v>
-      </c>
-      <c r="G3" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="4" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10072,13 +10089,13 @@
         <v>433</v>
       </c>
       <c r="D4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E4" t="s">
         <v>468</v>
       </c>
-      <c r="E4" t="s">
-        <v>469</v>
-      </c>
       <c r="F4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G4" t="s">
         <v>101</v>
@@ -10095,10 +10112,10 @@
         <v>421</v>
       </c>
       <c r="F5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.4">
@@ -10109,13 +10126,13 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10126,10 +10143,10 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G7" t="s">
         <v>101</v>
@@ -10143,13 +10160,13 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.4">
@@ -10160,13 +10177,13 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10177,10 +10194,10 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G10" t="s">
         <v>101</v>
@@ -10194,10 +10211,10 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G11" t="s">
         <v>101</v>
@@ -10211,13 +10228,13 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10225,13 +10242,13 @@
         <v>435</v>
       </c>
       <c r="D13" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G13" t="s">
         <v>101</v>
@@ -10245,10 +10262,10 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G14" t="s">
         <v>101</v>
@@ -10259,16 +10276,16 @@
         <v>435</v>
       </c>
       <c r="D15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10276,30 +10293,30 @@
         <v>435</v>
       </c>
       <c r="D16" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G16" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
         <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G17" t="s">
-        <v>483</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10307,10 +10324,10 @@
         <v>435</v>
       </c>
       <c r="D18" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G18" t="s">
         <v>101</v>
@@ -10321,10 +10338,10 @@
         <v>435</v>
       </c>
       <c r="D19" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G19" t="s">
         <v>101</v>
@@ -10335,13 +10352,13 @@
         <v>435</v>
       </c>
       <c r="D20" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10349,10 +10366,10 @@
         <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G21" t="s">
         <v>101</v>
@@ -10363,10 +10380,10 @@
         <v>435</v>
       </c>
       <c r="D22" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F22" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G22" t="s">
         <v>101</v>
@@ -10377,10 +10394,10 @@
         <v>435</v>
       </c>
       <c r="D23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F23" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G23" t="s">
         <v>101</v>
@@ -10391,10 +10408,10 @@
         <v>435</v>
       </c>
       <c r="D24" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G24" t="s">
         <v>101</v>
@@ -10402,13 +10419,13 @@
     </row>
     <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C25" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D25" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F25" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G25" t="s">
         <v>101</v>
@@ -10416,13 +10433,13 @@
     </row>
     <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D26" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F26" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G26" t="s">
         <v>101</v>
@@ -10430,47 +10447,47 @@
     </row>
     <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D27" t="s">
         <v>407</v>
       </c>
       <c r="E27" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F27" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G27" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
         <v>435</v>
       </c>
       <c r="D28" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F28" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G28" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
         <v>430</v>
       </c>
       <c r="D29" t="s">
+        <v>510</v>
+      </c>
+      <c r="E29" t="s">
         <v>511</v>
       </c>
-      <c r="E29" t="s">
-        <v>512</v>
-      </c>
       <c r="F29" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G29" t="s">
         <v>101</v>
@@ -10478,27 +10495,27 @@
     </row>
     <row r="30" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
+        <v>483</v>
+      </c>
+      <c r="D30" t="s">
         <v>484</v>
       </c>
-      <c r="D30" t="s">
-        <v>485</v>
-      </c>
       <c r="F30" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G30" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D31" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G31" t="s">
         <v>101</v>
@@ -10506,13 +10523,13 @@
     </row>
     <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D32" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F32" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G32" t="s">
         <v>101</v>
@@ -10520,13 +10537,13 @@
     </row>
     <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F33" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G33" t="s">
         <v>101</v>
@@ -10537,10 +10554,10 @@
         <v>440</v>
       </c>
       <c r="D34" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F34" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G34" t="s">
         <v>101</v>
@@ -10548,33 +10565,33 @@
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D35" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F35" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G35" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="36" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
+        <v>518</v>
+      </c>
+      <c r="D36" t="s">
         <v>519</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>520</v>
       </c>
-      <c r="E36" t="s">
-        <v>521</v>
-      </c>
       <c r="F36" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G36" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="37" spans="3:7" x14ac:dyDescent="0.4">
@@ -10582,16 +10599,16 @@
         <v>435</v>
       </c>
       <c r="D37" t="s">
+        <v>522</v>
+      </c>
+      <c r="E37" t="s">
         <v>523</v>
       </c>
-      <c r="E37" t="s">
-        <v>524</v>
-      </c>
       <c r="F37" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G37" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="38" spans="3:7" x14ac:dyDescent="0.4">
@@ -10599,13 +10616,13 @@
         <v>440</v>
       </c>
       <c r="D38" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F38" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G38" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="39" spans="3:7" x14ac:dyDescent="0.4">
@@ -10613,16 +10630,16 @@
         <v>440</v>
       </c>
       <c r="D39" t="s">
+        <v>495</v>
+      </c>
+      <c r="E39" t="s">
         <v>496</v>
       </c>
-      <c r="E39" t="s">
-        <v>497</v>
-      </c>
       <c r="F39" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G39" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10633,10 +10650,10 @@
         <v>407</v>
       </c>
       <c r="E40" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G40" t="s">
         <v>101</v>
@@ -10650,10 +10667,10 @@
         <v>407</v>
       </c>
       <c r="E41" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F41" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -10667,10 +10684,10 @@
         <v>407</v>
       </c>
       <c r="E42" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F42" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -10684,7 +10701,7 @@
         <v>408</v>
       </c>
       <c r="F43" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -10695,10 +10712,10 @@
         <v>440</v>
       </c>
       <c r="D44" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F44" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -10709,10 +10726,10 @@
         <v>440</v>
       </c>
       <c r="D45" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -10723,13 +10740,13 @@
         <v>434</v>
       </c>
       <c r="D46" t="s">
+        <v>490</v>
+      </c>
+      <c r="E46" t="s">
         <v>491</v>
       </c>
-      <c r="E46" t="s">
-        <v>492</v>
-      </c>
       <c r="F46" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -10740,10 +10757,10 @@
         <v>434</v>
       </c>
       <c r="D47" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F47" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -10754,10 +10771,10 @@
         <v>434</v>
       </c>
       <c r="D48" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F48" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G48" t="s">
         <v>101</v>
@@ -10768,10 +10785,10 @@
         <v>434</v>
       </c>
       <c r="D49" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F49" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G49" t="s">
         <v>101</v>
@@ -10779,13 +10796,13 @@
     </row>
     <row r="50" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C50" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D50" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F50" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G50" t="s">
         <v>101</v>
@@ -10793,19 +10810,19 @@
     </row>
     <row r="51" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C51" t="s">
+        <v>507</v>
+      </c>
+      <c r="D51" t="s">
         <v>508</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>509</v>
       </c>
-      <c r="E51" t="s">
-        <v>510</v>
-      </c>
       <c r="F51" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G51" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="52" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10813,10 +10830,10 @@
         <v>430</v>
       </c>
       <c r="D52" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F52" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G52" t="s">
         <v>101</v>
@@ -10827,13 +10844,13 @@
         <v>440</v>
       </c>
       <c r="D53" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F53" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G53" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -10855,7 +10872,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043CC552-7D3A-4DC6-8319-C35A74AECC01}">
-  <dimension ref="B1:E17"/>
+  <dimension ref="B1:E20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="21.5" customWidth="1"/>
@@ -10881,64 +10898,66 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D4" t="s">
-        <v>445</v>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D5" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D6" t="s">
         <v>525</v>
-      </c>
-      <c r="D6" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D10" t="s">
-        <v>530</v>
+      <c r="C10" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
-        <v>435</v>
+        <v>531</v>
       </c>
       <c r="D11" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D13" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="C14" t="s">
-        <v>535</v>
-      </c>
       <c r="D14" t="s">
         <v>533</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="C15" t="s">
-        <v>535</v>
-      </c>
-      <c r="D15" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.4">
@@ -10949,6 +10968,21 @@
     <row r="17" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
         <v>537</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D18" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D19" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.4">
+      <c r="D20" t="s">
+        <v>542</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A36B6F-C840-451F-BFFD-659DA386ACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289D042C-E550-4ADA-A9B2-04047B469286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="7" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="4965" yWindow="1560" windowWidth="24840" windowHeight="15210" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="541">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -6052,32 +6052,6 @@
   </si>
   <si>
     <t>なくてもいい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ポーズシーン起動時の音</t>
-    <rPh sb="6" eb="8">
-      <t>キドウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ポーズシーン終了時の音</t>
-    <rPh sb="6" eb="8">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オト</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -9577,7 +9551,7 @@
         <v>46044</v>
       </c>
       <c r="C321" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -10467,7 +10441,7 @@
         <v>435</v>
       </c>
       <c r="D28" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F28" t="s">
         <v>455</v>
@@ -10898,12 +10872,12 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
@@ -10950,39 +10924,29 @@
         <v>530</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D13" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D14" t="s">
-        <v>533</v>
-      </c>
-    </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="D16" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D18" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D20" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289D042C-E550-4ADA-A9B2-04047B469286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8B98BC-D177-4B8D-B0E9-CFB82B56B59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4965" yWindow="1560" windowWidth="24840" windowHeight="15210" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="542">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -6155,6 +6155,22 @@
       <t>ウエ</t>
     </rPh>
     <rPh sb="19" eb="21">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初の上十字キーのUiが見づらいので修正</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ウエジュウジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
       <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -6391,8 +6407,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G53" totalsRowShown="0">
-  <autoFilter ref="C2:G53" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}" name="テーブル4" displayName="テーブル4" ref="C2:G54" totalsRowShown="0">
+  <autoFilter ref="C2:G54" xr:uid="{E98803B4-4207-430E-940A-827B5EBAEF7B}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="高"/>
+        <filter val="中"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="4">
       <filters>
         <filter val="進行中"/>
@@ -10012,7 +10034,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F15660-75A5-4552-920B-33098E62048E}">
-  <dimension ref="C2:G53"/>
+  <dimension ref="C2:G54"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
@@ -10075,7 +10097,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>433</v>
       </c>
@@ -10194,7 +10216,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
         <v>435</v>
       </c>
@@ -10208,7 +10230,7 @@
         <v>456</v>
       </c>
       <c r="G12" t="s">
-        <v>469</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10321,7 +10343,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>435</v>
       </c>
@@ -10469,16 +10491,16 @@
     </row>
     <row r="30" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>483</v>
+        <v>435</v>
       </c>
       <c r="D30" t="s">
-        <v>484</v>
+        <v>541</v>
       </c>
       <c r="F30" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G30" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10486,13 +10508,13 @@
         <v>483</v>
       </c>
       <c r="D31" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G31" t="s">
-        <v>101</v>
+        <v>469</v>
       </c>
     </row>
     <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10500,7 +10522,7 @@
         <v>483</v>
       </c>
       <c r="D32" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="F32" t="s">
         <v>455</v>
@@ -10514,7 +10536,7 @@
         <v>483</v>
       </c>
       <c r="D33" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F33" t="s">
         <v>455</v>
@@ -10525,10 +10547,10 @@
     </row>
     <row r="34" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C34" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="D34" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F34" t="s">
         <v>455</v>
@@ -10537,63 +10559,63 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
-        <v>483</v>
+        <v>440</v>
       </c>
       <c r="D35" t="s">
-        <v>521</v>
+        <v>486</v>
       </c>
       <c r="F35" t="s">
         <v>455</v>
       </c>
       <c r="G35" t="s">
-        <v>469</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>518</v>
+        <v>483</v>
       </c>
       <c r="D36" t="s">
-        <v>519</v>
-      </c>
-      <c r="E36" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F36" t="s">
         <v>455</v>
       </c>
       <c r="G36" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.4">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
-        <v>435</v>
+        <v>518</v>
       </c>
       <c r="D37" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E37" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F37" t="s">
         <v>455</v>
       </c>
       <c r="G37" t="s">
-        <v>482</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D38" t="s">
-        <v>487</v>
+        <v>522</v>
+      </c>
+      <c r="E38" t="s">
+        <v>523</v>
       </c>
       <c r="F38" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G38" t="s">
         <v>482</v>
@@ -10604,33 +10626,30 @@
         <v>440</v>
       </c>
       <c r="D39" t="s">
-        <v>495</v>
-      </c>
-      <c r="E39" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="F39" t="s">
         <v>455</v>
       </c>
       <c r="G39" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="40" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
         <v>440</v>
       </c>
       <c r="D40" t="s">
-        <v>407</v>
+        <v>495</v>
       </c>
       <c r="E40" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F40" t="s">
         <v>455</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>469</v>
       </c>
     </row>
     <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10641,7 +10660,7 @@
         <v>407</v>
       </c>
       <c r="E41" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F41" t="s">
         <v>455</v>
@@ -10658,7 +10677,7 @@
         <v>407</v>
       </c>
       <c r="E42" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F42" t="s">
         <v>455</v>
@@ -10672,7 +10691,10 @@
         <v>440</v>
       </c>
       <c r="D43" t="s">
-        <v>408</v>
+        <v>407</v>
+      </c>
+      <c r="E43" t="s">
+        <v>494</v>
       </c>
       <c r="F43" t="s">
         <v>455</v>
@@ -10686,7 +10708,7 @@
         <v>440</v>
       </c>
       <c r="D44" t="s">
-        <v>492</v>
+        <v>408</v>
       </c>
       <c r="F44" t="s">
         <v>455</v>
@@ -10700,7 +10722,7 @@
         <v>440</v>
       </c>
       <c r="D45" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F45" t="s">
         <v>455</v>
@@ -10711,13 +10733,10 @@
     </row>
     <row r="46" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D46" t="s">
-        <v>490</v>
-      </c>
-      <c r="E46" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F46" t="s">
         <v>455</v>
@@ -10731,7 +10750,10 @@
         <v>434</v>
       </c>
       <c r="D47" t="s">
-        <v>492</v>
+        <v>490</v>
+      </c>
+      <c r="E47" t="s">
+        <v>491</v>
       </c>
       <c r="F47" t="s">
         <v>455</v>
@@ -10745,7 +10767,7 @@
         <v>434</v>
       </c>
       <c r="D48" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F48" t="s">
         <v>455</v>
@@ -10759,7 +10781,7 @@
         <v>434</v>
       </c>
       <c r="D49" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="F49" t="s">
         <v>455</v>
@@ -10770,70 +10792,84 @@
     </row>
     <row r="50" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C50" t="s">
-        <v>483</v>
+        <v>434</v>
       </c>
       <c r="D50" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F50" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G50" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C51" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="D51" t="s">
-        <v>508</v>
-      </c>
-      <c r="E51" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="F51" t="s">
         <v>456</v>
       </c>
       <c r="G51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C52" t="s">
+        <v>507</v>
+      </c>
+      <c r="D52" t="s">
+        <v>508</v>
+      </c>
+      <c r="E52" t="s">
+        <v>509</v>
+      </c>
+      <c r="F52" t="s">
+        <v>456</v>
+      </c>
+      <c r="G52" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="52" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="C52" t="s">
+    <row r="53" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="C53" t="s">
         <v>430</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>513</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F53" t="s">
         <v>455</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G53" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C53" t="s">
+    <row r="54" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C54" t="s">
         <v>440</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>517</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F54" t="s">
         <v>456</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G54" t="s">
         <v>469</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G53" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G54" xr:uid="{D8FD478A-16FD-461A-8D13-75C1B339E936}">
       <formula1>"完了,進行中,未着手"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F53" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F54" xr:uid="{0F997A19-EC74-4A04-B018-AB069E38C461}">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8B98BC-D177-4B8D-B0E9-CFB82B56B59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3192938B-BE51-489C-9DF5-C5466B3DC8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4965" yWindow="1560" windowWidth="24840" windowHeight="15210" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6900" yWindow="4965" windowWidth="24840" windowHeight="11820" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="537">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5357,13 +5357,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゲームおーばは三機にする</t>
-    <rPh sb="7" eb="9">
-      <t>サンキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マップ、フェード</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -6024,16 +6017,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>UIの幅を調整</t>
-    <rPh sb="3" eb="4">
-      <t>ハバ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>チョウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>赤いステージクリアしたらステージクリアシーンに行くようにする</t>
     <rPh sb="0" eb="1">
       <t>アカ</t>
@@ -6081,29 +6064,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ボスを倒したら、SEを入れる</t>
-    <rPh sb="3" eb="4">
-      <t>タオ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>→あとは、熊と狼の部屋だけ</t>
-    <rPh sb="5" eb="6">
-      <t>クマ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オオカミ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヘヤ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ロゴ出るまでが長い</t>
     <rPh sb="2" eb="3">
       <t>デ</t>
@@ -6120,22 +6080,6 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>波動の位置が地面に埋まっている</t>
-    <rPh sb="0" eb="2">
-      <t>ハドウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジメン</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9502,17 +9446,17 @@
         <v>46032</v>
       </c>
       <c r="C309" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="310" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C310" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="311" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C311" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="312" spans="2:3" x14ac:dyDescent="0.4">
@@ -9520,7 +9464,7 @@
         <v>46034</v>
       </c>
       <c r="C312" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="313" spans="2:3" x14ac:dyDescent="0.4">
@@ -9528,7 +9472,7 @@
         <v>46035</v>
       </c>
       <c r="C313" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="314" spans="2:3" x14ac:dyDescent="0.4">
@@ -9536,7 +9480,7 @@
         <v>46036</v>
       </c>
       <c r="C314" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="315" spans="2:3" x14ac:dyDescent="0.4">
@@ -9544,12 +9488,12 @@
         <v>46039</v>
       </c>
       <c r="C315" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="316" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C316" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="317" spans="2:3" x14ac:dyDescent="0.4">
@@ -9557,7 +9501,7 @@
         <v>46041</v>
       </c>
       <c r="C317" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="319" spans="2:3" x14ac:dyDescent="0.4">
@@ -9565,7 +9509,7 @@
         <v>46042</v>
       </c>
       <c r="C319" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="321" spans="2:3" x14ac:dyDescent="0.4">
@@ -9573,7 +9517,7 @@
         <v>46044</v>
       </c>
       <c r="C321" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -9794,7 +9738,7 @@
         <v>401</v>
       </c>
       <c r="D5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E5" t="s">
         <v>424</v>
@@ -9805,7 +9749,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="D6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
@@ -9819,15 +9763,15 @@
         <v>426</v>
       </c>
       <c r="F7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
@@ -9938,7 +9882,7 @@
         <v>407</v>
       </c>
       <c r="E25" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
@@ -9969,7 +9913,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E30" t="s">
         <v>429</v>
@@ -10048,19 +9992,19 @@
   <sheetData>
     <row r="2" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D2" t="s">
         <v>458</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>459</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>460</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>461</v>
-      </c>
-      <c r="G2" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="3" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10068,16 +10012,16 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E3" t="s">
         <v>463</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>464</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>465</v>
-      </c>
-      <c r="G3" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="4" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10085,13 +10029,13 @@
         <v>433</v>
       </c>
       <c r="D4" t="s">
+        <v>466</v>
+      </c>
+      <c r="E4" t="s">
         <v>467</v>
       </c>
-      <c r="E4" t="s">
-        <v>468</v>
-      </c>
       <c r="F4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G4" t="s">
         <v>101</v>
@@ -10108,10 +10052,10 @@
         <v>421</v>
       </c>
       <c r="F5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.4">
@@ -10122,13 +10066,13 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10139,10 +10083,10 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G7" t="s">
         <v>101</v>
@@ -10156,13 +10100,13 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.4">
@@ -10173,13 +10117,13 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10190,10 +10134,10 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G10" t="s">
         <v>101</v>
@@ -10207,10 +10151,10 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F11" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G11" t="s">
         <v>101</v>
@@ -10224,10 +10168,10 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F12" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G12" t="s">
         <v>101</v>
@@ -10238,13 +10182,13 @@
         <v>435</v>
       </c>
       <c r="D13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G13" t="s">
         <v>101</v>
@@ -10258,10 +10202,10 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G14" t="s">
         <v>101</v>
@@ -10272,16 +10216,16 @@
         <v>435</v>
       </c>
       <c r="D15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10289,13 +10233,13 @@
         <v>435</v>
       </c>
       <c r="D16" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G16" t="s">
         <v>101</v>
@@ -10306,10 +10250,10 @@
         <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G17" t="s">
         <v>101</v>
@@ -10320,10 +10264,10 @@
         <v>435</v>
       </c>
       <c r="D18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G18" t="s">
         <v>101</v>
@@ -10334,10 +10278,10 @@
         <v>435</v>
       </c>
       <c r="D19" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F19" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G19" t="s">
         <v>101</v>
@@ -10348,13 +10292,13 @@
         <v>435</v>
       </c>
       <c r="D20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F20" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G20" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="21" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10362,10 +10306,10 @@
         <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F21" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G21" t="s">
         <v>101</v>
@@ -10376,10 +10320,10 @@
         <v>435</v>
       </c>
       <c r="D22" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G22" t="s">
         <v>101</v>
@@ -10390,10 +10334,10 @@
         <v>435</v>
       </c>
       <c r="D23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F23" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G23" t="s">
         <v>101</v>
@@ -10404,10 +10348,10 @@
         <v>435</v>
       </c>
       <c r="D24" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F24" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G24" t="s">
         <v>101</v>
@@ -10415,13 +10359,13 @@
     </row>
     <row r="25" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C25" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D25" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F25" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G25" t="s">
         <v>101</v>
@@ -10429,13 +10373,13 @@
     </row>
     <row r="26" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G26" t="s">
         <v>101</v>
@@ -10443,16 +10387,16 @@
     </row>
     <row r="27" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D27" t="s">
         <v>407</v>
       </c>
       <c r="E27" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F27" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G27" t="s">
         <v>101</v>
@@ -10463,10 +10407,10 @@
         <v>435</v>
       </c>
       <c r="D28" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F28" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G28" t="s">
         <v>101</v>
@@ -10477,13 +10421,13 @@
         <v>430</v>
       </c>
       <c r="D29" t="s">
+        <v>509</v>
+      </c>
+      <c r="E29" t="s">
         <v>510</v>
       </c>
-      <c r="E29" t="s">
-        <v>511</v>
-      </c>
       <c r="F29" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G29" t="s">
         <v>101</v>
@@ -10494,38 +10438,38 @@
         <v>435</v>
       </c>
       <c r="D30" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F30" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G30" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="31" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
+        <v>482</v>
+      </c>
+      <c r="D31" t="s">
         <v>483</v>
       </c>
-      <c r="D31" t="s">
-        <v>484</v>
-      </c>
       <c r="F31" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G31" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D32" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F32" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G32" t="s">
         <v>101</v>
@@ -10533,13 +10477,13 @@
     </row>
     <row r="33" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D33" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F33" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G33" t="s">
         <v>101</v>
@@ -10547,13 +10491,13 @@
     </row>
     <row r="34" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C34" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D34" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F34" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G34" t="s">
         <v>101</v>
@@ -10564,10 +10508,10 @@
         <v>440</v>
       </c>
       <c r="D35" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F35" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G35" t="s">
         <v>101</v>
@@ -10575,30 +10519,30 @@
     </row>
     <row r="36" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D36" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F36" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G36" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="37" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
+        <v>517</v>
+      </c>
+      <c r="D37" t="s">
         <v>518</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>519</v>
       </c>
-      <c r="E37" t="s">
-        <v>520</v>
-      </c>
       <c r="F37" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G37" t="s">
         <v>101</v>
@@ -10609,16 +10553,16 @@
         <v>435</v>
       </c>
       <c r="D38" t="s">
+        <v>521</v>
+      </c>
+      <c r="E38" t="s">
         <v>522</v>
       </c>
-      <c r="E38" t="s">
-        <v>523</v>
-      </c>
       <c r="F38" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G38" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="39" spans="3:7" x14ac:dyDescent="0.4">
@@ -10626,13 +10570,13 @@
         <v>440</v>
       </c>
       <c r="D39" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F39" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G39" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="3:7" x14ac:dyDescent="0.4">
@@ -10640,16 +10584,16 @@
         <v>440</v>
       </c>
       <c r="D40" t="s">
+        <v>494</v>
+      </c>
+      <c r="E40" t="s">
         <v>495</v>
       </c>
-      <c r="E40" t="s">
-        <v>496</v>
-      </c>
       <c r="F40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G40" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10660,10 +10604,10 @@
         <v>407</v>
       </c>
       <c r="E41" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F41" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -10677,10 +10621,10 @@
         <v>407</v>
       </c>
       <c r="E42" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F42" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -10694,10 +10638,10 @@
         <v>407</v>
       </c>
       <c r="E43" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F43" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G43" t="s">
         <v>101</v>
@@ -10711,7 +10655,7 @@
         <v>408</v>
       </c>
       <c r="F44" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G44" t="s">
         <v>101</v>
@@ -10722,10 +10666,10 @@
         <v>440</v>
       </c>
       <c r="D45" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F45" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G45" t="s">
         <v>101</v>
@@ -10736,10 +10680,10 @@
         <v>440</v>
       </c>
       <c r="D46" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F46" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G46" t="s">
         <v>101</v>
@@ -10750,13 +10694,13 @@
         <v>434</v>
       </c>
       <c r="D47" t="s">
+        <v>489</v>
+      </c>
+      <c r="E47" t="s">
         <v>490</v>
       </c>
-      <c r="E47" t="s">
-        <v>491</v>
-      </c>
       <c r="F47" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G47" t="s">
         <v>101</v>
@@ -10767,10 +10711,10 @@
         <v>434</v>
       </c>
       <c r="D48" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F48" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G48" t="s">
         <v>101</v>
@@ -10781,10 +10725,10 @@
         <v>434</v>
       </c>
       <c r="D49" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F49" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G49" t="s">
         <v>101</v>
@@ -10795,10 +10739,10 @@
         <v>434</v>
       </c>
       <c r="D50" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F50" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G50" t="s">
         <v>101</v>
@@ -10806,13 +10750,13 @@
     </row>
     <row r="51" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="C51" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D51" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F51" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G51" t="s">
         <v>101</v>
@@ -10820,19 +10764,19 @@
     </row>
     <row r="52" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C52" t="s">
+        <v>506</v>
+      </c>
+      <c r="D52" t="s">
         <v>507</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>508</v>
       </c>
-      <c r="E52" t="s">
-        <v>509</v>
-      </c>
       <c r="F52" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G52" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="53" spans="3:7" hidden="1" x14ac:dyDescent="0.4">
@@ -10840,10 +10784,10 @@
         <v>430</v>
       </c>
       <c r="D53" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F53" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G53" t="s">
         <v>101</v>
@@ -10854,13 +10798,13 @@
         <v>440</v>
       </c>
       <c r="D54" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F54" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G54" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -10882,7 +10826,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043CC552-7D3A-4DC6-8319-C35A74AECC01}">
-  <dimension ref="B1:E20"/>
+  <dimension ref="B2:D20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="21.5" customWidth="1"/>
@@ -10890,15 +10834,7 @@
     <col min="4" max="4" width="61.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>29</v>
       </c>
@@ -10906,83 +10842,63 @@
         <v>443</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D4" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D6" t="s">
         <v>524</v>
       </c>
-      <c r="D6" t="s">
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D7" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D7" t="s">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D8" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D8" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D9" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C10" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D11" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="C12" t="s">
-        <v>531</v>
-      </c>
       <c r="D12" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D16" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D17" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D18" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D20" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3192938B-BE51-489C-9DF5-C5466B3DC8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCD1AD9-4E9B-4B26-9025-D503600BAF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="4965" windowWidth="24840" windowHeight="11820" firstSheet="1" activeTab="6" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="538">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -6116,6 +6116,19 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大砲のゲージのデバック間を消す</t>
+    <rPh sb="0" eb="2">
+      <t>タイホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ケ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10826,7 +10839,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043CC552-7D3A-4DC6-8319-C35A74AECC01}">
-  <dimension ref="B2:D20"/>
+  <dimension ref="B2:D16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="21.5" customWidth="1"/>
@@ -10891,14 +10904,19 @@
         <v>528</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D19" t="s">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D14" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D20" t="s">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D15" t="s">
         <v>535</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D16" t="s">
+        <v>537</v>
       </c>
     </row>
   </sheetData>

--- a/冬休みコスト表.xlsx
+++ b/冬休みコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2025_winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2025_winter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCD1AD9-4E9B-4B26-9025-D503600BAF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB621F4-C6D3-415B-9A01-16FA4DC5F628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
+    <workbookView xWindow="6900" yWindow="4965" windowWidth="24840" windowHeight="11820" firstSheet="1" activeTab="7" xr2:uid="{30C1D297-7632-433E-B4E2-F7DF95565528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="534">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -5990,16 +5990,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ボス戦などでのBgm変え</t>
-    <rPh sb="2" eb="3">
-      <t>セン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>タイトルシーンのタイトルロゴをパって出るのをやめる</t>
     <rPh sb="18" eb="19">
       <t>デ</t>
@@ -6007,16 +5997,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ハートの数を増やす</t>
-    <rPh sb="4" eb="5">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>フ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>赤いステージクリアしたらステージクリアシーンに行くようにする</t>
     <rPh sb="0" eb="1">
       <t>アカ</t>
@@ -6074,16 +6054,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>武器庫のマークがわかりづらいので、変える</t>
-    <rPh sb="0" eb="3">
-      <t>ブキコ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ドアを出すときのエフェクト</t>
     <rPh sb="3" eb="4">
       <t>ダ</t>
@@ -6116,19 +6086,6 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>シュウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>大砲のゲージのデバック間を消す</t>
-    <rPh sb="0" eb="2">
-      <t>タイホウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ケ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9530,7 +9487,7 @@
         <v>46044</v>
       </c>
       <c r="C321" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -10420,7 +10377,7 @@
         <v>435</v>
       </c>
       <c r="D28" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F28" t="s">
         <v>454</v>
@@ -10451,7 +10408,7 @@
         <v>435</v>
       </c>
       <c r="D30" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F30" t="s">
         <v>454</v>
@@ -10839,7 +10796,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043CC552-7D3A-4DC6-8319-C35A74AECC01}">
-  <dimension ref="B2:D16"/>
+  <dimension ref="B2:D15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="21.5" customWidth="1"/>
@@ -10855,32 +10812,19 @@
         <v>443</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="D4" t="s">
-        <v>533</v>
-      </c>
-    </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>523</v>
       </c>
-      <c r="D6" t="s">
-        <v>524</v>
-      </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D7" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="D8" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.4">
@@ -10890,33 +10834,28 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C11" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D11" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D12" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="D16" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
